--- a/Output/Data/meta_analysis_data.xlsx
+++ b/Output/Data/meta_analysis_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilylim/Documents/MSc/Course Work/Directed Readings/Meta_Analysis/Output/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilylim/Documents/MSc/Ch2-Meta-analysis/Output/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7708FD96-F156-FB4E-9A6C-9A7185710F28}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8861C88B-D63D-B847-8685-E54242DA9282}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11020" yWindow="460" windowWidth="26780" windowHeight="15940" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
+    <workbookView xWindow="10020" yWindow="2140" windowWidth="26780" windowHeight="15940" activeTab="2" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
   </bookViews>
   <sheets>
     <sheet name="Include" sheetId="1" r:id="rId1"/>

--- a/Output/Data/meta_analysis_data.xlsx
+++ b/Output/Data/meta_analysis_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilylim/Documents/MSc/Ch2-Meta-analysis/Output/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8861C88B-D63D-B847-8685-E54242DA9282}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47F9B81-BDD6-5F41-A566-200BDC1B9B52}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10020" yWindow="2140" windowWidth="26780" windowHeight="15940" activeTab="2" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
+    <workbookView xWindow="6820" yWindow="2140" windowWidth="26780" windowHeight="15940" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
   </bookViews>
   <sheets>
     <sheet name="Include" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7283" uniqueCount="1200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7283" uniqueCount="1199">
   <si>
     <t>paper_num</t>
   </si>
@@ -3072,9 +3072,6 @@
   </si>
   <si>
     <t>Halymeniaceae</t>
-  </si>
-  <si>
-    <t>spring-summer</t>
   </si>
   <si>
     <t>August 9th</t>
@@ -4468,7 +4465,7 @@
         <v>586</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AQ1" s="1" t="s">
         <v>320</v>
@@ -5087,16 +5084,16 @@
         <v>313</v>
       </c>
       <c r="AC6" s="11" t="s">
+        <v>936</v>
+      </c>
+      <c r="AD6" s="11" t="s">
         <v>937</v>
       </c>
-      <c r="AD6" s="11" t="s">
+      <c r="AE6" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="AF6" s="11" t="s">
         <v>938</v>
-      </c>
-      <c r="AE6" s="11" t="s">
-        <v>960</v>
-      </c>
-      <c r="AF6" s="11" t="s">
-        <v>939</v>
       </c>
       <c r="AG6" s="11" t="s">
         <v>923</v>
@@ -5230,16 +5227,16 @@
         <v>313</v>
       </c>
       <c r="AC7" s="11" t="s">
+        <v>936</v>
+      </c>
+      <c r="AD7" s="11" t="s">
         <v>937</v>
       </c>
-      <c r="AD7" s="11" t="s">
+      <c r="AE7" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="AF7" s="11" t="s">
         <v>938</v>
-      </c>
-      <c r="AE7" s="11" t="s">
-        <v>960</v>
-      </c>
-      <c r="AF7" s="11" t="s">
-        <v>939</v>
       </c>
       <c r="AG7" s="11" t="s">
         <v>923</v>
@@ -5388,7 +5385,7 @@
         <v>898</v>
       </c>
       <c r="AH8" s="1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="AI8" s="1" t="s">
         <v>362</v>
@@ -5397,7 +5394,7 @@
         <v>800</v>
       </c>
       <c r="AK8" s="1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="AL8" s="11" t="s">
         <v>315</v>
@@ -5531,7 +5528,7 @@
         <v>898</v>
       </c>
       <c r="AH9" s="1" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="AI9" s="1" t="s">
         <v>362</v>
@@ -5659,22 +5656,22 @@
         <v>313</v>
       </c>
       <c r="AC10" s="11" t="s">
+        <v>936</v>
+      </c>
+      <c r="AD10" s="11" t="s">
         <v>937</v>
       </c>
-      <c r="AD10" s="11" t="s">
+      <c r="AE10" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="AF10" s="11" t="s">
         <v>938</v>
-      </c>
-      <c r="AE10" s="11" t="s">
-        <v>960</v>
-      </c>
-      <c r="AF10" s="11" t="s">
-        <v>939</v>
       </c>
       <c r="AG10" s="11" t="s">
         <v>923</v>
       </c>
       <c r="AH10" s="11" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="AI10" s="11" t="s">
         <v>362</v>
@@ -5713,7 +5710,7 @@
         <v>9</v>
       </c>
       <c r="AU10" s="1" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="11" spans="1:47">
@@ -5802,22 +5799,22 @@
         <v>313</v>
       </c>
       <c r="AC11" s="11" t="s">
+        <v>936</v>
+      </c>
+      <c r="AD11" s="11" t="s">
         <v>937</v>
       </c>
-      <c r="AD11" s="11" t="s">
+      <c r="AE11" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="AF11" s="11" t="s">
         <v>938</v>
-      </c>
-      <c r="AE11" s="11" t="s">
-        <v>960</v>
-      </c>
-      <c r="AF11" s="11" t="s">
-        <v>939</v>
       </c>
       <c r="AG11" s="11" t="s">
         <v>923</v>
       </c>
       <c r="AH11" s="11" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="AI11" s="11" t="s">
         <v>362</v>
@@ -5856,7 +5853,7 @@
         <v>9</v>
       </c>
       <c r="AU11" s="1" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="12" spans="1:47">
@@ -5960,7 +5957,7 @@
         <v>898</v>
       </c>
       <c r="AH12" s="11" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="AI12" s="11" t="s">
         <v>362</v>
@@ -5969,7 +5966,7 @@
         <v>800</v>
       </c>
       <c r="AK12" s="11" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="AL12" s="11" t="s">
         <v>315</v>
@@ -5999,7 +5996,7 @@
         <v>9</v>
       </c>
       <c r="AU12" s="1" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="13" spans="1:47">
@@ -6103,7 +6100,7 @@
         <v>898</v>
       </c>
       <c r="AH13" s="11" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="AI13" s="11" t="s">
         <v>362</v>
@@ -6142,7 +6139,7 @@
         <v>9</v>
       </c>
       <c r="AU13" s="1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="14" spans="1:47">
@@ -6328,7 +6325,7 @@
         <v>424</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="R15" s="1" t="s">
         <v>315</v>
@@ -6340,7 +6337,7 @@
         <v>315</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="V15" s="1" t="s">
         <v>295</v>
@@ -6355,16 +6352,16 @@
         <v>581</v>
       </c>
       <c r="Z15" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="AA15" s="1" t="s">
         <v>975</v>
-      </c>
-      <c r="AA15" s="1" t="s">
-        <v>976</v>
       </c>
       <c r="AB15" s="1" t="s">
         <v>295</v>
       </c>
       <c r="AC15" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="AD15" s="1" t="s">
         <v>662</v>
@@ -6373,10 +6370,10 @@
         <v>601</v>
       </c>
       <c r="AF15" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="AG15" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="AH15" s="1" t="s">
         <v>615</v>
@@ -6418,7 +6415,7 @@
         <v>12</v>
       </c>
       <c r="AU15" s="1" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="16" spans="1:47">
@@ -6471,7 +6468,7 @@
         <v>424</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="R16" s="1" t="s">
         <v>315</v>
@@ -6483,7 +6480,7 @@
         <v>315</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="V16" s="1" t="s">
         <v>295</v>
@@ -6498,16 +6495,16 @@
         <v>581</v>
       </c>
       <c r="Z16" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="AA16" s="1" t="s">
         <v>975</v>
-      </c>
-      <c r="AA16" s="1" t="s">
-        <v>976</v>
       </c>
       <c r="AB16" s="1" t="s">
         <v>295</v>
       </c>
       <c r="AC16" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="AD16" s="1" t="s">
         <v>662</v>
@@ -6516,10 +6513,10 @@
         <v>601</v>
       </c>
       <c r="AF16" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="AG16" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="AH16" s="1" t="s">
         <v>640</v>
@@ -6561,7 +6558,7 @@
         <v>12</v>
       </c>
       <c r="AU16" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="17" spans="1:47">
@@ -6704,7 +6701,7 @@
         <v>3</v>
       </c>
       <c r="AU17" s="1" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="18" spans="1:47">
@@ -6847,7 +6844,7 @@
         <v>3</v>
       </c>
       <c r="AU18" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="19" spans="1:47">
@@ -7928,7 +7925,7 @@
         <v>723</v>
       </c>
       <c r="AG26" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="AH26" s="1" t="s">
         <v>593</v>
@@ -7970,7 +7967,7 @@
         <v>5</v>
       </c>
       <c r="AU26" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="27" spans="1:47">
@@ -8068,7 +8065,7 @@
         <v>723</v>
       </c>
       <c r="AG27" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="AH27" s="1" t="s">
         <v>593</v>
@@ -8110,7 +8107,7 @@
         <v>8</v>
       </c>
       <c r="AU27" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="28" spans="1:47">
@@ -8208,7 +8205,7 @@
         <v>723</v>
       </c>
       <c r="AG28" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="AH28" s="1" t="s">
         <v>593</v>
@@ -8250,7 +8247,7 @@
         <v>3</v>
       </c>
       <c r="AU28" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="29" spans="1:47">
@@ -8348,7 +8345,7 @@
         <v>723</v>
       </c>
       <c r="AG29" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="AH29" s="1" t="s">
         <v>593</v>
@@ -8390,7 +8387,7 @@
         <v>4</v>
       </c>
       <c r="AU29" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="30" spans="1:47">
@@ -8488,7 +8485,7 @@
         <v>723</v>
       </c>
       <c r="AG30" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="AH30" s="1" t="s">
         <v>593</v>
@@ -8530,7 +8527,7 @@
         <v>4</v>
       </c>
       <c r="AU30" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="31" spans="1:47">
@@ -8583,7 +8580,7 @@
         <v>294</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="R31" s="1" t="s">
         <v>315</v>
@@ -8601,7 +8598,7 @@
         <v>295</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="X31" s="1" t="s">
         <v>662</v>
@@ -8610,16 +8607,16 @@
         <v>663</v>
       </c>
       <c r="Z31" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="AA31" s="1" t="s">
         <v>1103</v>
-      </c>
-      <c r="AA31" s="1" t="s">
-        <v>1104</v>
       </c>
       <c r="AB31" s="1" t="s">
         <v>295</v>
       </c>
       <c r="AC31" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="AD31" s="1" t="s">
         <v>618</v>
@@ -8628,10 +8625,10 @@
         <v>621</v>
       </c>
       <c r="AF31" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AG31" s="1" t="s">
         <v>1100</v>
-      </c>
-      <c r="AG31" s="1" t="s">
-        <v>1101</v>
       </c>
       <c r="AH31" s="1" t="s">
         <v>715</v>
@@ -8673,7 +8670,7 @@
         <v>10</v>
       </c>
       <c r="AU31" s="1" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="32" spans="1:47">
@@ -9167,7 +9164,7 @@
         <v>315</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="V35" s="1" t="s">
         <v>345</v>
@@ -9242,7 +9239,7 @@
         <v>15</v>
       </c>
       <c r="AU35" s="1" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="36" spans="1:47">
@@ -9307,7 +9304,7 @@
         <v>315</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="V36" s="1" t="s">
         <v>345</v>
@@ -9334,10 +9331,10 @@
         <v>315</v>
       </c>
       <c r="AD36" s="1" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="AE36" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="AF36" s="1" t="s">
         <v>315</v>
@@ -9382,7 +9379,7 @@
         <v>15</v>
       </c>
       <c r="AU36" s="1" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="37" spans="1:47">
@@ -9447,7 +9444,7 @@
         <v>315</v>
       </c>
       <c r="U37" s="11" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="V37" s="1" t="s">
         <v>345</v>
@@ -9474,10 +9471,10 @@
         <v>315</v>
       </c>
       <c r="AD37" s="1" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="AE37" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="AF37" s="1" t="s">
         <v>315</v>
@@ -9522,7 +9519,7 @@
         <v>15</v>
       </c>
       <c r="AU37" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="38" spans="1:47">
@@ -9587,7 +9584,7 @@
         <v>315</v>
       </c>
       <c r="U38" s="11" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="V38" s="1" t="s">
         <v>345</v>
@@ -9614,10 +9611,10 @@
         <v>315</v>
       </c>
       <c r="AD38" s="1" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="AE38" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="AF38" s="1" t="s">
         <v>315</v>
@@ -9662,7 +9659,7 @@
         <v>15</v>
       </c>
       <c r="AU38" s="1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="39" spans="1:47">
@@ -9727,7 +9724,7 @@
         <v>315</v>
       </c>
       <c r="U39" s="11" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="V39" s="1" t="s">
         <v>345</v>
@@ -9802,7 +9799,7 @@
         <v>15</v>
       </c>
       <c r="AU39" s="1" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="40" spans="1:47">
@@ -9867,7 +9864,7 @@
         <v>315</v>
       </c>
       <c r="U40" s="11" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="V40" s="1" t="s">
         <v>345</v>
@@ -9942,7 +9939,7 @@
         <v>15</v>
       </c>
       <c r="AU40" s="1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="41" spans="1:47">
@@ -10007,7 +10004,7 @@
         <v>315</v>
       </c>
       <c r="U41" s="11" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="V41" s="1" t="s">
         <v>345</v>
@@ -10082,7 +10079,7 @@
         <v>15</v>
       </c>
       <c r="AU41" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="42" spans="1:47">
@@ -10195,7 +10192,7 @@
         <v>722</v>
       </c>
       <c r="AK42" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="AL42" s="1" t="s">
         <v>315</v>
@@ -10225,7 +10222,7 @@
         <v>50</v>
       </c>
       <c r="AU42" s="1" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="43" spans="1:47">
@@ -10338,7 +10335,7 @@
         <v>722</v>
       </c>
       <c r="AK43" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="AL43" s="1" t="s">
         <v>315</v>
@@ -10368,7 +10365,7 @@
         <v>60</v>
       </c>
       <c r="AU43" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="44" spans="1:47">
@@ -10481,7 +10478,7 @@
         <v>722</v>
       </c>
       <c r="AK44" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="AL44" s="1" t="s">
         <v>315</v>
@@ -10511,7 +10508,7 @@
         <v>60</v>
       </c>
       <c r="AU44" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="45" spans="1:47">
@@ -10624,7 +10621,7 @@
         <v>722</v>
       </c>
       <c r="AK45" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="AL45" s="1" t="s">
         <v>315</v>
@@ -10654,7 +10651,7 @@
         <v>60</v>
       </c>
       <c r="AU45" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="46" spans="1:47">
@@ -10767,7 +10764,7 @@
         <v>722</v>
       </c>
       <c r="AK46" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="AL46" s="1" t="s">
         <v>315</v>
@@ -10797,7 +10794,7 @@
         <v>60</v>
       </c>
       <c r="AU46" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="47" spans="1:47">
@@ -10910,7 +10907,7 @@
         <v>722</v>
       </c>
       <c r="AK47" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="AL47" s="1" t="s">
         <v>315</v>
@@ -10940,7 +10937,7 @@
         <v>50</v>
       </c>
       <c r="AU47" s="1" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="48" spans="1:47">
@@ -11053,7 +11050,7 @@
         <v>722</v>
       </c>
       <c r="AK48" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="AL48" s="1" t="s">
         <v>315</v>
@@ -11083,7 +11080,7 @@
         <v>60</v>
       </c>
       <c r="AU48" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="49" spans="1:47">
@@ -11196,7 +11193,7 @@
         <v>722</v>
       </c>
       <c r="AK49" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="AL49" s="1" t="s">
         <v>315</v>
@@ -11226,7 +11223,7 @@
         <v>60</v>
       </c>
       <c r="AU49" s="1" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="50" spans="1:47">
@@ -11339,7 +11336,7 @@
         <v>722</v>
       </c>
       <c r="AK50" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="AL50" s="1" t="s">
         <v>315</v>
@@ -11369,7 +11366,7 @@
         <v>60</v>
       </c>
       <c r="AU50" s="1" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="51" spans="1:47">
@@ -11482,7 +11479,7 @@
         <v>722</v>
       </c>
       <c r="AK51" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="AL51" s="1" t="s">
         <v>315</v>
@@ -11512,7 +11509,7 @@
         <v>60</v>
       </c>
       <c r="AU51" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="52" spans="1:47">
@@ -17316,10 +17313,10 @@
         <v>315</v>
       </c>
       <c r="AD92" s="1" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="AE92" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="AF92" s="1" t="s">
         <v>315</v>
@@ -17337,7 +17334,7 @@
         <v>800</v>
       </c>
       <c r="AK92" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="AL92" s="1" t="s">
         <v>671</v>
@@ -17367,7 +17364,7 @@
         <v>4</v>
       </c>
       <c r="AU92" s="1" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="93" spans="1:47">
@@ -17510,7 +17507,7 @@
         <v>3</v>
       </c>
       <c r="AU93" s="1" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="94" spans="1:47">
@@ -18043,7 +18040,7 @@
         <v>600</v>
       </c>
       <c r="AH97" s="1" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="AI97" s="1" t="s">
         <v>362</v>
@@ -18901,7 +18898,7 @@
         <v>362</v>
       </c>
       <c r="AJ103" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK103" s="1" t="s">
         <v>832</v>
@@ -18934,7 +18931,7 @@
         <v>10</v>
       </c>
       <c r="AU103" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="104" spans="1:47">
@@ -19038,7 +19035,7 @@
         <v>362</v>
       </c>
       <c r="AJ104" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK104" s="1" t="s">
         <v>832</v>
@@ -19071,7 +19068,7 @@
         <v>10</v>
       </c>
       <c r="AU104" s="1" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="105" spans="1:47">
@@ -19175,7 +19172,7 @@
         <v>362</v>
       </c>
       <c r="AJ105" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK105" s="1" t="s">
         <v>832</v>
@@ -19208,7 +19205,7 @@
         <v>10</v>
       </c>
       <c r="AU105" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="106" spans="1:47">
@@ -19312,7 +19309,7 @@
         <v>362</v>
       </c>
       <c r="AJ106" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK106" s="1" t="s">
         <v>832</v>
@@ -19345,7 +19342,7 @@
         <v>10</v>
       </c>
       <c r="AU106" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="107" spans="1:47">
@@ -19449,7 +19446,7 @@
         <v>362</v>
       </c>
       <c r="AJ107" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK107" s="1" t="s">
         <v>832</v>
@@ -19482,7 +19479,7 @@
         <v>10</v>
       </c>
       <c r="AU107" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="108" spans="1:47">
@@ -19586,7 +19583,7 @@
         <v>362</v>
       </c>
       <c r="AJ108" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK108" s="1" t="s">
         <v>832</v>
@@ -19619,7 +19616,7 @@
         <v>10</v>
       </c>
       <c r="AU108" s="1" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="109" spans="1:47">
@@ -19723,7 +19720,7 @@
         <v>362</v>
       </c>
       <c r="AJ109" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK109" s="1" t="s">
         <v>832</v>
@@ -19756,7 +19753,7 @@
         <v>10</v>
       </c>
       <c r="AU109" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="110" spans="1:47">
@@ -19860,7 +19857,7 @@
         <v>362</v>
       </c>
       <c r="AJ110" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK110" s="1" t="s">
         <v>832</v>
@@ -19893,7 +19890,7 @@
         <v>9</v>
       </c>
       <c r="AU110" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="111" spans="1:47">
@@ -19997,7 +19994,7 @@
         <v>362</v>
       </c>
       <c r="AJ111" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK111" s="1" t="s">
         <v>832</v>
@@ -20030,7 +20027,7 @@
         <v>9</v>
       </c>
       <c r="AU111" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="112" spans="1:47">
@@ -20134,7 +20131,7 @@
         <v>362</v>
       </c>
       <c r="AJ112" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK112" s="1" t="s">
         <v>832</v>
@@ -20167,7 +20164,7 @@
         <v>9</v>
       </c>
       <c r="AU112" s="1" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="113" spans="1:47">
@@ -20271,7 +20268,7 @@
         <v>362</v>
       </c>
       <c r="AJ113" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK113" s="1" t="s">
         <v>832</v>
@@ -20304,7 +20301,7 @@
         <v>9</v>
       </c>
       <c r="AU113" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="114" spans="1:47">
@@ -20408,7 +20405,7 @@
         <v>362</v>
       </c>
       <c r="AJ114" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK114" s="1" t="s">
         <v>832</v>
@@ -20441,7 +20438,7 @@
         <v>9</v>
       </c>
       <c r="AU114" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="115" spans="1:47" customFormat="1">
@@ -20551,7 +20548,7 @@
         <v>362</v>
       </c>
       <c r="AJ115" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="AK115" s="1" t="s">
         <v>584</v>
@@ -20584,7 +20581,7 @@
         <v>5</v>
       </c>
       <c r="AU115" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="116" spans="1:47" customFormat="1">
@@ -20694,7 +20691,7 @@
         <v>362</v>
       </c>
       <c r="AJ116" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="AK116" s="1" t="s">
         <v>584</v>
@@ -20727,7 +20724,7 @@
         <v>5</v>
       </c>
       <c r="AU116" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="117" spans="1:47" customFormat="1">
@@ -20837,10 +20834,10 @@
         <v>362</v>
       </c>
       <c r="AJ117" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="AK117" s="1" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="AL117" s="1" t="s">
         <v>315</v>
@@ -20870,7 +20867,7 @@
         <v>5</v>
       </c>
       <c r="AU117" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="118" spans="1:47" customFormat="1">
@@ -20980,10 +20977,10 @@
         <v>362</v>
       </c>
       <c r="AJ118" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="AK118" s="1" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="AL118" s="1" t="s">
         <v>315</v>
@@ -21013,7 +21010,7 @@
         <v>5</v>
       </c>
       <c r="AU118" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="119" spans="1:47" customFormat="1">
@@ -21117,16 +21114,16 @@
         <v>813</v>
       </c>
       <c r="AH119" s="1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="AI119" s="1" t="s">
         <v>362</v>
       </c>
       <c r="AJ119" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="AK119" s="1" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="AL119" s="1" t="s">
         <v>315</v>
@@ -21156,7 +21153,7 @@
         <v>5</v>
       </c>
       <c r="AU119" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="120" spans="1:47" customFormat="1">
@@ -21260,16 +21257,16 @@
         <v>813</v>
       </c>
       <c r="AH120" s="1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="AI120" s="1" t="s">
         <v>362</v>
       </c>
       <c r="AJ120" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="AK120" s="1" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="AL120" s="1" t="s">
         <v>315</v>
@@ -21299,7 +21296,7 @@
         <v>5</v>
       </c>
       <c r="AU120" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="121" spans="1:47">
@@ -24150,7 +24147,7 @@
         <v>295</v>
       </c>
       <c r="W141" s="1" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="X141" s="1" t="s">
         <v>885</v>
@@ -24171,10 +24168,10 @@
         <v>315</v>
       </c>
       <c r="AD141" s="1" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="AE141" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="AF141" s="1" t="s">
         <v>315</v>
@@ -24222,7 +24219,7 @@
         <v>4</v>
       </c>
       <c r="AU141" s="7" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="142" spans="1:47">
@@ -24308,28 +24305,28 @@
         <v>295</v>
       </c>
       <c r="AC142" s="1" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="AD142" s="1" t="s">
         <v>347</v>
       </c>
       <c r="AE142" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="AF142" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="AG142" s="1" t="s">
         <v>1073</v>
       </c>
-      <c r="AG142" s="1" t="s">
-        <v>1074</v>
-      </c>
       <c r="AH142" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AI142" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AJ142" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK142" s="1" t="s">
         <v>318</v>
@@ -24362,7 +24359,7 @@
         <v>3</v>
       </c>
       <c r="AU142" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="143" spans="1:47">
@@ -24448,28 +24445,28 @@
         <v>295</v>
       </c>
       <c r="AC143" s="1" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="AD143" s="1" t="s">
         <v>347</v>
       </c>
       <c r="AE143" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="AF143" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="AG143" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="AH143" s="1" t="s">
         <v>1082</v>
       </c>
-      <c r="AG143" s="1" t="s">
-        <v>1076</v>
-      </c>
-      <c r="AH143" s="1" t="s">
-        <v>1083</v>
-      </c>
       <c r="AI143" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AJ143" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK143" s="1" t="s">
         <v>318</v>
@@ -24502,7 +24499,7 @@
         <v>3</v>
       </c>
       <c r="AU143" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="144" spans="1:47">
@@ -24588,7 +24585,7 @@
         <v>295</v>
       </c>
       <c r="AC144" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="AD144" s="1" t="s">
         <v>347</v>
@@ -24597,19 +24594,19 @@
         <v>348</v>
       </c>
       <c r="AF144" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AG144" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="AH144" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AI144" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AJ144" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK144" s="1" t="s">
         <v>318</v>
@@ -24642,7 +24639,7 @@
         <v>3</v>
       </c>
       <c r="AU144" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="145" spans="1:47">
@@ -24740,16 +24737,16 @@
         <v>842</v>
       </c>
       <c r="AG145" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AH145" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AI145" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AJ145" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK145" s="1" t="s">
         <v>318</v>
@@ -24782,7 +24779,7 @@
         <v>3</v>
       </c>
       <c r="AU145" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="146" spans="1:47">
@@ -24823,7 +24820,7 @@
         <v>270</v>
       </c>
       <c r="M146" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="N146" s="1" t="s">
         <v>291</v>
@@ -24862,34 +24859,34 @@
         <v>582</v>
       </c>
       <c r="AA146" s="1" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="AB146" s="1" t="s">
         <v>295</v>
       </c>
       <c r="AC146" s="1" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="AD146" s="1" t="s">
         <v>347</v>
       </c>
       <c r="AE146" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="AF146" s="1" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="AG146" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="AH146" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AI146" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AJ146" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK146" s="1" t="s">
         <v>318</v>
@@ -24922,7 +24919,7 @@
         <v>3</v>
       </c>
       <c r="AU146" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="147" spans="1:47">
@@ -24963,7 +24960,7 @@
         <v>270</v>
       </c>
       <c r="M147" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="N147" s="1" t="s">
         <v>291</v>
@@ -25002,13 +24999,13 @@
         <v>582</v>
       </c>
       <c r="AA147" s="1" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="AB147" s="1" t="s">
         <v>295</v>
       </c>
       <c r="AC147" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="AD147" s="1" t="s">
         <v>347</v>
@@ -25017,19 +25014,19 @@
         <v>348</v>
       </c>
       <c r="AF147" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AG147" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="AH147" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AI147" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AJ147" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK147" s="1" t="s">
         <v>318</v>
@@ -25062,7 +25059,7 @@
         <v>3</v>
       </c>
       <c r="AU147" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="148" spans="1:47">
@@ -25130,7 +25127,7 @@
         <v>295</v>
       </c>
       <c r="W148" s="1" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="X148" s="1" t="s">
         <v>306</v>
@@ -25139,37 +25136,37 @@
         <v>307</v>
       </c>
       <c r="Z148" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="AA148" s="1" t="s">
         <v>1066</v>
-      </c>
-      <c r="AA148" s="1" t="s">
-        <v>1067</v>
       </c>
       <c r="AB148" s="1" t="s">
         <v>295</v>
       </c>
       <c r="AC148" s="1" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="AD148" s="1" t="s">
         <v>347</v>
       </c>
       <c r="AE148" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="AF148" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="AG148" s="1" t="s">
         <v>1073</v>
       </c>
-      <c r="AG148" s="1" t="s">
-        <v>1074</v>
-      </c>
       <c r="AH148" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AI148" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AJ148" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK148" s="1" t="s">
         <v>318</v>
@@ -25202,7 +25199,7 @@
         <v>3</v>
       </c>
       <c r="AU148" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="149" spans="1:47">
@@ -25270,7 +25267,7 @@
         <v>295</v>
       </c>
       <c r="W149" s="1" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="X149" s="1" t="s">
         <v>306</v>
@@ -25279,37 +25276,37 @@
         <v>307</v>
       </c>
       <c r="Z149" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="AA149" s="1" t="s">
         <v>1066</v>
-      </c>
-      <c r="AA149" s="1" t="s">
-        <v>1067</v>
       </c>
       <c r="AB149" s="1" t="s">
         <v>295</v>
       </c>
       <c r="AC149" s="1" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="AD149" s="1" t="s">
         <v>347</v>
       </c>
       <c r="AE149" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="AF149" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="AG149" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="AH149" s="1" t="s">
         <v>1082</v>
       </c>
-      <c r="AG149" s="1" t="s">
-        <v>1076</v>
-      </c>
-      <c r="AH149" s="1" t="s">
-        <v>1083</v>
-      </c>
       <c r="AI149" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AJ149" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK149" s="1" t="s">
         <v>318</v>
@@ -25342,7 +25339,7 @@
         <v>3</v>
       </c>
       <c r="AU149" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="150" spans="1:47">
@@ -25410,7 +25407,7 @@
         <v>295</v>
       </c>
       <c r="W150" s="1" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="X150" s="1" t="s">
         <v>306</v>
@@ -25419,16 +25416,16 @@
         <v>307</v>
       </c>
       <c r="Z150" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="AA150" s="1" t="s">
         <v>1066</v>
-      </c>
-      <c r="AA150" s="1" t="s">
-        <v>1067</v>
       </c>
       <c r="AB150" s="1" t="s">
         <v>295</v>
       </c>
       <c r="AC150" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="AD150" s="1" t="s">
         <v>347</v>
@@ -25437,19 +25434,19 @@
         <v>348</v>
       </c>
       <c r="AF150" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AG150" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="AH150" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AI150" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AJ150" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK150" s="1" t="s">
         <v>318</v>
@@ -25482,7 +25479,7 @@
         <v>3</v>
       </c>
       <c r="AU150" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="151" spans="1:47">
@@ -25550,7 +25547,7 @@
         <v>295</v>
       </c>
       <c r="W151" s="1" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="X151" s="1" t="s">
         <v>306</v>
@@ -25559,10 +25556,10 @@
         <v>307</v>
       </c>
       <c r="Z151" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="AA151" s="1" t="s">
         <v>1066</v>
-      </c>
-      <c r="AA151" s="1" t="s">
-        <v>1067</v>
       </c>
       <c r="AB151" s="1" t="s">
         <v>295</v>
@@ -25580,16 +25577,16 @@
         <v>842</v>
       </c>
       <c r="AG151" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="AH151" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AI151" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AJ151" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK151" s="1" t="s">
         <v>318</v>
@@ -25622,7 +25619,7 @@
         <v>3</v>
       </c>
       <c r="AU151" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="152" spans="1:47">
@@ -25663,7 +25660,7 @@
         <v>270</v>
       </c>
       <c r="M152" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="N152" s="1" t="s">
         <v>291</v>
@@ -25690,7 +25687,7 @@
         <v>295</v>
       </c>
       <c r="W152" s="1" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="X152" s="1" t="s">
         <v>306</v>
@@ -25699,37 +25696,37 @@
         <v>307</v>
       </c>
       <c r="Z152" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="AA152" s="1" t="s">
         <v>1070</v>
-      </c>
-      <c r="AA152" s="1" t="s">
-        <v>1071</v>
       </c>
       <c r="AB152" s="1" t="s">
         <v>295</v>
       </c>
       <c r="AC152" s="1" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="AD152" s="1" t="s">
         <v>347</v>
       </c>
       <c r="AE152" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="AF152" s="1" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="AG152" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="AH152" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AI152" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AJ152" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK152" s="1" t="s">
         <v>318</v>
@@ -25762,7 +25759,7 @@
         <v>3</v>
       </c>
       <c r="AU152" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="153" spans="1:47">
@@ -25803,7 +25800,7 @@
         <v>270</v>
       </c>
       <c r="M153" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="N153" s="1" t="s">
         <v>291</v>
@@ -25830,7 +25827,7 @@
         <v>295</v>
       </c>
       <c r="W153" s="1" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="X153" s="1" t="s">
         <v>306</v>
@@ -25839,16 +25836,16 @@
         <v>307</v>
       </c>
       <c r="Z153" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="AA153" s="1" t="s">
         <v>1070</v>
-      </c>
-      <c r="AA153" s="1" t="s">
-        <v>1071</v>
       </c>
       <c r="AB153" s="1" t="s">
         <v>295</v>
       </c>
       <c r="AC153" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="AD153" s="1" t="s">
         <v>347</v>
@@ -25857,19 +25854,19 @@
         <v>348</v>
       </c>
       <c r="AF153" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="AG153" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="AH153" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AI153" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="AJ153" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK153" s="1" t="s">
         <v>318</v>
@@ -25902,7 +25899,7 @@
         <v>3</v>
       </c>
       <c r="AU153" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="154" spans="1:47">
@@ -26250,7 +26247,7 @@
         <v>315</v>
       </c>
       <c r="U156" s="11" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="V156" s="1" t="s">
         <v>313</v>
@@ -26614,7 +26611,7 @@
         <v>10</v>
       </c>
       <c r="AU158" s="1" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="159" spans="1:47">
@@ -26757,12 +26754,12 @@
         <v>10</v>
       </c>
       <c r="AU159" s="1" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="160" spans="1:47">
       <c r="A160" s="1">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B160" s="1">
         <v>3</v>
@@ -26819,7 +26816,7 @@
         <v>336</v>
       </c>
       <c r="T160" s="11" t="s">
-        <v>931</v>
+        <v>578</v>
       </c>
       <c r="U160" s="11">
         <v>2005</v>
@@ -26900,12 +26897,12 @@
         <v>5</v>
       </c>
       <c r="AU160" s="1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="161" spans="1:47">
       <c r="A161" s="1">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B161" s="11">
         <v>1</v>
@@ -26971,7 +26968,7 @@
         <v>295</v>
       </c>
       <c r="W161" s="11" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="X161" s="11" t="s">
         <v>879</v>
@@ -26980,10 +26977,10 @@
         <v>880</v>
       </c>
       <c r="Z161" s="11" t="s">
+        <v>1137</v>
+      </c>
+      <c r="AA161" s="11" t="s">
         <v>1138</v>
-      </c>
-      <c r="AA161" s="11" t="s">
-        <v>1139</v>
       </c>
       <c r="AB161" s="11" t="s">
         <v>345</v>
@@ -27010,10 +27007,10 @@
         <v>362</v>
       </c>
       <c r="AJ161" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="AK161" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="AL161" s="1" t="s">
         <v>315</v>
@@ -27043,7 +27040,7 @@
         <v>3</v>
       </c>
       <c r="AU161" s="1" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="162" spans="1:47">
@@ -27228,10 +27225,10 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B1" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="C1" t="s">
         <v>318</v>
@@ -27240,7 +27237,7 @@
         <v>682</v>
       </c>
       <c r="E1" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -27390,12 +27387,12 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="D1" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="2" spans="1:20">
       <c r="D2" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="3" spans="1:20">
@@ -27405,66 +27402,66 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B4" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="C4" t="s">
         <v>683</v>
       </c>
       <c r="D4" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E4" t="s">
         <v>1046</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>1044</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="J4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="K4" t="s">
+        <v>1049</v>
+      </c>
+      <c r="L4" t="s">
+        <v>1050</v>
+      </c>
+      <c r="M4" t="s">
+        <v>1048</v>
+      </c>
+      <c r="N4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="O4" t="s">
         <v>1047</v>
       </c>
-      <c r="F4" t="s">
-        <v>1045</v>
-      </c>
-      <c r="G4" t="s">
-        <v>1003</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="P4" t="s">
         <v>1042</v>
-      </c>
-      <c r="I4" t="s">
-        <v>1041</v>
-      </c>
-      <c r="J4" t="s">
-        <v>1040</v>
-      </c>
-      <c r="K4" t="s">
-        <v>1050</v>
-      </c>
-      <c r="L4" t="s">
-        <v>1051</v>
-      </c>
-      <c r="M4" t="s">
-        <v>1049</v>
-      </c>
-      <c r="N4" t="s">
-        <v>1042</v>
-      </c>
-      <c r="O4" t="s">
-        <v>1048</v>
-      </c>
-      <c r="P4" t="s">
-        <v>1043</v>
       </c>
       <c r="R4" t="s">
         <v>319</v>
       </c>
       <c r="S4" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="T4" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B5">
         <v>0.2</v>
@@ -27536,7 +27533,7 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B6">
         <v>0.04</v>
@@ -27566,7 +27563,7 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B7">
         <v>0.05</v>
@@ -27624,7 +27621,7 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B8">
         <v>0.11</v>
@@ -27657,30 +27654,30 @@
         <v>699</v>
       </c>
       <c r="B10" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="C10" t="s">
         <v>683</v>
       </c>
       <c r="D10" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E10" t="s">
         <v>1046</v>
-      </c>
-      <c r="E10" t="s">
-        <v>1047</v>
       </c>
       <c r="R10" t="s">
         <v>320</v>
       </c>
       <c r="S10" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="T10" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B11">
         <v>0.14000000000000001</v>
@@ -27752,7 +27749,7 @@
     </row>
     <row r="12" spans="1:20">
       <c r="A12" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B12">
         <v>3.7999999999999999E-2</v>
@@ -27782,7 +27779,7 @@
     </row>
     <row r="13" spans="1:20">
       <c r="A13" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B13">
         <v>0.17</v>
@@ -27840,7 +27837,7 @@
     </row>
     <row r="18" spans="1:20">
       <c r="A18" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B18" t="s">
         <v>696</v>
@@ -27849,27 +27846,27 @@
         <v>683</v>
       </c>
       <c r="D18" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E18" t="s">
         <v>1046</v>
       </c>
-      <c r="E18" t="s">
-        <v>1047</v>
-      </c>
       <c r="F18" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="R18" t="s">
         <v>319</v>
       </c>
       <c r="S18" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="T18" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="19" spans="1:20">
       <c r="A19" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B19">
         <v>0.76</v>
@@ -27941,7 +27938,7 @@
     </row>
     <row r="20" spans="1:20">
       <c r="A20" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B20">
         <v>0.28999999999999998</v>
@@ -27971,7 +27968,7 @@
     </row>
     <row r="21" spans="1:20">
       <c r="A21" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B21">
         <v>0.44</v>
@@ -28029,7 +28026,7 @@
     </row>
     <row r="22" spans="1:20">
       <c r="A22" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B22">
         <v>0.49</v>
@@ -28062,33 +28059,33 @@
         <v>699</v>
       </c>
       <c r="B24" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="C24" t="s">
         <v>683</v>
       </c>
       <c r="D24" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E24" t="s">
         <v>1046</v>
       </c>
-      <c r="E24" t="s">
-        <v>1047</v>
-      </c>
       <c r="F24" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="R24" t="s">
         <v>320</v>
       </c>
       <c r="S24" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="T24" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="25" spans="1:20">
       <c r="A25" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B25">
         <v>0.82</v>
@@ -28160,7 +28157,7 @@
     </row>
     <row r="26" spans="1:20">
       <c r="A26" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B26">
         <v>0.4</v>
@@ -28190,7 +28187,7 @@
     </row>
     <row r="27" spans="1:20">
       <c r="A27" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B27">
         <v>0.39</v>
@@ -28437,7 +28434,7 @@
   <sheetData>
     <row r="1" spans="1:49" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -28584,7 +28581,7 @@
     </row>
     <row r="2" spans="1:49" s="1" customFormat="1">
       <c r="A2" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -28731,7 +28728,7 @@
     </row>
     <row r="3" spans="1:49" s="1" customFormat="1">
       <c r="A3" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B3" s="1">
         <v>1</v>
@@ -28878,7 +28875,7 @@
     </row>
     <row r="4" spans="1:49" s="1" customFormat="1">
       <c r="A4" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B4" s="1">
         <v>1</v>
@@ -29025,7 +29022,7 @@
     </row>
     <row r="5" spans="1:49" s="1" customFormat="1">
       <c r="A5" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B5" s="1">
         <v>2</v>
@@ -29112,16 +29109,16 @@
         <v>313</v>
       </c>
       <c r="AD5" s="11" t="s">
+        <v>936</v>
+      </c>
+      <c r="AE5" s="11" t="s">
         <v>937</v>
       </c>
-      <c r="AE5" s="11" t="s">
+      <c r="AF5" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="AG5" s="11" t="s">
         <v>938</v>
-      </c>
-      <c r="AF5" s="11" t="s">
-        <v>960</v>
-      </c>
-      <c r="AG5" s="11" t="s">
-        <v>939</v>
       </c>
       <c r="AH5" s="11" t="s">
         <v>923</v>
@@ -29167,12 +29164,12 @@
       </c>
       <c r="AV5"/>
       <c r="AW5" s="11" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="6" spans="1:49" s="1" customFormat="1">
       <c r="A6" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B6" s="1">
         <v>2</v>
@@ -29259,16 +29256,16 @@
         <v>313</v>
       </c>
       <c r="AD6" s="11" t="s">
+        <v>936</v>
+      </c>
+      <c r="AE6" s="11" t="s">
         <v>937</v>
       </c>
-      <c r="AE6" s="11" t="s">
+      <c r="AF6" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="AG6" s="11" t="s">
         <v>938</v>
-      </c>
-      <c r="AF6" s="11" t="s">
-        <v>960</v>
-      </c>
-      <c r="AG6" s="11" t="s">
-        <v>939</v>
       </c>
       <c r="AH6" s="11" t="s">
         <v>923</v>
@@ -29319,7 +29316,7 @@
     </row>
     <row r="7" spans="1:49" s="1" customFormat="1">
       <c r="A7" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B7" s="1">
         <v>2</v>
@@ -29430,7 +29427,7 @@
         <v>800</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="AM7" s="11" t="s">
         <v>315</v>
@@ -29466,7 +29463,7 @@
     </row>
     <row r="8" spans="1:49" s="1" customFormat="1">
       <c r="A8" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B8" s="1">
         <v>2</v>
@@ -29529,7 +29526,7 @@
         <v>578</v>
       </c>
       <c r="V8" s="5" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="W8" s="1" t="s">
         <v>295</v>
@@ -29553,22 +29550,22 @@
         <v>313</v>
       </c>
       <c r="AD8" s="11" t="s">
+        <v>936</v>
+      </c>
+      <c r="AE8" s="11" t="s">
         <v>937</v>
       </c>
-      <c r="AE8" s="11" t="s">
+      <c r="AF8" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="AG8" s="11" t="s">
         <v>938</v>
-      </c>
-      <c r="AF8" s="11" t="s">
-        <v>960</v>
-      </c>
-      <c r="AG8" s="11" t="s">
-        <v>939</v>
       </c>
       <c r="AH8" s="11" t="s">
         <v>923</v>
       </c>
       <c r="AI8" s="11" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="AJ8" s="11" t="s">
         <v>362</v>
@@ -29608,12 +29605,12 @@
       </c>
       <c r="AV8"/>
       <c r="AW8" s="1" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="9" spans="1:49" s="1" customFormat="1">
       <c r="A9" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B9" s="1">
         <v>2</v>
@@ -29698,22 +29695,22 @@
         <v>313</v>
       </c>
       <c r="AD9" s="11" t="s">
+        <v>936</v>
+      </c>
+      <c r="AE9" s="11" t="s">
         <v>937</v>
       </c>
-      <c r="AE9" s="11" t="s">
+      <c r="AF9" s="11" t="s">
+        <v>959</v>
+      </c>
+      <c r="AG9" s="11" t="s">
         <v>938</v>
-      </c>
-      <c r="AF9" s="11" t="s">
-        <v>960</v>
-      </c>
-      <c r="AG9" s="11" t="s">
-        <v>939</v>
       </c>
       <c r="AH9" s="11" t="s">
         <v>923</v>
       </c>
       <c r="AI9" s="11" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="AJ9" s="11" t="s">
         <v>362</v>
@@ -29753,12 +29750,12 @@
       </c>
       <c r="AV9"/>
       <c r="AW9" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="10" spans="1:49" s="1" customFormat="1">
       <c r="A10" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B10" s="1">
         <v>2</v>
@@ -29858,7 +29855,7 @@
         <v>898</v>
       </c>
       <c r="AI10" s="11" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="AJ10" s="11" t="s">
         <v>362</v>
@@ -29867,7 +29864,7 @@
         <v>800</v>
       </c>
       <c r="AL10" s="11" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="AM10" s="11" t="s">
         <v>315</v>
@@ -29898,12 +29895,12 @@
       </c>
       <c r="AV10"/>
       <c r="AW10" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="11" spans="1:49" s="1" customFormat="1">
       <c r="A11" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B11" s="1">
         <v>2</v>
@@ -30003,7 +30000,7 @@
         <v>898</v>
       </c>
       <c r="AI11" s="11" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="AJ11" s="11" t="s">
         <v>362</v>
@@ -30043,12 +30040,12 @@
       </c>
       <c r="AV11"/>
       <c r="AW11" s="1" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="12" spans="1:49" s="1" customFormat="1">
       <c r="A12" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B12" s="1">
         <v>3</v>
@@ -30099,7 +30096,7 @@
         <v>424</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="S12" s="1" t="s">
         <v>315</v>
@@ -30111,7 +30108,7 @@
         <v>315</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="W12" s="1" t="s">
         <v>295</v>
@@ -30126,16 +30123,16 @@
         <v>581</v>
       </c>
       <c r="AA12" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="AB12" s="1" t="s">
         <v>975</v>
-      </c>
-      <c r="AB12" s="1" t="s">
-        <v>976</v>
       </c>
       <c r="AC12" s="1" t="s">
         <v>295</v>
       </c>
       <c r="AD12" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="AE12" s="1" t="s">
         <v>662</v>
@@ -30144,10 +30141,10 @@
         <v>601</v>
       </c>
       <c r="AG12" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="AH12" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="AI12" s="1" t="s">
         <v>829</v>
@@ -30159,7 +30156,7 @@
         <v>746</v>
       </c>
       <c r="AL12" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="AM12" s="1" t="s">
         <v>315</v>
@@ -30190,12 +30187,12 @@
       </c>
       <c r="AV12"/>
       <c r="AW12" s="1" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="13" spans="1:49" s="1" customFormat="1">
       <c r="A13" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B13" s="1">
         <v>3</v>
@@ -30246,7 +30243,7 @@
         <v>424</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>315</v>
@@ -30258,7 +30255,7 @@
         <v>315</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="W13" s="1" t="s">
         <v>295</v>
@@ -30273,16 +30270,16 @@
         <v>581</v>
       </c>
       <c r="AA13" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="AB13" s="1" t="s">
         <v>975</v>
-      </c>
-      <c r="AB13" s="1" t="s">
-        <v>976</v>
       </c>
       <c r="AC13" s="1" t="s">
         <v>295</v>
       </c>
       <c r="AD13" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="AE13" s="1" t="s">
         <v>662</v>
@@ -30291,10 +30288,10 @@
         <v>601</v>
       </c>
       <c r="AG13" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="AH13" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="AI13" s="1" t="s">
         <v>732</v>
@@ -30306,7 +30303,7 @@
         <v>746</v>
       </c>
       <c r="AL13" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="AM13" s="1" t="s">
         <v>315</v>
@@ -30337,7 +30334,7 @@
       </c>
       <c r="AV13"/>
       <c r="AW13" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
   </sheetData>
@@ -30475,7 +30472,7 @@
         <v>586</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AQ1" s="1" t="s">
         <v>320</v>
@@ -30531,7 +30528,7 @@
         <v>272</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>291</v>
@@ -30563,10 +30560,10 @@
         <v>1998</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>1144</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>1145</v>
       </c>
       <c r="I3" s="1">
         <v>-36.306666999999997</v>
@@ -30578,7 +30575,7 @@
         <v>371</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="M3" s="1" t="s">
         <v>645</v>
@@ -30613,10 +30610,10 @@
         <v>1985</v>
       </c>
       <c r="G4" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>1147</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>1148</v>
       </c>
       <c r="I4" s="1">
         <v>17.758092999999999</v>
@@ -30628,7 +30625,7 @@
         <v>366</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>574</v>
@@ -30663,10 +30660,10 @@
         <v>2018</v>
       </c>
       <c r="G5" s="1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>1151</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>1152</v>
       </c>
       <c r="I5" s="1">
         <v>33.587860999999997</v>
@@ -30678,7 +30675,7 @@
         <v>366</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>574</v>
@@ -30713,10 +30710,10 @@
         <v>2018</v>
       </c>
       <c r="G6" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>1153</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>1154</v>
       </c>
       <c r="I6" s="1">
         <v>-5.8333329999999997</v>
@@ -30725,7 +30722,7 @@
         <v>72</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>380</v>
@@ -30763,10 +30760,10 @@
         <v>2017</v>
       </c>
       <c r="G7" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>1156</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>1157</v>
       </c>
       <c r="I7" s="1">
         <v>29.469228999999999</v>
@@ -30813,10 +30810,10 @@
         <v>2014</v>
       </c>
       <c r="G8" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>1158</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>1159</v>
       </c>
       <c r="I8" s="1">
         <v>24.095333</v>
@@ -30828,7 +30825,7 @@
         <v>363</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>574</v>
@@ -30863,10 +30860,10 @@
         <v>2014</v>
       </c>
       <c r="G9" s="1" t="s">
+        <v>1160</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>1161</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>1162</v>
       </c>
       <c r="I9" s="1">
         <v>42.224753999999997</v>
@@ -30875,7 +30872,7 @@
         <v>-8.8175150000000002</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="P9" s="1" t="s">
         <v>338</v>
@@ -30901,10 +30898,10 @@
         <v>2011</v>
       </c>
       <c r="G10" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>1163</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>1164</v>
       </c>
       <c r="I10" s="1">
         <v>-45.691389000000001</v>
@@ -30939,10 +30936,10 @@
         <v>2011</v>
       </c>
       <c r="G11" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>1166</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>1167</v>
       </c>
       <c r="I11" s="1">
         <v>-53.244253</v>
@@ -30951,7 +30948,7 @@
         <v>-37.673316</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="P11" s="1" t="s">
         <v>276</v>
@@ -30977,10 +30974,10 @@
         <v>2007</v>
       </c>
       <c r="G12" s="1" t="s">
+        <v>1168</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>1169</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>1170</v>
       </c>
       <c r="I12" s="1">
         <v>38.315517999999997</v>
@@ -31015,10 +31012,10 @@
         <v>2006</v>
       </c>
       <c r="G13" s="1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>1171</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>1172</v>
       </c>
       <c r="I13" s="1">
         <v>-45.783529999999999</v>
@@ -31053,10 +31050,10 @@
         <v>2004</v>
       </c>
       <c r="G14" s="1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>1173</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>1174</v>
       </c>
       <c r="I14" s="1">
         <v>44.255260999999997</v>
@@ -31091,10 +31088,10 @@
         <v>2000</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>1176</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>1177</v>
       </c>
       <c r="I15" s="1">
         <v>34.259346999999998</v>
@@ -31103,7 +31100,7 @@
         <v>133.40153699999999</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="P15" s="1" t="s">
         <v>424</v>
@@ -31129,10 +31126,10 @@
         <v>2000</v>
       </c>
       <c r="G16" s="1" t="s">
+        <v>1177</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>1178</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>1179</v>
       </c>
       <c r="I16" s="1">
         <v>-34.112057</v>
@@ -31167,10 +31164,10 @@
         <v>1999</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>1179</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>1180</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>1181</v>
       </c>
       <c r="I17" s="1">
         <v>30.5</v>
@@ -31205,10 +31202,10 @@
         <v>1998</v>
       </c>
       <c r="G18" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>1182</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>1183</v>
       </c>
       <c r="I18" s="1">
         <v>29.096662999999999</v>
@@ -31243,10 +31240,10 @@
         <v>1994</v>
       </c>
       <c r="G19" s="1" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>1184</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>1185</v>
       </c>
       <c r="I19" s="1">
         <v>48.853999999999999</v>
@@ -31281,10 +31278,10 @@
         <v>2010</v>
       </c>
       <c r="G20" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>1186</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>1187</v>
       </c>
       <c r="I20" s="1">
         <v>54.35</v>
@@ -31293,7 +31290,7 @@
         <v>10.15</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="P20" s="1" t="s">
         <v>338</v>
@@ -31319,10 +31316,10 @@
         <v>1998</v>
       </c>
       <c r="G21" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>1189</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>1190</v>
       </c>
       <c r="I21" s="1">
         <v>-63.134332999999998</v>
@@ -31331,7 +31328,7 @@
         <v>-51.091971999999998</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="P21" s="1" t="s">
         <v>276</v>
@@ -31357,10 +31354,10 @@
         <v>1993</v>
       </c>
       <c r="G22" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>1191</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>1192</v>
       </c>
       <c r="I22" s="1">
         <v>58.866667</v>
@@ -31369,7 +31366,7 @@
         <v>11.15</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="P22" s="1" t="s">
         <v>338</v>
@@ -31395,10 +31392,10 @@
         <v>1988</v>
       </c>
       <c r="G23" s="1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>1194</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>1195</v>
       </c>
       <c r="I23" s="1">
         <v>33.466667000000001</v>
@@ -31433,10 +31430,10 @@
         <v>1982</v>
       </c>
       <c r="G24" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>1196</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>1197</v>
       </c>
       <c r="I24" s="1">
         <v>41.588000000000001</v>
@@ -31585,7 +31582,7 @@
     </row>
     <row r="28" spans="1:49" s="1" customFormat="1">
       <c r="A28" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B28" s="1">
         <v>27</v>
@@ -31639,10 +31636,10 @@
         <v>581</v>
       </c>
       <c r="AA28" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="AB28" s="1" t="s">
         <v>1057</v>
-      </c>
-      <c r="AB28" s="1" t="s">
-        <v>1058</v>
       </c>
       <c r="AC28" s="1" t="s">
         <v>295</v>
@@ -31650,7 +31647,7 @@
     </row>
     <row r="29" spans="1:49" s="1" customFormat="1">
       <c r="A29" s="1" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B29" s="1">
         <v>28</v>
@@ -31668,10 +31665,10 @@
         <v>2013</v>
       </c>
       <c r="G29" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>1134</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>1135</v>
       </c>
       <c r="I29" s="1">
         <v>25.0349</v>
@@ -31719,7 +31716,7 @@
     </row>
     <row r="30" spans="1:49" s="1" customFormat="1">
       <c r="A30" s="1" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="B30" s="1">
         <v>29</v>
@@ -31905,7 +31902,7 @@
         <v>586</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="AQ1" s="1" t="s">
         <v>320</v>
@@ -32095,7 +32092,7 @@
     </row>
     <row r="12" spans="1:47" s="1" customFormat="1">
       <c r="A12" s="1" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>195</v>
@@ -32441,7 +32438,7 @@
     </row>
     <row r="26" spans="1:49" s="1" customFormat="1">
       <c r="A26" s="1" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B26" s="11">
         <v>1</v>
@@ -32489,7 +32486,7 @@
         <v>338</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>315</v>
@@ -32507,7 +32504,7 @@
         <v>313</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="X26" s="1" t="s">
         <v>885</v>
@@ -32516,7 +32513,7 @@
         <v>886</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="AA26" s="1" t="s">
         <v>923</v>
@@ -32524,7 +32521,7 @@
     </row>
     <row r="27" spans="1:49" s="1" customFormat="1">
       <c r="A27" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B27" s="11">
         <v>1</v>
@@ -32572,7 +32569,7 @@
         <v>425</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="R27" s="1" t="s">
         <v>315</v>
@@ -32590,7 +32587,7 @@
         <v>295</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="X27" s="1" t="s">
         <v>885</v>
@@ -32599,14 +32596,14 @@
         <v>886</v>
       </c>
       <c r="Z27" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="AA27" s="1" t="s">
         <v>1024</v>
-      </c>
-      <c r="AA27" s="1" t="s">
-        <v>1025</v>
       </c>
       <c r="AV27"/>
       <c r="AW27" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="28" spans="1:49" s="1" customFormat="1">
@@ -32718,7 +32715,7 @@
       </c>
       <c r="E1" s="3"/>
       <c r="F1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -32726,7 +32723,7 @@
         <v>420</v>
       </c>
       <c r="F2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -32734,7 +32731,7 @@
         <v>421</v>
       </c>
       <c r="F3" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -32829,7 +32826,7 @@
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="4" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
   </sheetData>
@@ -32847,10 +32844,10 @@
   <sheetData>
     <row r="1" spans="2:10">
       <c r="B1" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="E1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="G1" t="s">
         <v>865</v>
@@ -32861,7 +32858,7 @@
         <v>682</v>
       </c>
       <c r="C2" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="D2" t="s">
         <v>683</v>
@@ -32870,7 +32867,7 @@
         <v>682</v>
       </c>
       <c r="H2" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="I2" t="s">
         <v>683</v>
@@ -33223,7 +33220,7 @@
         <v>586</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>320</v>
@@ -33866,7 +33863,7 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -34013,7 +34010,7 @@
     </row>
     <row r="35" spans="1:16">
       <c r="A35" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -34082,7 +34079,7 @@
     </row>
     <row r="41" spans="1:16">
       <c r="A41" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C41" t="s">
         <v>682</v>
@@ -34146,10 +34143,10 @@
     </row>
     <row r="45" spans="1:16">
       <c r="A45" s="10" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="J45" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -34157,7 +34154,7 @@
         <v>350</v>
       </c>
       <c r="B46" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="J46" t="s">
         <v>350</v>
@@ -34287,7 +34284,7 @@
     </row>
     <row r="52" spans="1:16">
       <c r="A52" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C52" t="s">
         <v>682</v>
@@ -34305,7 +34302,7 @@
         <v>736</v>
       </c>
       <c r="J52" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="L52" t="s">
         <v>682</v>
@@ -34409,10 +34406,10 @@
     </row>
     <row r="56" spans="1:16">
       <c r="A56" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="J56" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -34539,7 +34536,7 @@
     </row>
     <row r="62" spans="1:16">
       <c r="A62" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C62" t="s">
         <v>682</v>
@@ -34557,7 +34554,7 @@
         <v>736</v>
       </c>
       <c r="J62" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="L62" t="s">
         <v>682</v>
@@ -34661,10 +34658,10 @@
     </row>
     <row r="66" spans="1:16">
       <c r="A66" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="J66" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -34791,7 +34788,7 @@
     </row>
     <row r="72" spans="1:16">
       <c r="A72" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C72" t="s">
         <v>682</v>
@@ -34809,7 +34806,7 @@
         <v>736</v>
       </c>
       <c r="J72" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="L72" t="s">
         <v>682</v>
@@ -34913,10 +34910,10 @@
     </row>
     <row r="76" spans="1:16">
       <c r="A76" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="J76" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -35043,7 +35040,7 @@
     </row>
     <row r="82" spans="1:16">
       <c r="A82" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C82" t="s">
         <v>682</v>
@@ -35061,7 +35058,7 @@
         <v>736</v>
       </c>
       <c r="J82" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="L82" t="s">
         <v>682</v>
@@ -35165,7 +35162,7 @@
     </row>
     <row r="86" spans="1:16">
       <c r="A86" s="10" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -35239,7 +35236,7 @@
     </row>
     <row r="93" spans="1:16">
       <c r="A93" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C93" t="s">
         <v>682</v>
@@ -35372,7 +35369,7 @@
     </row>
     <row r="103" spans="1:7">
       <c r="A103" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C103" t="s">
         <v>682</v>
@@ -35532,7 +35529,7 @@
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="7" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B113" s="7"/>
       <c r="C113" s="7" t="s">
@@ -35599,7 +35596,7 @@
     </row>
     <row r="118" spans="1:7">
       <c r="A118" s="10" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="120" spans="1:7">
@@ -35689,7 +35686,7 @@
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="7" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B125" s="7"/>
       <c r="C125" s="7" t="s">
@@ -35756,12 +35753,12 @@
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="10" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="7" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="B132" s="7"/>
       <c r="C132" s="7" t="s">
@@ -35846,7 +35843,7 @@
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="7" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="B137" s="7"/>
       <c r="C137" s="7" t="s">
@@ -35913,12 +35910,12 @@
     </row>
     <row r="142" spans="1:7">
       <c r="A142" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="7" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B144" s="7"/>
       <c r="C144" s="7" t="s">
@@ -36003,7 +36000,7 @@
     </row>
     <row r="149" spans="1:7">
       <c r="A149" s="7" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B149" s="7"/>
       <c r="C149" s="7" t="s">
@@ -36090,7 +36087,7 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -36869,7 +36866,7 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -36972,35 +36969,35 @@
     </row>
     <row r="52" spans="1:10">
       <c r="A52" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="D53" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E53" t="s">
+        <v>1092</v>
+      </c>
+      <c r="F53" t="s">
+        <v>1095</v>
+      </c>
+      <c r="H53" t="s">
         <v>1094</v>
       </c>
-      <c r="E53" t="s">
-        <v>1093</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="I53" t="s">
+        <v>1092</v>
+      </c>
+      <c r="J53" t="s">
         <v>1096</v>
-      </c>
-      <c r="H53" t="s">
-        <v>1095</v>
-      </c>
-      <c r="I53" t="s">
-        <v>1093</v>
-      </c>
-      <c r="J53" t="s">
-        <v>1097</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C54" t="s">
         <v>1085</v>
-      </c>
-      <c r="C54" t="s">
-        <v>1086</v>
       </c>
       <c r="D54">
         <v>0.35</v>
@@ -37025,7 +37022,7 @@
     </row>
     <row r="55" spans="1:10">
       <c r="C55" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="D55">
         <v>0.49</v>
@@ -37050,7 +37047,7 @@
     </row>
     <row r="56" spans="1:10">
       <c r="C56" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="D56">
         <v>0.46</v>
@@ -37075,7 +37072,7 @@
     </row>
     <row r="57" spans="1:10">
       <c r="C57" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="D57">
         <v>0.96</v>
@@ -37103,7 +37100,7 @@
         <v>746</v>
       </c>
       <c r="C59" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="D59">
         <v>0.43</v>
@@ -37128,7 +37125,7 @@
     </row>
     <row r="60" spans="1:10">
       <c r="C60" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="D60">
         <v>1.63</v>
@@ -37153,11 +37150,11 @@
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="7" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B62" s="7"/>
       <c r="C62" s="7" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="D62">
         <v>0.35</v>
@@ -37184,7 +37181,7 @@
       <c r="A63" s="7"/>
       <c r="B63" s="7"/>
       <c r="C63" s="7" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="D63">
         <v>0.42</v>
@@ -37211,7 +37208,7 @@
       <c r="A64" s="7"/>
       <c r="B64" s="7"/>
       <c r="C64" s="7" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -37238,7 +37235,7 @@
       <c r="A65" s="7"/>
       <c r="B65" s="7"/>
       <c r="C65" s="7" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="D65">
         <v>0.28999999999999998</v>
@@ -37263,11 +37260,11 @@
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="7" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B67" s="7"/>
       <c r="C67" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="D67">
         <v>0.28999999999999998</v>
@@ -37294,7 +37291,7 @@
       <c r="A68" s="7"/>
       <c r="B68" s="7"/>
       <c r="C68" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="D68">
         <v>0.15</v>
@@ -37329,24 +37326,24 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" t="s">
+        <v>997</v>
+      </c>
+      <c r="B1" t="s">
         <v>998</v>
       </c>
-      <c r="B1" t="s">
-        <v>999</v>
-      </c>
       <c r="R1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="S1" t="s">
         <v>682</v>
       </c>
       <c r="T1" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="2" spans="1:20">
       <c r="B2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="C2">
         <v>0.42857142857142799</v>
@@ -37445,7 +37442,7 @@
     </row>
     <row r="5" spans="1:20">
       <c r="B5" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="C5">
         <v>0.22396313364055201</v>
@@ -37503,10 +37500,10 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B8" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="C8">
         <v>0.29308755760368599</v>
@@ -37653,7 +37650,7 @@
     </row>
     <row r="11" spans="1:20">
       <c r="B11" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="C11">
         <v>0.31244239631336301</v>
@@ -37750,7 +37747,7 @@
         <v>586</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>320</v>

--- a/Output/Data/meta_analysis_data.xlsx
+++ b/Output/Data/meta_analysis_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilylim/Documents/MSc/Ch2-Meta-analysis/Output/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{929B4D3E-53F9-BB40-B812-4CEFF04A2FD0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46E8F86A-FAEF-804C-AA6E-D6028D63EFBF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10700" yWindow="460" windowWidth="19600" windowHeight="15940" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
+    <workbookView xWindow="9200" yWindow="460" windowWidth="19600" windowHeight="15840" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
   </bookViews>
   <sheets>
     <sheet name="Include" sheetId="1" r:id="rId1"/>

--- a/Output/Data/meta_analysis_data.xlsx
+++ b/Output/Data/meta_analysis_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilylim/Documents/MSc/Ch2-Meta-analysis/Output/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6014E838-D7CC-8F49-8BD3-FB52D40FAA1C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F651994A-96A8-7E4D-A8F7-A42A790DD72B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9520" yWindow="460" windowWidth="27540" windowHeight="18740" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
+    <workbookView xWindow="6560" yWindow="460" windowWidth="27540" windowHeight="15860" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
   </bookViews>
   <sheets>
     <sheet name="Include" sheetId="1" r:id="rId1"/>
@@ -20357,11 +20357,11 @@
       <c r="I107" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="J107" s="1">
-        <v>29.770776999999999</v>
-      </c>
-      <c r="K107" s="1">
-        <v>-85.357286000000002</v>
+      <c r="J107">
+        <v>29.704194999999999</v>
+      </c>
+      <c r="K107">
+        <v>-85.469155999999998</v>
       </c>
       <c r="L107" s="1" t="s">
         <v>365</v>
@@ -20506,11 +20506,11 @@
       <c r="I108" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="J108" s="1">
-        <v>29.770776999999999</v>
-      </c>
-      <c r="K108" s="1">
-        <v>-85.357286000000002</v>
+      <c r="J108">
+        <v>29.704194999999999</v>
+      </c>
+      <c r="K108">
+        <v>-85.469155999999998</v>
       </c>
       <c r="L108" s="1" t="s">
         <v>365</v>
@@ -20655,11 +20655,11 @@
       <c r="I109" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="J109" s="1">
-        <v>29.770776999999999</v>
-      </c>
-      <c r="K109" s="1">
-        <v>-85.357286000000002</v>
+      <c r="J109">
+        <v>29.704194999999999</v>
+      </c>
+      <c r="K109">
+        <v>-85.469155999999998</v>
       </c>
       <c r="L109" s="1" t="s">
         <v>365</v>
@@ -20804,11 +20804,11 @@
       <c r="I110" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="J110" s="1">
-        <v>29.770776999999999</v>
-      </c>
-      <c r="K110" s="1">
-        <v>-85.357286000000002</v>
+      <c r="J110">
+        <v>29.704194999999999</v>
+      </c>
+      <c r="K110">
+        <v>-85.469155999999998</v>
       </c>
       <c r="L110" s="1" t="s">
         <v>365</v>
@@ -20953,11 +20953,11 @@
       <c r="I111" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="J111" s="1">
-        <v>29.770776999999999</v>
-      </c>
-      <c r="K111" s="1">
-        <v>-85.357286000000002</v>
+      <c r="J111">
+        <v>29.704194999999999</v>
+      </c>
+      <c r="K111">
+        <v>-85.469155999999998</v>
       </c>
       <c r="L111" s="1" t="s">
         <v>365</v>
@@ -21102,11 +21102,11 @@
       <c r="I112" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="J112" s="1">
-        <v>29.770776999999999</v>
-      </c>
-      <c r="K112" s="1">
-        <v>-85.357286000000002</v>
+      <c r="J112">
+        <v>29.704194999999999</v>
+      </c>
+      <c r="K112">
+        <v>-85.469155999999998</v>
       </c>
       <c r="L112" s="1" t="s">
         <v>365</v>
@@ -21251,11 +21251,11 @@
       <c r="I113" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="J113" s="1">
-        <v>29.770776999999999</v>
-      </c>
-      <c r="K113" s="1">
-        <v>-85.357286000000002</v>
+      <c r="J113">
+        <v>29.704194999999999</v>
+      </c>
+      <c r="K113">
+        <v>-85.469155999999998</v>
       </c>
       <c r="L113" s="1" t="s">
         <v>365</v>
@@ -21400,11 +21400,11 @@
       <c r="I114" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="J114" s="1">
-        <v>29.770776999999999</v>
-      </c>
-      <c r="K114" s="1">
-        <v>-85.357286000000002</v>
+      <c r="J114">
+        <v>29.704194999999999</v>
+      </c>
+      <c r="K114">
+        <v>-85.469155999999998</v>
       </c>
       <c r="L114" s="1" t="s">
         <v>365</v>

--- a/Output/Data/meta_analysis_data.xlsx
+++ b/Output/Data/meta_analysis_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilylim/Documents/MSc/Ch2-Meta-analysis/Output/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F651994A-96A8-7E4D-A8F7-A42A790DD72B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE70B841-728B-814F-AF37-407DC381DCCA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6560" yWindow="460" windowWidth="27540" windowHeight="15860" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
+    <workbookView xWindow="4480" yWindow="460" windowWidth="27540" windowHeight="15860" activeTab="4" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
   </bookViews>
   <sheets>
     <sheet name="Include" sheetId="1" r:id="rId1"/>
@@ -37951,62 +37951,62 @@
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="4" t="s">
-        <v>1211</v>
+        <v>905</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="4" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="4" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="4" t="s">
-        <v>300</v>
+        <v>609</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="4" t="s">
-        <v>301</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="4" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="4" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="4" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="4" t="s">
-        <v>609</v>
+        <v>301</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" s="4" t="s">
-        <v>608</v>
+        <v>302</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" s="4" t="s">
-        <v>305</v>
+        <v>608</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" s="4" t="s">
-        <v>905</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>

--- a/Output/Data/meta_analysis_data.xlsx
+++ b/Output/Data/meta_analysis_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilylim/Documents/MSc/Ch2-Meta-analysis/Output/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9389781A-99F2-8648-AA41-EC64839987E3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965E1AE5-D7BA-F049-8728-EE034CCC1698}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="460" windowWidth="27540" windowHeight="15860" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
   </bookViews>
@@ -30091,7 +30091,7 @@
         <v>880</v>
       </c>
       <c r="AF172" s="11" t="s">
-        <v>314</v>
+        <v>656</v>
       </c>
       <c r="AG172" s="11" t="s">
         <v>596</v>

--- a/Output/Data/meta_analysis_data.xlsx
+++ b/Output/Data/meta_analysis_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilylim/Documents/MSc/Ch2-Meta-analysis/Output/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965E1AE5-D7BA-F049-8728-EE034CCC1698}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A75613-1494-D644-BFB1-AD7F2C0E0FCA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="880" yWindow="460" windowWidth="27540" windowHeight="15860" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
+    <workbookView xWindow="8780" yWindow="460" windowWidth="23540" windowHeight="15840" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
   </bookViews>
   <sheets>
     <sheet name="Include" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8217" uniqueCount="1265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8321" uniqueCount="1274">
   <si>
     <t>paper_num</t>
   </si>
@@ -4111,6 +4111,33 @@
   </si>
   <si>
     <t>MI</t>
+  </si>
+  <si>
+    <t>reason</t>
+  </si>
+  <si>
+    <t>design</t>
+  </si>
+  <si>
+    <t>marine</t>
+  </si>
+  <si>
+    <t>pp</t>
+  </si>
+  <si>
+    <t>zdup</t>
+  </si>
+  <si>
+    <t>zcouldn't find</t>
+  </si>
+  <si>
+    <t>aareason</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t>disturbance was the moderator of the response, this paper is included in the disturbance tab</t>
   </si>
 </sst>
 </file>
@@ -4199,7 +4226,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4209,6 +4236,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4226,7 +4271,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4250,6 +4295,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -8155,7 +8203,7 @@
         <v>10</v>
       </c>
       <c r="C25" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>65</v>
@@ -8304,7 +8352,7 @@
         <v>10</v>
       </c>
       <c r="C26" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>65</v>
@@ -8453,7 +8501,7 @@
         <v>10</v>
       </c>
       <c r="C27" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>65</v>
@@ -8602,7 +8650,7 @@
         <v>10</v>
       </c>
       <c r="C28" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>65</v>
@@ -8751,7 +8799,7 @@
         <v>10</v>
       </c>
       <c r="C29" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>65</v>
@@ -8900,7 +8948,7 @@
         <v>10</v>
       </c>
       <c r="C30" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>65</v>
@@ -9049,7 +9097,7 @@
         <v>10</v>
       </c>
       <c r="C31" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>65</v>
@@ -14994,7 +15042,7 @@
         <v>20</v>
       </c>
       <c r="C71" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>120</v>
@@ -35096,2806 +35144,3285 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{609A8BB8-D56F-804E-8A1C-E33492E2E26C}">
-  <dimension ref="A1:AW33"/>
+  <dimension ref="A1:AX34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="2" max="2" width="50.33203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:47" s="1" customFormat="1">
+    <row r="1" spans="1:49" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>960</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:47" s="1" customFormat="1">
+    <row r="2" spans="1:49" s="1" customFormat="1">
       <c r="A2" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="1">
+        <v>2019</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="J2" s="1">
+        <v>43.447499999999998</v>
+      </c>
+      <c r="K2" s="1">
+        <v>3.6516670000000002</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="V2" s="1">
+        <v>2013</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="AB2" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="AC2" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="AE2" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="AF2" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="AG2" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="AI2" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>401.01522842639503</v>
+      </c>
+      <c r="AR2" s="5">
+        <v>27.918781725888199</v>
+      </c>
+      <c r="AV2" s="1" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="3" spans="1:49" s="1" customFormat="1">
+      <c r="A3" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C3" s="1">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2019</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="J3" s="1">
+        <v>43.447499999999998</v>
+      </c>
+      <c r="K3" s="1">
+        <v>3.6516670000000002</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="V3" s="1">
+        <v>2013</v>
+      </c>
+      <c r="W3" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="AD3" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="AF3" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="AN3" s="1">
+        <v>22.842639593908601</v>
+      </c>
+      <c r="AR3" s="5">
+        <v>27.918781725888199</v>
+      </c>
+      <c r="AV3" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="4" spans="1:49" s="1" customFormat="1">
+      <c r="A4" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1996</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="K4" s="1">
+        <v>29.490614000000001</v>
+      </c>
+      <c r="L4" s="1">
+        <v>34.945005000000002</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="P4" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="AR4"/>
+    </row>
+    <row r="5" spans="1:49" s="1" customFormat="1">
+      <c r="A5" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="C5" s="1">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G5" s="1">
+        <v>2014</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="J5" s="1">
+        <v>42.224753999999997</v>
+      </c>
+      <c r="K5" s="1">
+        <v>-8.8175150000000002</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="6" spans="1:49" s="1" customFormat="1">
+      <c r="A6" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="C6" s="1">
+        <v>4</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="1">
+        <v>2010</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="J6" s="1">
+        <v>54.35</v>
+      </c>
+      <c r="K6" s="1">
+        <v>10.15</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="7" spans="1:49" s="1" customFormat="1">
+      <c r="A7" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C7" s="1">
+        <v>5</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1993</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>1160</v>
+      </c>
+      <c r="J7" s="1">
+        <v>58.866667</v>
+      </c>
+      <c r="K7" s="1">
+        <v>11.15</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="8" spans="1:49" s="1" customFormat="1">
+      <c r="A8" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C8" s="1">
+        <v>6</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1982</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="J8" s="1">
+        <v>41.588000000000001</v>
+      </c>
+      <c r="K8" s="1">
+        <v>-70.646495000000002</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="9" spans="1:49" s="1" customFormat="1">
+      <c r="A9" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C9" s="1">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1993</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="J9" s="1">
+        <v>-33.75</v>
+      </c>
+      <c r="K9" s="1">
+        <v>26.55</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="AA9" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="AB9" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="AC9" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="AD9" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="10" spans="1:49" s="1" customFormat="1">
+      <c r="A10" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C10" s="1">
+        <v>8</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="1">
+        <v>2018</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="J10" s="1">
+        <v>47.048614000000001</v>
+      </c>
+      <c r="K10" s="1">
+        <v>-2.1556639999999998</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="11" spans="1:49" s="1" customFormat="1">
+      <c r="A11" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C11" s="1">
+        <v>9</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="1">
+        <v>2019</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="J11" s="1">
+        <v>-5.8333329999999997</v>
+      </c>
+      <c r="K11" s="1">
+        <v>72</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>605</v>
+      </c>
+      <c r="V11" s="5" t="s">
+        <v>641</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="Z11" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="AA11" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="AB11" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="AC11" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="AD11" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="AE11" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="AF11" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="AG11" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="AH11" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="AI11" s="1" t="s">
+        <v>610</v>
+      </c>
+      <c r="AJ11" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="AK11" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="AL11" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="AM11" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="AN11" s="1">
+        <v>-10.103626943005203</v>
+      </c>
+      <c r="AO11" s="1">
+        <v>5.8202005886577881</v>
+      </c>
+      <c r="AP11" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="AQ11" s="1">
+        <v>5</v>
+      </c>
+      <c r="AR11" s="1">
+        <v>-7.3056994818653003</v>
+      </c>
+      <c r="AS11" s="1">
+        <v>4.663212435233139</v>
+      </c>
+      <c r="AT11" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="AU11" s="1">
+        <v>5</v>
+      </c>
+      <c r="AV11"/>
+      <c r="AW11" s="1" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="12" spans="1:49" s="1" customFormat="1">
+      <c r="A12" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="C12" s="1">
+        <v>10</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G12" s="1">
         <v>2020</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="I2" s="2">
+      <c r="J12" s="2">
         <v>-33.5</v>
       </c>
-      <c r="J2" s="2">
+      <c r="K12" s="2">
         <v>71.5</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M12" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N12" s="1" t="s">
         <v>1024</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O12" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P12" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q12" s="1" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="3" spans="1:47" s="1" customFormat="1">
-      <c r="A3" s="1" t="s">
+    <row r="13" spans="1:49" s="1" customFormat="1">
+      <c r="A13" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="B3" s="1">
-        <v>2</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="C13" s="1">
+        <v>11</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G13" s="1">
         <v>1998</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>1112</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>1113</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J13" s="1">
         <v>-36.306666999999997</v>
       </c>
-      <c r="J3" s="1">
+      <c r="K13" s="1">
         <v>174.815</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M13" s="1" t="s">
         <v>1114</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N13" s="1" t="s">
         <v>640</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O13" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P13" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Q13" s="1" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="4" spans="1:47" s="1" customFormat="1">
-      <c r="A4" s="1" t="s">
+    <row r="14" spans="1:49" s="1" customFormat="1">
+      <c r="A14" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B4" s="1">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="C14" s="1">
+        <v>12</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E14" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F4" s="1">
+      <c r="G14" s="1">
         <v>1985</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>1115</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>1116</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J14" s="1">
         <v>17.758092999999999</v>
       </c>
-      <c r="J4" s="1">
+      <c r="K14" s="1">
         <v>-64.605564000000001</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L14" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="M14" s="1" t="s">
         <v>1117</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="N14" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="O14" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="P14" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="Q14" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="5" spans="1:47" s="1" customFormat="1">
-      <c r="A5" s="1" t="s">
+    <row r="15" spans="1:49" s="1" customFormat="1">
+      <c r="A15" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B5" s="1">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="C15" s="1">
+        <v>13</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E15" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G15" s="1">
         <v>2018</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>1119</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>1120</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J15" s="1">
         <v>33.587860999999997</v>
       </c>
-      <c r="J5" s="1">
+      <c r="K15" s="1">
         <v>-117.86708299999999</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="M15" s="1" t="s">
         <v>1118</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="N15" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="O15" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="P15" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="Q15" s="1" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="6" spans="1:47" s="1" customFormat="1">
-      <c r="A6" s="1" t="s">
+    <row r="16" spans="1:49" s="1" customFormat="1">
+      <c r="A16" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B6" s="1">
-        <v>5</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="C16" s="1">
+        <v>14</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G16" s="1">
         <v>2018</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>1121</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>1122</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J16" s="1">
         <v>-5.8333329999999997</v>
       </c>
-      <c r="J6" s="1">
+      <c r="K16" s="1">
         <v>72</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>1123</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="M16" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="N16" s="1" t="s">
         <v>647</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="O16" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="P16" s="1" t="s">
         <v>603</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="Q16" s="1" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="7" spans="1:47" s="1" customFormat="1">
-      <c r="A7" s="1" t="s">
+    <row r="17" spans="1:50" s="1" customFormat="1">
+      <c r="A17" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="B7" s="1">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="C17" s="1">
+        <v>15</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E17" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F17" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G17" s="1">
         <v>2017</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>1125</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J17" s="1">
         <v>29.469228999999999</v>
       </c>
-      <c r="J7" s="1">
+      <c r="K17" s="1">
         <v>34.931817000000002</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L17" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="M17" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="N17" s="1" t="s">
         <v>639</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="O17" s="1" t="s">
         <v>602</v>
       </c>
-      <c r="O7" s="1" t="s">
+      <c r="P17" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="Q17" s="1" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="8" spans="1:47" s="1" customFormat="1">
-      <c r="A8" s="1" t="s">
+    <row r="18" spans="1:50" s="1" customFormat="1">
+      <c r="A18" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="B8" s="1">
-        <v>7</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="C18" s="1">
+        <v>16</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E18" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F18" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G18" s="1">
         <v>2014</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>1126</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>1127</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J18" s="1">
         <v>24.095333</v>
       </c>
-      <c r="J8" s="1">
+      <c r="K18" s="1">
         <v>-75.808361000000005</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="L18" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="M18" s="1" t="s">
         <v>1128</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="N18" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="O18" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="O8" s="1" t="s">
+      <c r="P18" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="P8" s="1" t="s">
+      <c r="Q18" s="1" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="9" spans="1:47" s="1" customFormat="1">
-      <c r="A9" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="B9" s="1">
-        <v>8</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" s="1" t="s">
+    <row r="19" spans="1:50" s="1" customFormat="1">
+      <c r="A19" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C19" s="1">
+        <v>17</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G19" s="1">
+        <v>2011</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="J19" s="1">
+        <v>-45.691389000000001</v>
+      </c>
+      <c r="K19" s="1">
+        <v>170.61666700000001</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="20" spans="1:50" s="1" customFormat="1">
+      <c r="A20" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="C20" s="1">
+        <v>18</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G20" s="1">
+        <v>2011</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="J20" s="1">
+        <v>-53.244253</v>
+      </c>
+      <c r="K20" s="1">
+        <v>-37.673316</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="21" spans="1:50" s="1" customFormat="1">
+      <c r="A21" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="C21" s="1">
+        <v>19</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G21" s="1">
+        <v>2007</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="J21" s="1">
+        <v>38.315517999999997</v>
+      </c>
+      <c r="K21" s="1">
+        <v>-123.074901</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="22" spans="1:50" s="1" customFormat="1">
+      <c r="A22" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="C22" s="1">
+        <v>20</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G22" s="1">
+        <v>2006</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="J22" s="1">
+        <v>-45.783529999999999</v>
+      </c>
+      <c r="K22" s="1">
+        <v>170.71993499999999</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="23" spans="1:50" s="1" customFormat="1">
+      <c r="A23" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>411</v>
+      </c>
+      <c r="C23" s="1">
+        <v>21</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G23" s="1">
+        <v>2004</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="J23" s="1">
+        <v>44.255260999999997</v>
+      </c>
+      <c r="K23" s="1">
+        <v>-124.1126</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="24" spans="1:50" s="1" customFormat="1">
+      <c r="A24" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C24" s="1">
+        <v>22</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="J24" s="1">
+        <v>34.259346999999998</v>
+      </c>
+      <c r="K24" s="1">
+        <v>133.40153699999999</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="25" spans="1:50" s="1" customFormat="1">
+      <c r="A25" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="C25" s="1">
+        <v>23</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G25" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="J25" s="1">
+        <v>-34.112057</v>
+      </c>
+      <c r="K25" s="1">
+        <v>18.475390999999998</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="26" spans="1:50" s="1" customFormat="1">
+      <c r="A26" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C26" s="1">
+        <v>24</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G26" s="1">
+        <v>1999</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J26" s="1">
+        <v>30.5</v>
+      </c>
+      <c r="K26" s="1">
+        <v>-88</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="AW26"/>
+      <c r="AX26" s="1" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="27" spans="1:50" s="1" customFormat="1">
+      <c r="A27" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="C27" s="1">
+        <v>25</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G27" s="1">
+        <v>1998</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="J27" s="1">
+        <v>29.096662999999999</v>
+      </c>
+      <c r="K27" s="1">
+        <v>34.77319</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="AW27"/>
+      <c r="AX27" s="1" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="28" spans="1:50" s="1" customFormat="1">
+      <c r="A28" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="C28" s="1">
+        <v>26</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G28" s="1">
+        <v>1994</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="J28" s="1">
+        <v>48.853999999999999</v>
+      </c>
+      <c r="K28" s="1">
+        <v>-125.11666700000001</v>
+      </c>
+      <c r="L28" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="AW28"/>
+      <c r="AX28" s="1" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="29" spans="1:50" s="1" customFormat="1">
+      <c r="A29" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="C29" s="1">
+        <v>27</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="G29" s="1">
+        <v>1998</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>1158</v>
+      </c>
+      <c r="J29" s="1">
+        <v>-63.134332999999998</v>
+      </c>
+      <c r="K29" s="1">
+        <v>-51.091971999999998</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="30" spans="1:50" s="1" customFormat="1">
+      <c r="A30" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="C30" s="1">
+        <v>28</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="G30" s="1">
+        <v>1988</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="J30" s="1">
+        <v>33.466667000000001</v>
+      </c>
+      <c r="K30" s="1">
+        <v>-118.483333</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="31" spans="1:50" s="1" customFormat="1">
+      <c r="A31" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="C31" s="1">
+        <v>29</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G31" s="1">
         <v>2014</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>1129</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>1130</v>
-      </c>
-      <c r="I9" s="1">
-        <v>42.224753999999997</v>
-      </c>
-      <c r="J9" s="1">
-        <v>-8.8175150000000002</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>1133</v>
-      </c>
-      <c r="P9" s="1" t="s">
+      <c r="H31" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="J31" s="1">
+        <v>48.297351999999997</v>
+      </c>
+      <c r="K31" s="1">
+        <v>-124.240292</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q31" s="1" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="10" spans="1:47" s="1" customFormat="1">
-      <c r="A10" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="B10" s="1">
-        <v>9</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F10" s="1">
-        <v>2011</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>1131</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>1132</v>
-      </c>
-      <c r="I10" s="1">
-        <v>-45.691389000000001</v>
-      </c>
-      <c r="J10" s="1">
-        <v>170.61666700000001</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="11" spans="1:47" s="1" customFormat="1">
-      <c r="A11" s="1" t="s">
-        <v>394</v>
-      </c>
-      <c r="B11" s="1">
-        <v>10</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="F11" s="1">
-        <v>2011</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>1134</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>1135</v>
-      </c>
-      <c r="I11" s="1">
-        <v>-53.244253</v>
-      </c>
-      <c r="J11" s="1">
-        <v>-37.673316</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>1136</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="12" spans="1:47" s="1" customFormat="1">
-      <c r="A12" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="B12" s="1">
-        <v>11</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="F12" s="1">
-        <v>2007</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>1137</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>1138</v>
-      </c>
-      <c r="I12" s="1">
-        <v>38.315517999999997</v>
-      </c>
-      <c r="J12" s="1">
-        <v>-123.074901</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="13" spans="1:47" s="1" customFormat="1">
-      <c r="A13" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="B13" s="1">
-        <v>12</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="F13" s="1">
-        <v>2006</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>1139</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>1140</v>
-      </c>
-      <c r="I13" s="1">
-        <v>-45.783529999999999</v>
-      </c>
-      <c r="J13" s="1">
-        <v>170.71993499999999</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="14" spans="1:47" s="1" customFormat="1">
-      <c r="A14" s="11" t="s">
-        <v>411</v>
-      </c>
-      <c r="B14" s="1">
-        <v>13</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="F14" s="1">
-        <v>2004</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>1141</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>1142</v>
-      </c>
-      <c r="I14" s="1">
-        <v>44.255260999999997</v>
-      </c>
-      <c r="J14" s="1">
-        <v>-124.1126</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="P14" s="1" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="15" spans="1:47" s="1" customFormat="1">
-      <c r="A15" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="B15" s="1">
-        <v>14</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>1144</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>1145</v>
-      </c>
-      <c r="I15" s="1">
-        <v>34.259346999999998</v>
-      </c>
-      <c r="J15" s="1">
-        <v>133.40153699999999</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>1143</v>
-      </c>
-      <c r="P15" s="1" t="s">
+    <row r="32" spans="1:50" s="1" customFormat="1">
+      <c r="A32" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="C32" s="1">
+        <v>30</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G32" s="1">
+        <v>2014</v>
+      </c>
+      <c r="H32" s="11" t="s">
+        <v>452</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>453</v>
+      </c>
+      <c r="J32" s="1">
+        <v>32.473244000000001</v>
+      </c>
+      <c r="K32" s="1">
+        <v>-64.871342999999996</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q32" s="1" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="16" spans="1:47" s="1" customFormat="1">
-      <c r="A16" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="B16" s="1">
-        <v>15</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F16" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>1146</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>1147</v>
-      </c>
-      <c r="I16" s="1">
-        <v>-34.112057</v>
-      </c>
-      <c r="J16" s="1">
-        <v>18.475390999999998</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="17" spans="1:49" s="1" customFormat="1">
-      <c r="A17" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="B17" s="1">
-        <v>16</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="F17" s="1">
-        <v>1999</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>1148</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>1149</v>
-      </c>
-      <c r="I17" s="1">
-        <v>30.5</v>
-      </c>
-      <c r="J17" s="1">
-        <v>-88</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="18" spans="1:49" s="1" customFormat="1">
-      <c r="A18" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="B18" s="1">
-        <v>17</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="F18" s="1">
-        <v>1998</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>1150</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>1151</v>
-      </c>
-      <c r="I18" s="1">
-        <v>29.096662999999999</v>
-      </c>
-      <c r="J18" s="1">
-        <v>34.77319</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="P18" s="1" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="19" spans="1:49" s="1" customFormat="1">
-      <c r="A19" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="B19" s="1">
-        <v>18</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1994</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>1152</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>1153</v>
-      </c>
-      <c r="I19" s="1">
-        <v>48.853999999999999</v>
-      </c>
-      <c r="J19" s="1">
-        <v>-125.11666700000001</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>365</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="20" spans="1:49" s="1" customFormat="1">
-      <c r="A20" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="B20" s="1">
-        <v>19</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F20" s="1">
-        <v>2010</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>1154</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>1155</v>
-      </c>
-      <c r="I20" s="1">
-        <v>54.35</v>
-      </c>
-      <c r="J20" s="1">
-        <v>10.15</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>1156</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="21" spans="1:49" s="1" customFormat="1">
-      <c r="A21" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="B21" s="1">
-        <v>20</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="F21" s="1">
-        <v>1998</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>1157</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="I21" s="1">
-        <v>-63.134332999999998</v>
-      </c>
-      <c r="J21" s="1">
-        <v>-51.091971999999998</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>1136</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="22" spans="1:49" s="1" customFormat="1">
-      <c r="A22" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="B22" s="1">
-        <v>21</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="F22" s="1">
-        <v>1993</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>1159</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>1160</v>
-      </c>
-      <c r="I22" s="1">
-        <v>58.866667</v>
-      </c>
-      <c r="J22" s="1">
-        <v>11.15</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>1161</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="23" spans="1:49" s="1" customFormat="1">
-      <c r="A23" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="B23" s="1">
-        <v>22</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="F23" s="1">
-        <v>1988</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>1162</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>1163</v>
-      </c>
-      <c r="I23" s="1">
-        <v>33.466667000000001</v>
-      </c>
-      <c r="J23" s="1">
-        <v>-118.483333</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="24" spans="1:49" s="1" customFormat="1">
-      <c r="A24" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="B24" s="1">
-        <v>23</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F24" s="1">
-        <v>1982</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>1164</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>1165</v>
-      </c>
-      <c r="I24" s="1">
-        <v>41.588000000000001</v>
-      </c>
-      <c r="J24" s="1">
-        <v>-70.646495000000002</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="P24" s="1" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="25" spans="1:49" s="1" customFormat="1">
-      <c r="A25" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="B25" s="1">
-        <v>24</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F25" s="1">
-        <v>2014</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="I25" s="1">
-        <v>48.297351999999997</v>
-      </c>
-      <c r="J25" s="1">
-        <v>-124.240292</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="P25" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="AV25"/>
-      <c r="AW25" s="1" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="26" spans="1:49" s="1" customFormat="1">
-      <c r="A26" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="B26" s="1">
-        <v>25</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F26" s="1">
-        <v>2014</v>
-      </c>
-      <c r="G26" s="11" t="s">
-        <v>452</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>453</v>
-      </c>
-      <c r="I26" s="1">
-        <v>32.473244000000001</v>
-      </c>
-      <c r="J26" s="1">
-        <v>-64.871342999999996</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="AV26"/>
-      <c r="AW26" s="1" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="27" spans="1:49" s="1" customFormat="1">
-      <c r="A27" s="1" t="s">
+    <row r="33" spans="1:50" s="1" customFormat="1">
+      <c r="A33" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>691</v>
       </c>
-      <c r="B27" s="1">
-        <v>26</v>
-      </c>
-      <c r="C27" s="1" t="s">
+      <c r="C33" s="1">
+        <v>31</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="F27" s="1">
+      <c r="G33" s="1">
         <v>2015</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="H33" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="I33" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="I27" s="1">
+      <c r="J33" s="1">
         <v>30.279878</v>
       </c>
-      <c r="J27" s="1">
+      <c r="K33" s="1">
         <v>-115.913456</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="L33" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="L27" s="1" t="s">
+      <c r="M33" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="P27" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="AV27"/>
-      <c r="AW27" s="1" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="28" spans="1:49" s="1" customFormat="1">
-      <c r="A28" s="1" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B28" s="1">
-        <v>27</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F28" s="1">
-        <v>1993</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="I28" s="1">
-        <v>-33.75</v>
-      </c>
-      <c r="J28" s="1">
-        <v>26.55</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>511</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>863</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>602</v>
-      </c>
-      <c r="O28" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="P28" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="W28" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="Z28" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="AA28" s="1" t="s">
-        <v>1025</v>
-      </c>
-      <c r="AB28" s="1" t="s">
-        <v>1026</v>
-      </c>
-      <c r="AC28" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="29" spans="1:49" s="1" customFormat="1">
-      <c r="A29" s="1" t="s">
-        <v>1104</v>
-      </c>
-      <c r="B29" s="1">
-        <v>28</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F29" s="1">
-        <v>2013</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>1102</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>1103</v>
-      </c>
-      <c r="I29" s="1">
-        <v>25.0349</v>
-      </c>
-      <c r="J29" s="1">
-        <v>-80.34845</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="M29" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="O29" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="P29" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="R29" s="1" t="s">
-        <v>604</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="U29" s="11" t="s">
-        <v>574</v>
-      </c>
-      <c r="V29" s="11">
-        <v>2010</v>
-      </c>
-      <c r="W29" s="11" t="s">
-        <v>343</v>
-      </c>
-      <c r="X29" s="11"/>
-    </row>
-    <row r="30" spans="1:49" s="1" customFormat="1">
-      <c r="A30" s="1" t="s">
-        <v>1166</v>
-      </c>
-      <c r="B30" s="1">
-        <v>29</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F30" s="1">
-        <v>2018</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="I30" s="1">
-        <v>47.048614000000001</v>
-      </c>
-      <c r="J30" s="1">
-        <v>-2.1556639999999998</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="O30" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="P30" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="Q30" s="1" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="31" spans="1:49" s="1" customFormat="1">
-      <c r="A31" s="1" t="s">
-        <v>1187</v>
-      </c>
-      <c r="B31" s="1">
-        <v>1</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F31" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="I31" s="1">
-        <v>43.447499999999998</v>
-      </c>
-      <c r="J31" s="1">
-        <v>3.6516670000000002</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="P31" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="Q31" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="S31" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="T31" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="U31" s="1">
-        <v>2013</v>
-      </c>
-      <c r="V31" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="W31" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="X31" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="Y31" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="Z31" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="AA31" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="AB31" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="AC31" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="AD31" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="AE31" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="AF31" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="AG31" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="AH31" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="AI31" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="AK31" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="AM31" s="1">
-        <v>401.01522842639503</v>
-      </c>
-      <c r="AQ31" s="5">
-        <v>27.918781725888199</v>
-      </c>
-      <c r="AU31" s="1" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="32" spans="1:49" s="1" customFormat="1">
-      <c r="A32" s="1" t="s">
-        <v>1187</v>
-      </c>
-      <c r="B32" s="1">
-        <v>2</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F32" s="1">
-        <v>2019</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="I32" s="1">
-        <v>43.447499999999998</v>
-      </c>
-      <c r="J32" s="1">
-        <v>3.6516670000000002</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="O32" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="P32" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="S32" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="T32" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="U32" s="1">
-        <v>2013</v>
-      </c>
-      <c r="V32" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="W32" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="X32" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="Y32" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="Z32" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="AA32" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="AB32" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="AC32" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="AD32" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="AE32" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="AF32" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="AG32" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="AH32" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="AI32" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="AK32" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="AM32" s="1">
-        <v>22.842639593908601</v>
-      </c>
-      <c r="AQ32" s="5">
-        <v>27.918781725888199</v>
-      </c>
-      <c r="AU32" s="1" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="33" spans="1:49" s="1" customFormat="1">
-      <c r="A33" s="1" t="s">
-        <v>1260</v>
-      </c>
-      <c r="B33" s="1">
-        <v>33</v>
-      </c>
-      <c r="C33" s="5">
-        <v>1</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="G33" s="1">
-        <v>1996</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="J33" s="1">
-        <v>29.490614000000001</v>
-      </c>
-      <c r="K33" s="1">
-        <v>34.945005000000002</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="P33" s="1" t="s">
-        <v>314</v>
       </c>
       <c r="Q33" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="R33" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="S33" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="T33" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="AQ33"/>
-      <c r="AW33" s="1" t="s">
+    </row>
+    <row r="34" spans="1:50" s="1" customFormat="1">
+      <c r="A34" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C34" s="1">
+        <v>32</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G34" s="1">
+        <v>2013</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="J34" s="1">
+        <v>25.0349</v>
+      </c>
+      <c r="K34" s="1">
+        <v>-80.34845</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="S34" s="1" t="s">
+        <v>604</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="U34" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="V34" s="11" t="s">
+        <v>574</v>
+      </c>
+      <c r="W34" s="11">
+        <v>2010</v>
+      </c>
+      <c r="X34" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="Y34" s="11"/>
+      <c r="AX34" s="1" t="s">
         <v>497</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AV34">
+    <sortCondition ref="A1"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DED2D794-525F-A546-BCFF-DDC9B2940F7E}">
-  <dimension ref="A1:AW33"/>
+  <dimension ref="A1:AX33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="2" max="2" width="67.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:47" s="1" customFormat="1">
+    <row r="1" spans="1:50" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>568</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>582</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>960</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:47" s="1" customFormat="1">
+    <row r="2" spans="1:50" s="1" customFormat="1">
       <c r="A2" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
         <v>2019</v>
       </c>
     </row>
-    <row r="3" spans="1:47" s="1" customFormat="1">
+    <row r="3" spans="1:50" s="1" customFormat="1">
       <c r="A3" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="4" spans="1:50" s="1" customFormat="1">
+      <c r="A4" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="C4" s="1">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="1">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="5" spans="1:50" s="1" customFormat="1">
+      <c r="A5" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C5" s="1">
+        <v>4</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:50" s="1" customFormat="1">
+      <c r="A6" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="7" spans="1:50" s="1" customFormat="1">
+      <c r="A7" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="8" spans="1:50" s="1" customFormat="1">
+      <c r="A8" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="C8" s="1">
+        <v>7</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="9" spans="1:50" s="1" customFormat="1">
+      <c r="A9" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C9" s="1">
+        <v>8</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:50" s="1" customFormat="1">
+      <c r="A10" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="C10" s="1">
+        <v>9</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="11" spans="1:50" s="1" customFormat="1">
+      <c r="A11" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="C11" s="1">
+        <v>10</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1988</v>
+      </c>
+    </row>
+    <row r="12" spans="1:50" s="1" customFormat="1">
+      <c r="A12" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C12" s="1">
+        <v>11</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2004</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="J12" s="1">
+        <v>59.751111000000002</v>
+      </c>
+      <c r="K12" s="1">
+        <v>23.219166999999999</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="V12" s="1">
+        <v>2000</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="Z12" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="AA12" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="AB12" s="1" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="13" spans="1:50" s="1" customFormat="1">
+      <c r="A13" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C13" s="1">
+        <v>12</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="14" spans="1:50" s="1" customFormat="1">
+      <c r="A14" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C14" s="1">
+        <v>13</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="15" spans="1:50" s="1" customFormat="1">
+      <c r="A15" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="C15" s="1">
+        <v>14</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2017</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="J15" s="1">
+        <v>-37.006335999999997</v>
+      </c>
+      <c r="K15" s="1">
+        <v>175.89027200000001</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="O15" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="V15" s="1">
+        <v>2008</v>
+      </c>
+      <c r="W15" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="X15" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="Y15" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="Z15" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="AA15" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="AB15" s="1" t="s">
+        <v>993</v>
+      </c>
+      <c r="AW15"/>
+      <c r="AX15" s="1" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="16" spans="1:50" s="1" customFormat="1">
+      <c r="A16" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C16" s="1">
+        <v>15</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1980</v>
+      </c>
+    </row>
+    <row r="17" spans="1:50" s="1" customFormat="1">
+      <c r="A17" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="C17" s="1">
+        <v>16</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="18" spans="1:50" s="1" customFormat="1">
+      <c r="A18" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="C18" s="1">
+        <v>17</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G18" s="11">
+        <v>2009</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>466</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>467</v>
+      </c>
+      <c r="J18" s="11">
+        <v>7.588381</v>
+      </c>
+      <c r="K18" s="11">
+        <v>134.73338100000001</v>
+      </c>
+      <c r="L18" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>469</v>
+      </c>
+      <c r="N18" s="11"/>
+      <c r="Q18" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="AW18"/>
+      <c r="AX18" s="1" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="19" spans="1:50" s="1" customFormat="1">
+      <c r="A19" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="C19" s="1">
+        <v>18</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19" s="11">
+        <v>2015</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>517</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>518</v>
+      </c>
+      <c r="J19" s="11">
+        <v>47.016666999999998</v>
+      </c>
+      <c r="K19" s="11">
+        <v>-2.0333329999999998</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>326</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>372</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="AW19"/>
+    </row>
+    <row r="20" spans="1:50" s="1" customFormat="1">
+      <c r="A20" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C20" s="1">
+        <v>19</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G20" s="1">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="21" spans="1:50" s="1" customFormat="1">
+      <c r="A21" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C21" s="1">
+        <v>20</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G21" s="1">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="22" spans="1:50" s="1" customFormat="1">
+      <c r="A22" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C22" s="1">
+        <v>21</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="23" spans="1:50" s="1" customFormat="1">
+      <c r="A23" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C23" s="1">
+        <v>22</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G23" s="1">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="24" spans="1:50" s="1" customFormat="1">
+      <c r="A24" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C24" s="1">
+        <v>23</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1985</v>
+      </c>
+      <c r="AR24" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="25" spans="1:50" s="1" customFormat="1">
+      <c r="A25" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C25" s="1">
+        <v>24</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="26" spans="1:50" s="1" customFormat="1" ht="18">
+      <c r="A26" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>515</v>
+      </c>
+      <c r="C26" s="1">
+        <v>28</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="G26" s="1">
+        <v>2016</v>
+      </c>
+      <c r="AW26"/>
+      <c r="AX26" s="8" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="27" spans="1:50" s="1" customFormat="1">
+      <c r="A27" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>520</v>
+      </c>
+      <c r="C27" s="1">
+        <v>29</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="G27" s="1">
+        <v>2013</v>
+      </c>
+      <c r="AW27"/>
+      <c r="AX27" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="28" spans="1:50" s="1" customFormat="1">
+      <c r="A28" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>549</v>
+      </c>
+      <c r="C28" s="1">
+        <v>30</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="G28" s="1">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="29" spans="1:50" s="5" customFormat="1">
+      <c r="A29" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>535</v>
+      </c>
+      <c r="C29" s="1">
+        <v>16</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G29" s="1">
+        <v>2001</v>
+      </c>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1"/>
+      <c r="W29" s="1"/>
+      <c r="X29" s="1"/>
+      <c r="Y29" s="1"/>
+      <c r="Z29" s="1"/>
+      <c r="AA29" s="1"/>
+      <c r="AB29" s="1"/>
+      <c r="AC29" s="1"/>
+      <c r="AD29" s="1"/>
+      <c r="AE29" s="1"/>
+      <c r="AF29" s="1"/>
+      <c r="AG29" s="1"/>
+      <c r="AH29" s="1"/>
+      <c r="AI29" s="1"/>
+      <c r="AJ29" s="1"/>
+      <c r="AK29" s="1"/>
+      <c r="AL29" s="1"/>
+      <c r="AM29" s="1"/>
+      <c r="AN29" s="1"/>
+      <c r="AO29" s="1"/>
+      <c r="AP29" s="1"/>
+      <c r="AQ29" s="1"/>
+      <c r="AR29" s="1"/>
+      <c r="AS29" s="1"/>
+      <c r="AT29" s="1"/>
+      <c r="AU29" s="1"/>
+      <c r="AV29" s="1"/>
+      <c r="AW29" s="1"/>
+      <c r="AX29" s="1"/>
+    </row>
+    <row r="30" spans="1:50" s="1" customFormat="1">
+      <c r="A30" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B30" s="18" t="s">
         <v>519</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C30" s="1">
+        <v>2</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F30" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G30" s="1">
         <v>2013</v>
       </c>
     </row>
-    <row r="4" spans="1:47" s="1" customFormat="1">
-      <c r="A4" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F4" s="1">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="5" spans="1:47" s="1" customFormat="1">
-      <c r="A5" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F5" s="1">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="6" spans="1:47" s="1" customFormat="1">
-      <c r="A6" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" s="1">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="7" spans="1:47" s="1" customFormat="1">
-      <c r="A7" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="F7" s="1">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="8" spans="1:47" s="1" customFormat="1">
-      <c r="A8" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="F8" s="1">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="9" spans="1:47" s="1" customFormat="1">
-      <c r="A9" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1996</v>
-      </c>
-    </row>
-    <row r="10" spans="1:47" s="1" customFormat="1">
-      <c r="A10" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="11" spans="1:47" s="1" customFormat="1">
-      <c r="A11" s="1" t="s">
-        <v>506</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="12" spans="1:47" s="1" customFormat="1">
-      <c r="A12" s="1" t="s">
-        <v>1101</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1993</v>
-      </c>
-    </row>
-    <row r="13" spans="1:47" s="1" customFormat="1">
-      <c r="A13" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1991</v>
-      </c>
-    </row>
-    <row r="14" spans="1:47" s="1" customFormat="1">
-      <c r="A14" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="F14" s="1">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="15" spans="1:47" s="1" customFormat="1">
-      <c r="A15" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="F15" s="1">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="16" spans="1:47" s="1" customFormat="1">
-      <c r="A16" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="F16" s="1">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="17" spans="1:49" s="1" customFormat="1">
-      <c r="A17" s="1" t="s">
+    <row r="31" spans="1:50" s="1" customFormat="1">
+      <c r="A31" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>535</v>
+      </c>
+      <c r="C31" s="1">
+        <v>24</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="G31" s="11">
+        <v>2009</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>524</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>525</v>
+      </c>
+      <c r="J31" s="11">
+        <v>38.315705000000001</v>
+      </c>
+      <c r="K31" s="11">
+        <v>-123.070932</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>398</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="32" spans="1:50" s="1" customFormat="1">
+      <c r="A32" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>535</v>
+      </c>
+      <c r="C32" s="1">
+        <v>32</v>
+      </c>
+      <c r="D32" s="5">
+        <v>1</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="H32" s="5">
+        <v>2004</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>533</v>
+      </c>
+      <c r="K32" s="16">
+        <v>44.620725</v>
+      </c>
+      <c r="L32" s="16">
+        <v>-124.090729</v>
+      </c>
+      <c r="M32" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="N32" s="5" t="s">
+        <v>534</v>
+      </c>
+      <c r="O32" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="P32" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q32" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="R32" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="S32" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="T32" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="U32" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="V32" s="5"/>
+      <c r="W32" s="5" t="s">
+        <v>605</v>
+      </c>
+      <c r="X32" s="5">
+        <v>2002</v>
+      </c>
+      <c r="Y32" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="Z32" s="5" t="s">
+        <v>575</v>
+      </c>
+      <c r="AA32" s="5" t="s">
+        <v>576</v>
+      </c>
+      <c r="AB32" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="AC32" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="AD32" s="5" t="s">
+        <v>730</v>
+      </c>
+      <c r="AE32" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="AF32" s="5" t="s">
+        <v>799</v>
+      </c>
+      <c r="AG32" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="AH32" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="AI32" s="5" t="s">
+        <v>797</v>
+      </c>
+      <c r="AJ32" s="5" t="s">
+        <v>798</v>
+      </c>
+      <c r="AK32" s="5" t="s">
+        <v>739</v>
+      </c>
+      <c r="AL32" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="AM32" s="5" t="s">
+        <v>732</v>
+      </c>
+      <c r="AN32" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="AO32" s="5" t="s">
+        <v>663</v>
+      </c>
+      <c r="AP32" s="5">
+        <v>74.473684210526301</v>
+      </c>
+      <c r="AQ32" s="5">
+        <v>10.789473684210506</v>
+      </c>
+      <c r="AR32" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="AS32" s="5">
+        <v>15</v>
+      </c>
+      <c r="AT32" s="5">
+        <v>30.2631578947368</v>
+      </c>
+      <c r="AU32" s="5">
+        <v>7.6315789473684035</v>
+      </c>
+      <c r="AV32" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="AW32" s="5">
+        <v>12</v>
+      </c>
+      <c r="AX32" s="5" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" s="1" customFormat="1">
+      <c r="A33" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B33" s="19" t="s">
         <v>536</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C33" s="1">
+        <v>15</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E33" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="F33" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="F17" s="1">
+      <c r="G33" s="1">
         <v>2003</v>
       </c>
     </row>
-    <row r="18" spans="1:49" s="1" customFormat="1">
-      <c r="A18" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F18" s="1">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:49" s="1" customFormat="1">
-      <c r="A19" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="20" spans="1:49" s="1" customFormat="1">
-      <c r="A20" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="F20" s="1">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="21" spans="1:49" s="1" customFormat="1">
-      <c r="A21" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="F21" s="1">
-        <v>1988</v>
-      </c>
-    </row>
-    <row r="22" spans="1:49" s="1" customFormat="1">
-      <c r="A22" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="F22" s="1">
-        <v>1985</v>
-      </c>
-      <c r="AQ22" s="1" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="23" spans="1:49" s="1" customFormat="1">
-      <c r="A23" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="B23" s="11">
-        <v>1</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="F23" s="11">
-        <v>2009</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>466</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>467</v>
-      </c>
-      <c r="I23" s="11">
-        <v>7.588381</v>
-      </c>
-      <c r="J23" s="11">
-        <v>134.73338100000001</v>
-      </c>
-      <c r="K23" s="12" t="s">
-        <v>364</v>
-      </c>
-      <c r="L23" s="11" t="s">
-        <v>469</v>
-      </c>
-      <c r="M23" s="11"/>
-      <c r="P23" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="AV23"/>
-      <c r="AW23" s="1" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="24" spans="1:49" s="1" customFormat="1">
-      <c r="A24" s="1" t="s">
-        <v>774</v>
-      </c>
-      <c r="B24" s="11">
-        <v>1</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="F24" s="11">
-        <v>2015</v>
-      </c>
-      <c r="G24" s="11" t="s">
-        <v>517</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>518</v>
-      </c>
-      <c r="I24" s="11">
-        <v>47.016666999999998</v>
-      </c>
-      <c r="J24" s="11">
-        <v>-2.0333329999999998</v>
-      </c>
-      <c r="K24" s="11" t="s">
-        <v>326</v>
-      </c>
-      <c r="L24" s="11" t="s">
-        <v>372</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="O24" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="P24" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>875</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="AV24"/>
-    </row>
-    <row r="25" spans="1:49" s="1" customFormat="1">
-      <c r="A25" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="B25" s="11">
-        <v>1</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="F25" s="11">
-        <v>2009</v>
-      </c>
-      <c r="G25" s="11" t="s">
-        <v>524</v>
-      </c>
-      <c r="H25" s="11" t="s">
-        <v>525</v>
-      </c>
-      <c r="I25" s="11">
-        <v>38.315705000000001</v>
-      </c>
-      <c r="J25" s="11">
-        <v>-123.070932</v>
-      </c>
-      <c r="K25" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="L25" s="11" t="s">
-        <v>398</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="O25" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="P25" s="1" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="26" spans="1:49" s="1" customFormat="1">
-      <c r="A26" s="1" t="s">
-        <v>1031</v>
-      </c>
-      <c r="B26" s="11">
-        <v>1</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="F26" s="1">
-        <v>2004</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="I26" s="1">
-        <v>59.751111000000002</v>
-      </c>
-      <c r="J26" s="1">
-        <v>23.219166999999999</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>647</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="O26" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="Q26" s="1" t="s">
-        <v>1028</v>
-      </c>
-      <c r="R26" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="T26" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="U26" s="1">
-        <v>2000</v>
-      </c>
-      <c r="V26" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="W26" s="1" t="s">
-        <v>1029</v>
-      </c>
-      <c r="X26" s="1" t="s">
-        <v>859</v>
-      </c>
-      <c r="Y26" s="1" t="s">
-        <v>860</v>
-      </c>
-      <c r="Z26" s="1" t="s">
-        <v>1030</v>
-      </c>
-      <c r="AA26" s="1" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="27" spans="1:49" s="1" customFormat="1">
-      <c r="A27" s="1" t="s">
-        <v>995</v>
-      </c>
-      <c r="B27" s="11">
-        <v>1</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F27" s="1">
-        <v>2017</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="I27" s="1">
-        <v>-37.006335999999997</v>
-      </c>
-      <c r="J27" s="1">
-        <v>175.89027200000001</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="O27" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="P27" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>991</v>
-      </c>
-      <c r="R27" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="S27" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="T27" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="U27" s="1">
-        <v>2008</v>
-      </c>
-      <c r="V27" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="W27" s="1" t="s">
-        <v>994</v>
-      </c>
-      <c r="X27" s="1" t="s">
-        <v>859</v>
-      </c>
-      <c r="Y27" s="1" t="s">
-        <v>860</v>
-      </c>
-      <c r="Z27" s="1" t="s">
-        <v>992</v>
-      </c>
-      <c r="AA27" s="1" t="s">
-        <v>993</v>
-      </c>
-      <c r="AV27"/>
-      <c r="AW27" s="1" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="28" spans="1:49" s="1" customFormat="1">
-      <c r="A28" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="F28" s="1">
-        <v>1980</v>
-      </c>
-    </row>
-    <row r="29" spans="1:49" s="1" customFormat="1" ht="18">
-      <c r="A29" s="1" t="s">
-        <v>515</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="F29" s="1">
-        <v>2016</v>
-      </c>
-      <c r="AV29"/>
-      <c r="AW29" s="8" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="30" spans="1:49" s="1" customFormat="1">
-      <c r="A30" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="F30" s="1">
-        <v>2013</v>
-      </c>
-      <c r="AV30"/>
-      <c r="AW30" s="1" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="31" spans="1:49" s="1" customFormat="1">
-      <c r="A31" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="F31" s="1">
-        <v>1967</v>
-      </c>
-    </row>
-    <row r="32" spans="1:49" s="1" customFormat="1">
-      <c r="A32" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F32" s="1">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="33" spans="1:49" s="5" customFormat="1">
-      <c r="A33" s="5" t="s">
-        <v>535</v>
-      </c>
-      <c r="B33" s="5">
-        <v>37</v>
-      </c>
-      <c r="C33" s="5">
-        <v>1</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>531</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="G33" s="5">
-        <v>2004</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>532</v>
-      </c>
-      <c r="I33" s="5" t="s">
-        <v>533</v>
-      </c>
-      <c r="J33" s="16">
-        <v>44.620725</v>
-      </c>
-      <c r="K33" s="16">
-        <v>-124.090729</v>
-      </c>
-      <c r="L33" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="M33" s="5" t="s">
-        <v>534</v>
-      </c>
-      <c r="N33" s="5" t="s">
-        <v>570</v>
-      </c>
-      <c r="O33" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="P33" s="5" t="s">
-        <v>775</v>
-      </c>
-      <c r="Q33" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="R33" s="5" t="s">
-        <v>896</v>
-      </c>
-      <c r="S33" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="T33" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="V33" s="5" t="s">
-        <v>605</v>
-      </c>
-      <c r="W33" s="5">
-        <v>2002</v>
-      </c>
-      <c r="X33" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="Y33" s="5" t="s">
-        <v>575</v>
-      </c>
-      <c r="Z33" s="5" t="s">
-        <v>576</v>
-      </c>
-      <c r="AA33" s="5" t="s">
-        <v>577</v>
-      </c>
-      <c r="AB33" s="5" t="s">
-        <v>578</v>
-      </c>
-      <c r="AC33" s="5" t="s">
-        <v>730</v>
-      </c>
-      <c r="AD33" s="5" t="s">
-        <v>295</v>
-      </c>
-      <c r="AE33" s="5" t="s">
-        <v>799</v>
-      </c>
-      <c r="AF33" s="5" t="s">
-        <v>613</v>
-      </c>
-      <c r="AG33" s="5" t="s">
-        <v>637</v>
-      </c>
-      <c r="AH33" s="5" t="s">
-        <v>797</v>
-      </c>
-      <c r="AI33" s="5" t="s">
-        <v>798</v>
-      </c>
-      <c r="AJ33" s="5" t="s">
-        <v>739</v>
-      </c>
-      <c r="AK33" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="AL33" s="5" t="s">
-        <v>732</v>
-      </c>
-      <c r="AM33" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="AN33" s="5" t="s">
-        <v>663</v>
-      </c>
-      <c r="AO33" s="5">
-        <v>74.473684210526301</v>
-      </c>
-      <c r="AP33" s="5">
-        <v>10.789473684210506</v>
-      </c>
-      <c r="AQ33" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="AR33" s="5">
-        <v>15</v>
-      </c>
-      <c r="AS33" s="5">
-        <v>30.2631578947368</v>
-      </c>
-      <c r="AT33" s="5">
-        <v>7.6315789473684035</v>
-      </c>
-      <c r="AU33" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="AV33" s="5">
-        <v>12</v>
-      </c>
-      <c r="AW33" s="5" t="s">
-        <v>895</v>
-      </c>
-    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:AX40">
+    <sortCondition ref="A1"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/Output/Data/meta_analysis_data.xlsx
+++ b/Output/Data/meta_analysis_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilylim/Documents/MSc/Ch2-Meta-analysis/Output/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34A75613-1494-D644-BFB1-AD7F2C0E0FCA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E53B579-787C-2E41-9EC5-361EAB8E9158}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8780" yWindow="460" windowWidth="23540" windowHeight="15840" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
+    <workbookView xWindow="3060" yWindow="460" windowWidth="23540" windowHeight="15840" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
   </bookViews>
   <sheets>
     <sheet name="Include" sheetId="1" r:id="rId1"/>
@@ -13502,7 +13502,7 @@
         <v>314</v>
       </c>
       <c r="AJ60" s="1" t="s">
-        <v>805</v>
+        <v>718</v>
       </c>
       <c r="AK60" s="1" t="s">
         <v>360</v>
@@ -13651,7 +13651,7 @@
         <v>314</v>
       </c>
       <c r="AJ61" s="1" t="s">
-        <v>718</v>
+        <v>805</v>
       </c>
       <c r="AK61" s="1" t="s">
         <v>360</v>
@@ -13800,7 +13800,7 @@
         <v>314</v>
       </c>
       <c r="AJ62" s="1" t="s">
-        <v>718</v>
+        <v>805</v>
       </c>
       <c r="AK62" s="1" t="s">
         <v>360</v>
@@ -13949,7 +13949,7 @@
         <v>314</v>
       </c>
       <c r="AJ63" s="1" t="s">
-        <v>718</v>
+        <v>805</v>
       </c>
       <c r="AK63" s="1" t="s">
         <v>360</v>
@@ -14098,7 +14098,7 @@
         <v>314</v>
       </c>
       <c r="AJ64" s="1" t="s">
-        <v>718</v>
+        <v>805</v>
       </c>
       <c r="AK64" s="1" t="s">
         <v>360</v>
@@ -14247,7 +14247,7 @@
         <v>314</v>
       </c>
       <c r="AJ65" s="1" t="s">
-        <v>718</v>
+        <v>805</v>
       </c>
       <c r="AK65" s="1" t="s">
         <v>360</v>

--- a/Output/Data/meta_analysis_data.xlsx
+++ b/Output/Data/meta_analysis_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emilylim/Documents/MSc/Ch2-Meta-analysis/Output/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emlim/Documents/MSc/Ch2-Meta-analysis/Output/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E53B579-787C-2E41-9EC5-361EAB8E9158}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B9D777A-A66C-1D4D-811A-89F35DF3626A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3060" yWindow="460" windowWidth="23540" windowHeight="15840" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
+    <workbookView xWindow="41800" yWindow="960" windowWidth="23540" windowHeight="15840" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
   </bookViews>
   <sheets>
     <sheet name="Include" sheetId="1" r:id="rId1"/>
@@ -37115,7 +37115,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AV34">
+  <sortState ref="A2:AV34">
     <sortCondition ref="A1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -38420,7 +38420,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:AX40">
+  <sortState ref="A1:AX40">
     <sortCondition ref="A1"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Output/Data/meta_analysis_data.xlsx
+++ b/Output/Data/meta_analysis_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emlim/Documents/MSc/Ch2-Meta-analysis/Output/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD260D8B-CF07-9D48-80A2-D4836210D8E6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77699900-491D-6242-8B77-0FE6151AE526}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41120" yWindow="460" windowWidth="24360" windowHeight="18320" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
+    <workbookView xWindow="36200" yWindow="460" windowWidth="24360" windowHeight="18320" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
   </bookViews>
   <sheets>
     <sheet name="Include" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11394" uniqueCount="1342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11405" uniqueCount="1341">
   <si>
     <t>paper_num</t>
   </si>
@@ -4210,9 +4210,6 @@
   </si>
   <si>
     <t>shoot size</t>
-  </si>
-  <si>
-    <t>144.7.3</t>
   </si>
   <si>
     <t>measured NPP over the day, have NPP estimates for each time period. I summed the total NPP over the day and got the adjusted se by sqrt(sum of squares). The oysters are "stocked" but the seagrass is unmanipulated. Water column ammonium, nitrate, and porewater ammonium</t>
@@ -5459,7 +5456,7 @@
         <v>11.3</v>
       </c>
       <c r="BR3" s="1" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="4" spans="1:70">
@@ -7367,7 +7364,7 @@
         <v>25</v>
       </c>
       <c r="BR12" s="1" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="13" spans="1:70">
@@ -7579,7 +7576,7 @@
         <v>25</v>
       </c>
       <c r="BR13" s="1" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="14" spans="1:70">
@@ -7791,7 +7788,7 @@
         <v>25</v>
       </c>
       <c r="BR14" s="1" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="15" spans="1:70">
@@ -8003,7 +8000,7 @@
         <v>23</v>
       </c>
       <c r="BR15" s="1" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="16" spans="1:70">
@@ -8215,7 +8212,7 @@
         <v>23</v>
       </c>
       <c r="BR16" s="1" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="17" spans="1:70">
@@ -8851,7 +8848,7 @@
         <v>18</v>
       </c>
       <c r="BR19" s="11" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="20" spans="1:70">
@@ -8961,7 +8958,7 @@
         <v>665</v>
       </c>
       <c r="AJ20" s="1" t="s">
-        <v>666</v>
+        <v>985</v>
       </c>
       <c r="AK20" s="1" t="s">
         <v>360</v>
@@ -9063,7 +9060,7 @@
         <v>18</v>
       </c>
       <c r="BR20" s="11" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="21" spans="1:70">
@@ -9173,7 +9170,7 @@
         <v>665</v>
       </c>
       <c r="AJ21" s="1" t="s">
-        <v>666</v>
+        <v>985</v>
       </c>
       <c r="AK21" s="1" t="s">
         <v>360</v>
@@ -9275,7 +9272,7 @@
         <v>18</v>
       </c>
       <c r="BR21" s="11" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="22" spans="1:70">
@@ -9385,7 +9382,7 @@
         <v>665</v>
       </c>
       <c r="AJ22" s="1" t="s">
-        <v>666</v>
+        <v>985</v>
       </c>
       <c r="AK22" s="1" t="s">
         <v>360</v>
@@ -9487,7 +9484,7 @@
         <v>18</v>
       </c>
       <c r="BR22" s="11" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="23" spans="1:70">
@@ -9597,7 +9594,7 @@
         <v>665</v>
       </c>
       <c r="AJ23" s="1" t="s">
-        <v>666</v>
+        <v>985</v>
       </c>
       <c r="AK23" s="1" t="s">
         <v>360</v>
@@ -9611,8 +9608,11 @@
       <c r="AN23" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="AO23" s="1" t="s">
-        <v>1300</v>
+      <c r="AO23" s="1">
+        <v>144.69999999999999</v>
+      </c>
+      <c r="AP23" s="1">
+        <v>7.3</v>
       </c>
       <c r="AQ23" s="11" t="s">
         <v>314</v>
@@ -9696,7 +9696,7 @@
         <v>18</v>
       </c>
       <c r="BR23" s="11" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="24" spans="1:70">
@@ -9908,7 +9908,7 @@
         <v>25</v>
       </c>
       <c r="BR24" s="1" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="25" spans="1:70">
@@ -10120,7 +10120,7 @@
         <v>25</v>
       </c>
       <c r="BR25" s="1" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="26" spans="1:70">
@@ -10332,7 +10332,7 @@
         <v>25</v>
       </c>
       <c r="BR26" s="1" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="27" spans="1:70">
@@ -10544,7 +10544,7 @@
         <v>19.458930899999999</v>
       </c>
       <c r="BR27" s="1" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="28" spans="1:70">
@@ -10756,7 +10756,7 @@
         <v>25.725274725274684</v>
       </c>
       <c r="BR28" s="1" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="29" spans="1:70">
@@ -12452,7 +12452,7 @@
         <v>27.2</v>
       </c>
       <c r="BR36" s="1" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="37" spans="1:70">
@@ -12664,7 +12664,7 @@
         <v>26</v>
       </c>
       <c r="BR37" s="1" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="38" spans="1:70">
@@ -12876,7 +12876,7 @@
         <v>26</v>
       </c>
       <c r="BR38" s="1" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="39" spans="1:70">
@@ -13088,7 +13088,7 @@
         <v>26</v>
       </c>
       <c r="BR39" s="1" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="40" spans="1:70">
@@ -13300,7 +13300,7 @@
         <v>26</v>
       </c>
       <c r="BR40" s="1" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="41" spans="1:70">
@@ -13512,7 +13512,7 @@
         <v>26</v>
       </c>
       <c r="BR41" s="1" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="42" spans="1:70">
@@ -13724,7 +13724,7 @@
         <v>26</v>
       </c>
       <c r="BR42" s="1" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="43" spans="1:70">
@@ -13936,7 +13936,7 @@
         <v>28.65</v>
       </c>
       <c r="BR43" s="1" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="44" spans="1:70">
@@ -14148,7 +14148,7 @@
         <v>17</v>
       </c>
       <c r="BR44" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="45" spans="1:70">
@@ -14360,7 +14360,7 @@
         <v>27.94</v>
       </c>
       <c r="BR45" s="1" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="46" spans="1:70">
@@ -14572,7 +14572,7 @@
         <v>25</v>
       </c>
       <c r="BR46" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="47" spans="1:70">
@@ -14784,7 +14784,7 @@
         <v>26.17</v>
       </c>
       <c r="BR47" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="48" spans="1:70">
@@ -18388,7 +18388,7 @@
         <v>27</v>
       </c>
       <c r="BR64" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="65" spans="1:70">
@@ -27716,7 +27716,7 @@
         <v>25</v>
       </c>
       <c r="BR108" s="1" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="109" spans="1:70">
@@ -35842,6 +35842,9 @@
       <c r="V147" s="1" t="s">
         <v>602</v>
       </c>
+      <c r="W147" s="1" t="s">
+        <v>314</v>
+      </c>
       <c r="X147" s="1" t="s">
         <v>295</v>
       </c>
@@ -36051,6 +36054,9 @@
       <c r="V148" s="1" t="s">
         <v>602</v>
       </c>
+      <c r="W148" s="1" t="s">
+        <v>314</v>
+      </c>
       <c r="X148" s="1" t="s">
         <v>295</v>
       </c>
@@ -36260,6 +36266,9 @@
       <c r="V149" s="1" t="s">
         <v>602</v>
       </c>
+      <c r="W149" s="1" t="s">
+        <v>314</v>
+      </c>
       <c r="X149" s="1" t="s">
         <v>295</v>
       </c>
@@ -36469,6 +36478,9 @@
       <c r="V150" s="1" t="s">
         <v>602</v>
       </c>
+      <c r="W150" s="1" t="s">
+        <v>314</v>
+      </c>
       <c r="X150" s="1" t="s">
         <v>295</v>
       </c>
@@ -36678,6 +36690,9 @@
       <c r="V151" s="1" t="s">
         <v>602</v>
       </c>
+      <c r="W151" s="1" t="s">
+        <v>314</v>
+      </c>
       <c r="X151" s="1" t="s">
         <v>295</v>
       </c>
@@ -36887,6 +36902,9 @@
       <c r="V152" s="1" t="s">
         <v>602</v>
       </c>
+      <c r="W152" s="1" t="s">
+        <v>314</v>
+      </c>
       <c r="X152" s="1" t="s">
         <v>295</v>
       </c>
@@ -37096,6 +37114,9 @@
       <c r="V153" s="1" t="s">
         <v>574</v>
       </c>
+      <c r="W153" s="1" t="s">
+        <v>314</v>
+      </c>
       <c r="X153" s="1" t="s">
         <v>295</v>
       </c>
@@ -37305,6 +37326,9 @@
       <c r="V154" s="1" t="s">
         <v>574</v>
       </c>
+      <c r="W154" s="1" t="s">
+        <v>314</v>
+      </c>
       <c r="X154" s="1" t="s">
         <v>295</v>
       </c>
@@ -37514,6 +37538,9 @@
       <c r="V155" s="1" t="s">
         <v>574</v>
       </c>
+      <c r="W155" s="1" t="s">
+        <v>314</v>
+      </c>
       <c r="X155" s="1" t="s">
         <v>295</v>
       </c>
@@ -37723,6 +37750,9 @@
       <c r="V156" s="1" t="s">
         <v>574</v>
       </c>
+      <c r="W156" s="1" t="s">
+        <v>314</v>
+      </c>
       <c r="X156" s="1" t="s">
         <v>295</v>
       </c>
@@ -37932,6 +37962,9 @@
       <c r="V157" s="1" t="s">
         <v>574</v>
       </c>
+      <c r="W157" s="1" t="s">
+        <v>314</v>
+      </c>
       <c r="X157" s="1" t="s">
         <v>295</v>
       </c>
@@ -38141,6 +38174,9 @@
       <c r="V158" s="1" t="s">
         <v>574</v>
       </c>
+      <c r="W158" s="1" t="s">
+        <v>314</v>
+      </c>
       <c r="X158" s="1" t="s">
         <v>295</v>
       </c>
@@ -41740,7 +41776,7 @@
         <v>314</v>
       </c>
       <c r="W175" s="1" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="X175" s="11" t="s">
         <v>312</v>
@@ -41788,7 +41824,7 @@
         <v>1134</v>
       </c>
       <c r="AM175" s="11" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="AN175" s="11" t="s">
         <v>314</v>
@@ -41881,7 +41917,7 @@
         <v>26.499666666666666</v>
       </c>
       <c r="BR175" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="176" spans="1:70">
@@ -41952,7 +41988,7 @@
         <v>314</v>
       </c>
       <c r="W176" s="1" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="X176" s="11" t="s">
         <v>312</v>
@@ -42093,7 +42129,7 @@
         <v>26.499666666666666</v>
       </c>
       <c r="BR176" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="177" spans="1:70">
@@ -42164,7 +42200,7 @@
         <v>314</v>
       </c>
       <c r="W177" s="1" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="X177" s="11" t="s">
         <v>312</v>
@@ -42212,7 +42248,7 @@
         <v>1134</v>
       </c>
       <c r="AM177" s="11" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="AN177" s="11" t="s">
         <v>314</v>
@@ -42305,7 +42341,7 @@
         <v>26.499666666666666</v>
       </c>
       <c r="BR177" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="178" spans="1:70">
@@ -42373,7 +42409,7 @@
         <v>1</v>
       </c>
       <c r="V178" s="1" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="W178" s="1">
         <v>1981</v>
@@ -42517,7 +42553,7 @@
         <v>26.499666666666666</v>
       </c>
       <c r="BR178" s="1" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="179" spans="1:70">
@@ -42585,7 +42621,7 @@
         <v>1</v>
       </c>
       <c r="V179" s="1" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="W179" s="1">
         <v>1981</v>
@@ -42636,7 +42672,7 @@
         <v>1134</v>
       </c>
       <c r="AM179" s="11" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="AN179" s="11" t="s">
         <v>658</v>
@@ -42729,7 +42765,7 @@
         <v>26.499666666666666</v>
       </c>
       <c r="BR179" s="1" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="180" spans="1:70">
@@ -42797,7 +42833,7 @@
         <v>1</v>
       </c>
       <c r="V180" s="1" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="W180" s="1">
         <v>1981</v>
@@ -42848,7 +42884,7 @@
         <v>1134</v>
       </c>
       <c r="AM180" s="11" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="AN180" s="11" t="s">
         <v>658</v>
@@ -42941,7 +42977,7 @@
         <v>26.499666666666666</v>
       </c>
       <c r="BR180" s="1" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="181" spans="1:70">
@@ -43009,7 +43045,7 @@
         <v>1</v>
       </c>
       <c r="V181" s="1" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="W181" s="1">
         <v>1981</v>
@@ -43060,7 +43096,7 @@
         <v>1134</v>
       </c>
       <c r="AM181" s="11" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="AN181" s="11" t="s">
         <v>658</v>
@@ -43153,7 +43189,7 @@
         <v>26.499666666666666</v>
       </c>
       <c r="BR181" s="1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="182" spans="1:70">
@@ -43221,7 +43257,7 @@
         <v>1</v>
       </c>
       <c r="V182" s="1" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="W182" s="1">
         <v>1981</v>
@@ -43365,7 +43401,7 @@
         <v>26.499666666666666</v>
       </c>
       <c r="BR182" s="1" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="183" spans="1:70">
@@ -43433,7 +43469,7 @@
         <v>1</v>
       </c>
       <c r="V183" s="1" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="W183" s="1">
         <v>1981</v>
@@ -43484,7 +43520,7 @@
         <v>1134</v>
       </c>
       <c r="AM183" s="11" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="AN183" s="11" t="s">
         <v>658</v>
@@ -43577,7 +43613,7 @@
         <v>26.499666666666666</v>
       </c>
       <c r="BR183" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="184" spans="1:70">

--- a/Output/Data/meta_analysis_data.xlsx
+++ b/Output/Data/meta_analysis_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emlim/Documents/MSc/Ch2-Meta-analysis/Output/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77699900-491D-6242-8B77-0FE6151AE526}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332DD5A0-2595-EB40-8170-C1A37CB01AA4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36200" yWindow="460" windowWidth="24360" windowHeight="18320" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
+    <workbookView xWindow="31920" yWindow="460" windowWidth="30920" windowHeight="19400" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
   </bookViews>
   <sheets>
     <sheet name="Include" sheetId="1" r:id="rId1"/>

--- a/Output/Data/meta_analysis_data.xlsx
+++ b/Output/Data/meta_analysis_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emlim/Documents/MSc/Ch2-Meta-analysis/Output/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332DD5A0-2595-EB40-8170-C1A37CB01AA4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE7F0A8-014D-D34A-8F0F-B5710DC0B5CA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31920" yWindow="460" windowWidth="30920" windowHeight="19400" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
+    <workbookView xWindow="30480" yWindow="460" windowWidth="34880" windowHeight="21840" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
   </bookViews>
   <sheets>
     <sheet name="Include" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11405" uniqueCount="1341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11669" uniqueCount="1350">
   <si>
     <t>paper_num</t>
   </si>
@@ -3990,9 +3990,6 @@
     <t>used bivalves to filter phytoplankton, not as a source of nutrients. Found that bivalves decreased chl a concentration and increased light availability</t>
   </si>
   <si>
-    <t>the regeneration is the area of basal disk relative to the initial area. They also measured the concentration of zooxanthellae. Background = amount of ammonium in natural water. This paper states nitrate was below detection limit (https://royalsocietypublishing.org/doi/epdf/10.1098/rspb.1989.0025).     temp from http://www.int-res.com/articles/meps/77/m077p253.pdf</t>
-  </si>
-  <si>
     <t>concentration of zooxanthellae in tentacles (zooxanthellae per g tentacle tissue. Background = amount of ammonium in natural water. This paper states nitrate was below detection limit (https://royalsocietypublishing.org/doi/epdf/10.1098/rspb.1989.0025).     temp from http://www.int-res.com/articles/meps/77/m077p253.pdf</t>
   </si>
   <si>
@@ -4155,12 +4152,6 @@
     <t>went to cays with and without roosting birds, found more aboveground biomass at cays with birds. Also found enriched N in mangrove leaves at cays with birds, and that over time the cays with birds are washing away faster bc of eutrophication. Temp from Ellison</t>
   </si>
   <si>
-    <t>coral growth in mg/cm^2/day. Nutrients were presented as the calculated N provided by each treatment</t>
-  </si>
-  <si>
-    <t>algae (algae/cm^2). Nutrients were presented as the calculated N provided by each treatment</t>
-  </si>
-  <si>
     <t>belowground biomass in (g) between plots planted with seagrass seeds vs seeds and clams. Temp from https://link.springer.com/content/pdf/10.1007/BF00341470.pdf</t>
   </si>
   <si>
@@ -4272,15 +4263,9 @@
     <t>caves have sponges, nitrate signal comes from cave. MC cave lost sponges after sediment. Transplant experiment from communal garden location to MC cave (control)  and AFBH cace (treatment). Data shows change (pre - post) coral circumference over 2 years. Background = avg from MC and AFBH</t>
   </si>
   <si>
-    <t>really well done! Grew Ulva with different nutrient additions, including snail excretion. There was also a field experiment but they had inner vs outer harbour and two time series and also the snails were eating the ulva. Just going with the one simple lab study. Ammonium and nitrate in μmol N indiv−1 d−1 excretion rates</t>
-  </si>
-  <si>
     <t>artificial reefs built at 4 sites, 4 controls. Measured PP in 3 quads at each reef, also measured leaf area and aboveground biomass but showed with herbivory estimates that these were affected by graazing so I decided to just use productivity so its not confounded with grazing. background https://link.springer.com/content/pdf/10.2307/1352460.pdf     temp from https://link.springer.com/content/pdf/10.2307/1352460.pdf</t>
   </si>
   <si>
-    <t>artificial reefs, not 100% sure about sample size??? 2-5 blades per stake, 9 stakes per site, 12 sites???? But 4 treatment levels? small, medium, large and xl. Background from https://aslopubs.onlinelibrary.wiley.com/doi/epdf/10.4319/lo.2010.55.6.2660.      temp from https://link.springer.com/article/10.1007/s00338-020-01948-0</t>
-  </si>
-  <si>
     <t>state that they had balanced 10 vs 10 design but raw data only shows 2 control colonies. Nh4 is the calculated excretion rate of the group of damsel fish in umoles l-1 h-1. Estimated background nitrate from https://www.jstor.org/stable/24862064?seq=1            temperature estimated from https://www.int-res.com/articles/meps/121/m121p181.pdf</t>
   </si>
   <si>
@@ -4332,7 +4317,49 @@
     <t>Looked at corals with and without grunts</t>
   </si>
   <si>
-    <t>Looked at corals with and without grunts. Background from Meyer, nh4 addition estimated 400 umol/L per year</t>
+    <t>Looked at corals with and without grunts. Background from Meyer, nh4 addition estimated 400 umol/L per year, I converted it to umol/L/day</t>
+  </si>
+  <si>
+    <t>coral growth in mg/cm^2/day. Nutrients were presented as the calculated N provided by each treatment (g/day)</t>
+  </si>
+  <si>
+    <t>algae (algae/cm^2). Nutrients were presented as the calculated N provided by each treatment (g/day)</t>
+  </si>
+  <si>
+    <t>artificial reefs, not 100% sure about sample size??? 2-5 blades per stake, 9 stakes per site, 12 sites???? But 4 treatment levels? small, medium, large and xl. Calculated fish excretion (g/day) Background from https://aslopubs.onlinelibrary.wiley.com/doi/epdf/10.4319/lo.2010.55.6.2660.      temp from https://link.springer.com/article/10.1007/s00338-020-01948-0</t>
+  </si>
+  <si>
+    <t>prov_units</t>
+  </si>
+  <si>
+    <t>g/day</t>
+  </si>
+  <si>
+    <t>mg/m^2/day</t>
+  </si>
+  <si>
+    <t>umol/L/day</t>
+  </si>
+  <si>
+    <t>umol/L</t>
+  </si>
+  <si>
+    <t>really well done! Grew Ulva with different nutrient additions, including snail excretion. There was also a field experiment but they had inner vs outer harbour and two time series and also the snails were eating the ulva. Just going with the one simple lab study. Ammonium and nitrate in μmol N indiv−1 d−1 excretion rates. But there was 1 snail in 100 mL water for 24 hours  so I converted it to umol/L as a measured concentration</t>
+  </si>
+  <si>
+    <t>mmol/m^2/day</t>
+  </si>
+  <si>
+    <t>the regeneration is the area of basal disk relative to the initial area. They also measured the concentration of zooxanthellae. Background = amount of ammonium in natural water. Measured excretion in umol/L/h, two hour experiment = double that? This paper states nitrate was below detection limit (https://royalsocietypublishing.org/doi/epdf/10.1098/rspb.1989.0025).     temp from http://www.int-res.com/articles/meps/77/m077p253.pdf</t>
+  </si>
+  <si>
+    <t>umol/hour</t>
+  </si>
+  <si>
+    <t>umol/L/h</t>
+  </si>
+  <si>
+    <t>mg/L/h</t>
   </si>
 </sst>
 </file>
@@ -4810,7 +4837,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{373FE451-5807-5F48-890D-6AF5AC78FE37}">
-  <dimension ref="A1:BR189"/>
+  <dimension ref="A1:BS189"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="62" width="10.83203125" style="1"/>
@@ -4818,12 +4845,12 @@
     <col min="64" max="64" width="10.83203125" style="1"/>
     <col min="65" max="65" width="10.83203125" style="1" customWidth="1"/>
     <col min="66" max="66" width="10.83203125" style="1"/>
-    <col min="67" max="67" width="10.83203125" style="1" customWidth="1"/>
-    <col min="68" max="68" width="11.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="69" max="16384" width="10.83203125" style="1"/>
+    <col min="67" max="68" width="10.83203125" style="1" customWidth="1"/>
+    <col min="69" max="69" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="70" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:70">
+    <row r="1" spans="1:71">
       <c r="A1" s="1" t="s">
         <v>1130</v>
       </c>
@@ -5011,31 +5038,34 @@
         <v>1203</v>
       </c>
       <c r="BK1" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="BN1" s="1" t="s">
         <v>1294</v>
-      </c>
-      <c r="BL1" s="1" t="s">
-        <v>1295</v>
-      </c>
-      <c r="BM1" s="1" t="s">
-        <v>1296</v>
-      </c>
-      <c r="BN1" s="1" t="s">
-        <v>1297</v>
       </c>
       <c r="BO1" s="1" t="s">
         <v>1205</v>
       </c>
       <c r="BP1" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
         <v>1210</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>1212</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:70">
+    <row r="2" spans="1:71">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -5237,17 +5267,20 @@
       <c r="BO2" s="1" t="s">
         <v>1206</v>
       </c>
-      <c r="BP2" s="1">
+      <c r="BP2" s="1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ2" s="1">
         <v>1.0649999999999999</v>
       </c>
-      <c r="BQ2" s="1">
+      <c r="BR2" s="1">
         <v>27.950000000000003</v>
       </c>
-      <c r="BR2" s="1" t="s">
-        <v>1287</v>
-      </c>
-    </row>
-    <row r="3" spans="1:70">
+      <c r="BS2" s="1" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="3" spans="1:71">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -5449,17 +5482,20 @@
       <c r="BO3" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="BP3" s="11">
+      <c r="BP3" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BQ3" s="11">
         <v>10.1</v>
       </c>
-      <c r="BQ3" s="1">
+      <c r="BR3" s="1">
         <v>11.3</v>
       </c>
-      <c r="BR3" s="1" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="4" spans="1:70">
+      <c r="BS3" s="1" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="4" spans="1:71">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -5661,17 +5697,20 @@
       <c r="BO4" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="BP4" s="1">
+      <c r="BP4" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BQ4" s="1">
         <v>1.17E-6</v>
       </c>
-      <c r="BQ4" s="1">
+      <c r="BR4" s="1">
         <v>25</v>
       </c>
-      <c r="BR4" s="11" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="5" spans="1:70">
+      <c r="BS4" s="11" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="5" spans="1:71">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -5873,17 +5912,20 @@
       <c r="BO5" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="BP5" s="1">
+      <c r="BP5" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BQ5" s="1">
         <v>1.17E-6</v>
       </c>
-      <c r="BQ5" s="1">
+      <c r="BR5" s="1">
         <v>25</v>
       </c>
-      <c r="BR5" s="1" t="s">
-        <v>1289</v>
-      </c>
-    </row>
-    <row r="6" spans="1:70">
+      <c r="BS5" s="1" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="6" spans="1:71">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -6085,17 +6127,20 @@
       <c r="BO6" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="BP6" s="1">
+      <c r="BP6" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BQ6" s="1">
         <v>1.17E-6</v>
       </c>
-      <c r="BQ6" s="1">
+      <c r="BR6" s="1">
         <v>25</v>
       </c>
-      <c r="BR6" s="1" t="s">
-        <v>1289</v>
-      </c>
-    </row>
-    <row r="7" spans="1:70">
+      <c r="BS6" s="1" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="7" spans="1:71">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -6297,17 +6342,20 @@
       <c r="BO7" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="BP7" s="1">
+      <c r="BP7" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BQ7" s="1">
         <v>1.17E-6</v>
       </c>
-      <c r="BQ7" s="1">
+      <c r="BR7" s="1">
         <v>25</v>
       </c>
-      <c r="BR7" s="1" t="s">
-        <v>1289</v>
-      </c>
-    </row>
-    <row r="8" spans="1:70">
+      <c r="BS7" s="1" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="8" spans="1:71">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -6509,17 +6557,20 @@
       <c r="BO8" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="BP8" s="1">
+      <c r="BP8" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BQ8" s="1">
         <v>1.17E-6</v>
       </c>
-      <c r="BQ8" s="1">
+      <c r="BR8" s="1">
         <v>25</v>
       </c>
-      <c r="BR8" s="1" t="s">
-        <v>1290</v>
-      </c>
-    </row>
-    <row r="9" spans="1:70">
+      <c r="BS8" s="1" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="9" spans="1:71">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -6721,17 +6772,20 @@
       <c r="BO9" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="BP9" s="1">
+      <c r="BP9" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BQ9" s="1">
         <v>1.17E-6</v>
       </c>
-      <c r="BQ9" s="1">
+      <c r="BR9" s="1">
         <v>25</v>
       </c>
-      <c r="BR9" s="1" t="s">
-        <v>1291</v>
-      </c>
-    </row>
-    <row r="10" spans="1:70">
+      <c r="BS9" s="1" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="10" spans="1:71">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -6933,17 +6987,20 @@
       <c r="BO10" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="BP10" s="1">
+      <c r="BP10" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BQ10" s="1">
         <v>1.17E-6</v>
       </c>
-      <c r="BQ10" s="1">
+      <c r="BR10" s="1">
         <v>25</v>
       </c>
-      <c r="BR10" s="1" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="11" spans="1:70">
+      <c r="BS10" s="1" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="11" spans="1:71">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -7145,17 +7202,20 @@
       <c r="BO11" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="BP11" s="1">
+      <c r="BP11" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BQ11" s="1">
         <v>1.17E-6</v>
       </c>
-      <c r="BQ11" s="1">
+      <c r="BR11" s="1">
         <v>25</v>
       </c>
-      <c r="BR11" s="1" t="s">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="12" spans="1:70">
+      <c r="BS11" s="1" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="12" spans="1:71">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -7357,17 +7417,20 @@
       <c r="BO12" s="11" t="s">
         <v>1207</v>
       </c>
-      <c r="BP12" s="11">
+      <c r="BP12" s="11" t="s">
+        <v>1340</v>
+      </c>
+      <c r="BQ12" s="11">
         <v>2.13</v>
       </c>
-      <c r="BQ12" s="11">
+      <c r="BR12" s="11">
         <v>25</v>
       </c>
-      <c r="BR12" s="1" t="s">
-        <v>1304</v>
-      </c>
-    </row>
-    <row r="13" spans="1:70">
+      <c r="BS12" s="1" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="13" spans="1:71">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -7569,17 +7632,20 @@
       <c r="BO13" s="11" t="s">
         <v>1207</v>
       </c>
-      <c r="BP13" s="11">
+      <c r="BP13" s="11" t="s">
+        <v>1340</v>
+      </c>
+      <c r="BQ13" s="11">
         <v>2.13</v>
       </c>
-      <c r="BQ13" s="11">
+      <c r="BR13" s="11">
         <v>25</v>
       </c>
-      <c r="BR13" s="1" t="s">
-        <v>1304</v>
-      </c>
-    </row>
-    <row r="14" spans="1:70">
+      <c r="BS13" s="1" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="14" spans="1:71">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -7781,17 +7847,20 @@
       <c r="BO14" s="11" t="s">
         <v>1207</v>
       </c>
-      <c r="BP14" s="11">
+      <c r="BP14" s="11" t="s">
+        <v>1340</v>
+      </c>
+      <c r="BQ14" s="11">
         <v>2.13</v>
       </c>
-      <c r="BQ14" s="11">
+      <c r="BR14" s="11">
         <v>25</v>
       </c>
-      <c r="BR14" s="1" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="15" spans="1:70">
+      <c r="BS14" s="1" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="15" spans="1:71">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -7993,17 +8062,20 @@
       <c r="BO15" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP15" s="11">
+      <c r="BP15" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ15" s="11">
         <v>2.7777777777777701</v>
       </c>
-      <c r="BQ15" s="11">
+      <c r="BR15" s="11">
         <v>23</v>
       </c>
-      <c r="BR15" s="1" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="16" spans="1:70">
+      <c r="BS15" s="1" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="16" spans="1:71">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -8205,17 +8277,20 @@
       <c r="BO16" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP16" s="11">
+      <c r="BP16" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ16" s="11">
         <v>2.7777777777777701</v>
       </c>
-      <c r="BQ16" s="11">
+      <c r="BR16" s="11">
         <v>23</v>
       </c>
-      <c r="BR16" s="1" t="s">
-        <v>1308</v>
-      </c>
-    </row>
-    <row r="17" spans="1:70">
+      <c r="BS16" s="1" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="17" spans="1:71">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -8417,17 +8492,20 @@
       <c r="BO17" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP17">
+      <c r="BP17" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ17">
         <v>10.616666666666667</v>
       </c>
-      <c r="BQ17" s="11">
+      <c r="BR17" s="11">
         <v>-0.23428571428571424</v>
       </c>
-      <c r="BR17" s="1" t="s">
+      <c r="BS17" s="1" t="s">
         <v>956</v>
       </c>
     </row>
-    <row r="18" spans="1:70">
+    <row r="18" spans="1:71">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -8629,17 +8707,20 @@
       <c r="BO18" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP18">
+      <c r="BP18" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ18">
         <v>10.616666666666667</v>
       </c>
-      <c r="BQ18" s="11">
+      <c r="BR18" s="11">
         <v>-0.23428571428571424</v>
       </c>
-      <c r="BR18" s="1" t="s">
+      <c r="BS18" s="1" t="s">
         <v>957</v>
       </c>
     </row>
-    <row r="19" spans="1:70">
+    <row r="19" spans="1:71">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -8841,17 +8922,20 @@
       <c r="BO19" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP19" s="11">
+      <c r="BP19" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ19" s="11">
         <v>1.0699999999999998</v>
       </c>
-      <c r="BQ19" s="11">
+      <c r="BR19" s="11">
         <v>18</v>
       </c>
-      <c r="BR19" s="11" t="s">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="20" spans="1:70">
+      <c r="BS19" s="11" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="20" spans="1:71">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -8967,7 +9051,7 @@
         <v>1134</v>
       </c>
       <c r="AM20" s="1" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="AN20" s="1" t="s">
         <v>314</v>
@@ -9053,17 +9137,20 @@
       <c r="BO20" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP20" s="11">
+      <c r="BP20" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ20" s="11">
         <v>1.0699999999999998</v>
       </c>
-      <c r="BQ20" s="11">
+      <c r="BR20" s="11">
         <v>18</v>
       </c>
-      <c r="BR20" s="11" t="s">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="21" spans="1:70">
+      <c r="BS20" s="11" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="21" spans="1:71">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -9182,7 +9269,7 @@
         <v>317</v>
       </c>
       <c r="AN21" s="1" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="AO21">
         <v>8.9999999999999993E-3</v>
@@ -9265,17 +9352,20 @@
       <c r="BO21" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP21" s="11">
+      <c r="BP21" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ21" s="11">
         <v>1.0699999999999998</v>
       </c>
-      <c r="BQ21" s="11">
+      <c r="BR21" s="11">
         <v>18</v>
       </c>
-      <c r="BR21" s="11" t="s">
-        <v>1302</v>
-      </c>
-    </row>
-    <row r="22" spans="1:70">
+      <c r="BS21" s="11" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="22" spans="1:71">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -9477,17 +9567,20 @@
       <c r="BO22" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP22" s="11">
+      <c r="BP22" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ22" s="11">
         <v>1.0699999999999998</v>
       </c>
-      <c r="BQ22" s="11">
+      <c r="BR22" s="11">
         <v>18</v>
       </c>
-      <c r="BR22" s="11" t="s">
-        <v>1303</v>
-      </c>
-    </row>
-    <row r="23" spans="1:70">
+      <c r="BS22" s="11" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="23" spans="1:71">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -9689,17 +9782,20 @@
       <c r="BO23" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP23" s="11">
+      <c r="BP23" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ23" s="11">
         <v>1.0699999999999998</v>
       </c>
-      <c r="BQ23" s="11">
+      <c r="BR23" s="11">
         <v>18</v>
       </c>
-      <c r="BR23" s="11" t="s">
-        <v>1302</v>
-      </c>
-    </row>
-    <row r="24" spans="1:70">
+      <c r="BS23" s="11" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="24" spans="1:71">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -9901,17 +9997,20 @@
       <c r="BO24" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="BP24" s="11">
+      <c r="BP24" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="BQ24" s="11">
         <v>2.13</v>
       </c>
-      <c r="BQ24" s="11">
+      <c r="BR24" s="11">
         <v>25</v>
       </c>
-      <c r="BR24" s="1" t="s">
-        <v>1306</v>
-      </c>
-    </row>
-    <row r="25" spans="1:70">
+      <c r="BS24" s="1" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="25" spans="1:71">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -10113,17 +10212,20 @@
       <c r="BO25" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="BP25" s="11">
+      <c r="BP25" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="BQ25" s="11">
         <v>2.13</v>
       </c>
-      <c r="BQ25" s="11">
+      <c r="BR25" s="11">
         <v>25</v>
       </c>
-      <c r="BR25" s="1" t="s">
-        <v>1306</v>
-      </c>
-    </row>
-    <row r="26" spans="1:70">
+      <c r="BS25" s="1" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="26" spans="1:71">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -10325,17 +10427,20 @@
       <c r="BO26" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="BP26" s="11">
+      <c r="BP26" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="BQ26" s="11">
         <v>2.13</v>
       </c>
-      <c r="BQ26" s="11">
+      <c r="BR26" s="11">
         <v>25</v>
       </c>
-      <c r="BR26" s="1" t="s">
-        <v>1306</v>
-      </c>
-    </row>
-    <row r="27" spans="1:70">
+      <c r="BS26" s="1" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="27" spans="1:71">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -10537,17 +10642,20 @@
       <c r="BO27" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP27" s="11">
+      <c r="BP27" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ27" s="11">
         <v>3</v>
       </c>
-      <c r="BQ27" s="11">
+      <c r="BR27" s="11">
         <v>19.458930899999999</v>
       </c>
-      <c r="BR27" s="1" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="28" spans="1:70">
+      <c r="BS27" s="1" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="28" spans="1:71">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -10749,17 +10857,20 @@
       <c r="BO28" s="11" t="s">
         <v>1207</v>
       </c>
-      <c r="BP28" s="11">
+      <c r="BP28" s="11" t="s">
+        <v>1341</v>
+      </c>
+      <c r="BQ28" s="11">
         <v>1.4</v>
       </c>
-      <c r="BQ28">
+      <c r="BR28">
         <v>25.725274725274684</v>
       </c>
-      <c r="BR28" s="1" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="29" spans="1:70">
+      <c r="BS28" s="1" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="29" spans="1:71">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -10961,17 +11072,20 @@
       <c r="BO29" s="11" t="s">
         <v>1207</v>
       </c>
-      <c r="BP29" s="11">
+      <c r="BP29" s="11" t="s">
+        <v>1341</v>
+      </c>
+      <c r="BQ29" s="11">
         <v>1.4</v>
       </c>
-      <c r="BQ29">
+      <c r="BR29">
         <v>25.725274725274684</v>
       </c>
-      <c r="BR29" s="1" t="s">
+      <c r="BS29" s="1" t="s">
         <v>1141</v>
       </c>
     </row>
-    <row r="30" spans="1:70">
+    <row r="30" spans="1:71">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -11173,17 +11287,20 @@
       <c r="BO30" s="11" t="s">
         <v>1207</v>
       </c>
-      <c r="BP30" s="11">
+      <c r="BP30" s="11" t="s">
+        <v>1341</v>
+      </c>
+      <c r="BQ30" s="11">
         <v>1.4</v>
       </c>
-      <c r="BQ30">
+      <c r="BR30">
         <v>25.725274725274684</v>
       </c>
-      <c r="BR30" s="1" t="s">
+      <c r="BS30" s="1" t="s">
         <v>1142</v>
       </c>
     </row>
-    <row r="31" spans="1:70">
+    <row r="31" spans="1:71">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -11385,17 +11502,20 @@
       <c r="BO31" s="11" t="s">
         <v>1207</v>
       </c>
-      <c r="BP31" s="11">
+      <c r="BP31" s="11" t="s">
+        <v>1341</v>
+      </c>
+      <c r="BQ31" s="11">
         <v>1.4</v>
       </c>
-      <c r="BQ31">
+      <c r="BR31">
         <v>25.725274725274684</v>
       </c>
-      <c r="BR31" s="1" t="s">
+      <c r="BS31" s="1" t="s">
         <v>1143</v>
       </c>
     </row>
-    <row r="32" spans="1:70">
+    <row r="32" spans="1:71">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -11597,17 +11717,20 @@
       <c r="BO32" s="11" t="s">
         <v>1207</v>
       </c>
-      <c r="BP32" s="11">
+      <c r="BP32" s="11" t="s">
+        <v>1341</v>
+      </c>
+      <c r="BQ32" s="11">
         <v>1.4</v>
       </c>
-      <c r="BQ32">
+      <c r="BR32">
         <v>25.725274725274684</v>
       </c>
-      <c r="BR32" s="1" t="s">
+      <c r="BS32" s="1" t="s">
         <v>1140</v>
       </c>
     </row>
-    <row r="33" spans="1:70">
+    <row r="33" spans="1:71">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -11809,17 +11932,20 @@
       <c r="BO33" s="11" t="s">
         <v>1207</v>
       </c>
-      <c r="BP33" s="11">
+      <c r="BP33" s="11" t="s">
+        <v>1341</v>
+      </c>
+      <c r="BQ33" s="11">
         <v>1.4</v>
       </c>
-      <c r="BQ33">
+      <c r="BR33">
         <v>25.725274725274684</v>
       </c>
-      <c r="BR33" s="1" t="s">
+      <c r="BS33" s="1" t="s">
         <v>1139</v>
       </c>
     </row>
-    <row r="34" spans="1:70">
+    <row r="34" spans="1:71">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -12021,17 +12147,20 @@
       <c r="BO34" s="11" t="s">
         <v>1207</v>
       </c>
-      <c r="BP34" s="11">
+      <c r="BP34" s="11" t="s">
+        <v>1341</v>
+      </c>
+      <c r="BQ34" s="11">
         <v>1.4</v>
       </c>
-      <c r="BQ34">
+      <c r="BR34">
         <v>25.725274725274684</v>
       </c>
-      <c r="BR34" s="1" t="s">
+      <c r="BS34" s="1" t="s">
         <v>1144</v>
       </c>
     </row>
-    <row r="35" spans="1:70">
+    <row r="35" spans="1:71">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -12233,17 +12362,20 @@
       <c r="BO35" s="11" t="s">
         <v>1207</v>
       </c>
-      <c r="BP35" s="11">
+      <c r="BP35" s="11" t="s">
+        <v>1341</v>
+      </c>
+      <c r="BQ35" s="11">
         <v>1.4</v>
       </c>
-      <c r="BQ35">
+      <c r="BR35">
         <v>25.725274725274684</v>
       </c>
-      <c r="BR35" s="1" t="s">
+      <c r="BS35" s="1" t="s">
         <v>1145</v>
       </c>
     </row>
-    <row r="36" spans="1:70">
+    <row r="36" spans="1:71">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -12445,17 +12577,20 @@
       <c r="BO36" s="11" t="s">
         <v>819</v>
       </c>
-      <c r="BP36" s="11">
+      <c r="BP36" s="11" t="s">
+        <v>1349</v>
+      </c>
+      <c r="BQ36" s="11">
         <v>2.13</v>
       </c>
-      <c r="BQ36">
+      <c r="BR36">
         <v>27.2</v>
       </c>
-      <c r="BR36" s="1" t="s">
-        <v>1312</v>
-      </c>
-    </row>
-    <row r="37" spans="1:70">
+      <c r="BS36" s="1" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="37" spans="1:71">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -12657,17 +12792,20 @@
       <c r="BO37" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP37">
+      <c r="BP37" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ37">
         <v>6.3507812955294964</v>
       </c>
-      <c r="BQ37" s="11">
+      <c r="BR37" s="11">
         <v>26</v>
       </c>
-      <c r="BR37" s="1" t="s">
-        <v>1313</v>
-      </c>
-    </row>
-    <row r="38" spans="1:70">
+      <c r="BS37" s="1" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="38" spans="1:71">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -12869,17 +13007,20 @@
       <c r="BO38" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP38">
+      <c r="BP38" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ38">
         <v>8.6337418919616322</v>
       </c>
-      <c r="BQ38" s="11">
+      <c r="BR38" s="11">
         <v>26</v>
       </c>
-      <c r="BR38" s="1" t="s">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="39" spans="1:70">
+      <c r="BS38" s="1" t="s">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="39" spans="1:71">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -13081,17 +13222,20 @@
       <c r="BO39" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP39">
+      <c r="BP39" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ39">
         <v>7.5545241554664546</v>
       </c>
-      <c r="BQ39" s="11">
+      <c r="BR39" s="11">
         <v>26</v>
       </c>
-      <c r="BR39" s="1" t="s">
-        <v>1315</v>
-      </c>
-    </row>
-    <row r="40" spans="1:70">
+      <c r="BS39" s="1" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="40" spans="1:71">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -13293,17 +13437,20 @@
       <c r="BO40" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP40">
+      <c r="BP40" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ40">
         <v>9.9620098753403727</v>
       </c>
-      <c r="BQ40" s="11">
+      <c r="BR40" s="11">
         <v>26</v>
       </c>
-      <c r="BR40" s="1" t="s">
-        <v>1316</v>
-      </c>
-    </row>
-    <row r="41" spans="1:70">
+      <c r="BS40" s="1" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="41" spans="1:71">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -13505,17 +13652,20 @@
       <c r="BO41" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP41">
+      <c r="BP41" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ41">
         <v>7.4715074065052436</v>
       </c>
-      <c r="BQ41" s="11">
+      <c r="BR41" s="11">
         <v>26</v>
       </c>
-      <c r="BR41" s="1" t="s">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="42" spans="1:70">
+      <c r="BS41" s="1" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="42" spans="1:71">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -13717,17 +13867,20 @@
       <c r="BO42" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP42">
+      <c r="BP42" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ42">
         <v>7.6375409044275955</v>
       </c>
-      <c r="BQ42" s="11">
+      <c r="BR42" s="11">
         <v>26</v>
       </c>
-      <c r="BR42" s="1" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="43" spans="1:70">
+      <c r="BS42" s="1" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="43" spans="1:71">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -13929,17 +14082,20 @@
       <c r="BO43" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="BP43" s="1">
+      <c r="BP43" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="BQ43" s="1">
         <v>0.20198875962343635</v>
       </c>
-      <c r="BQ43" s="11">
+      <c r="BR43" s="11">
         <v>28.65</v>
       </c>
-      <c r="BR43" s="1" t="s">
-        <v>1324</v>
-      </c>
-    </row>
-    <row r="44" spans="1:70">
+      <c r="BS43" s="1" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="44" spans="1:71">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -14085,10 +14241,10 @@
         <v>5</v>
       </c>
       <c r="AW44" s="1">
-        <v>9</v>
+        <v>0.9</v>
       </c>
       <c r="AX44" s="1">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="AY44" s="1">
         <v>0</v>
@@ -14097,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="BA44" s="1">
-        <v>0.7</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="BB44" s="1">
-        <v>0.3</v>
+        <v>0.03</v>
       </c>
       <c r="BC44" s="1">
         <v>0</v>
@@ -14114,44 +14270,47 @@
       <c r="BF44" s="1">
         <v>5</v>
       </c>
-      <c r="BG44" s="1">
-        <v>0</v>
-      </c>
-      <c r="BH44" s="1">
-        <v>0</v>
-      </c>
-      <c r="BI44" s="1">
-        <v>0</v>
-      </c>
-      <c r="BJ44" s="1">
-        <v>0</v>
-      </c>
-      <c r="BK44" s="1">
-        <v>15.4</v>
-      </c>
-      <c r="BL44" s="1">
-        <v>0.9</v>
-      </c>
-      <c r="BM44" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN44" s="1">
-        <v>0</v>
+      <c r="BG44" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BH44" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BI44" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BJ44" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BK44" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BL44" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BM44" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BN44" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="BO44" s="11" t="s">
-        <v>819</v>
+        <v>1206</v>
       </c>
       <c r="BP44" s="11" t="s">
-        <v>314</v>
-      </c>
-      <c r="BQ44" s="11">
+        <v>1343</v>
+      </c>
+      <c r="BQ44" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="BR44" s="11">
         <v>17</v>
       </c>
-      <c r="BR44" s="1" t="s">
-        <v>1320</v>
-      </c>
-    </row>
-    <row r="45" spans="1:70">
+      <c r="BS44" s="1" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="45" spans="1:71">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -14353,17 +14512,20 @@
       <c r="BO45" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="BP45" s="11">
+      <c r="BP45" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="BQ45" s="11">
         <v>2.02</v>
       </c>
-      <c r="BQ45">
+      <c r="BR45">
         <v>27.94</v>
       </c>
-      <c r="BR45" s="1" t="s">
-        <v>1321</v>
-      </c>
-    </row>
-    <row r="46" spans="1:70">
+      <c r="BS45" s="1" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="46" spans="1:71">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -14565,17 +14727,20 @@
       <c r="BO46" s="11" t="s">
         <v>1207</v>
       </c>
-      <c r="BP46" s="11">
+      <c r="BP46" s="11" t="s">
+        <v>1340</v>
+      </c>
+      <c r="BQ46" s="11">
         <v>2.13</v>
       </c>
-      <c r="BQ46" s="1">
+      <c r="BR46" s="1">
         <v>25</v>
       </c>
-      <c r="BR46" s="1" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="47" spans="1:70">
+      <c r="BS46" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="47" spans="1:71">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -14777,17 +14942,20 @@
       <c r="BO47" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP47" s="1">
+      <c r="BP47" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ47" s="1">
         <v>0.16129032258064363</v>
       </c>
-      <c r="BQ47" s="11">
+      <c r="BR47" s="11">
         <v>26.17</v>
       </c>
-      <c r="BR47" s="1" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="48" spans="1:70">
+      <c r="BS47" s="1" t="s">
+        <v>1316</v>
+      </c>
+    </row>
+    <row r="48" spans="1:71">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -14989,17 +15157,20 @@
       <c r="BO48" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP48" s="1">
+      <c r="BP48" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ48" s="1">
         <v>0.16129032258064363</v>
       </c>
-      <c r="BQ48" s="11">
+      <c r="BR48" s="11">
         <v>26.17</v>
       </c>
-      <c r="BR48" s="1" t="s">
+      <c r="BS48" s="1" t="s">
         <v>1022</v>
       </c>
     </row>
-    <row r="49" spans="1:70">
+    <row r="49" spans="1:71">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -15201,17 +15372,20 @@
       <c r="BO49" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP49" s="1">
+      <c r="BP49" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ49" s="1">
         <v>0.16129032258064363</v>
       </c>
-      <c r="BQ49" s="11">
+      <c r="BR49" s="11">
         <v>26.17</v>
       </c>
-      <c r="BR49" s="1" t="s">
+      <c r="BS49" s="1" t="s">
         <v>1023</v>
       </c>
     </row>
-    <row r="50" spans="1:70">
+    <row r="50" spans="1:71">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -15413,17 +15587,20 @@
       <c r="BO50" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP50" s="1">
+      <c r="BP50" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ50" s="1">
         <v>0.16129032258064363</v>
       </c>
-      <c r="BQ50" s="11">
+      <c r="BR50" s="11">
         <v>26.17</v>
       </c>
-      <c r="BR50" s="1" t="s">
+      <c r="BS50" s="1" t="s">
         <v>1024</v>
       </c>
     </row>
-    <row r="51" spans="1:70">
+    <row r="51" spans="1:71">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -15625,17 +15802,20 @@
       <c r="BO51" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP51" s="1">
+      <c r="BP51" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ51" s="1">
         <v>0.16129032258064363</v>
       </c>
-      <c r="BQ51" s="11">
+      <c r="BR51" s="11">
         <v>26.17</v>
       </c>
-      <c r="BR51" s="1" t="s">
+      <c r="BS51" s="1" t="s">
         <v>1025</v>
       </c>
     </row>
-    <row r="52" spans="1:70">
+    <row r="52" spans="1:71">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -15837,17 +16017,20 @@
       <c r="BO52" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP52" s="1">
+      <c r="BP52" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ52" s="1">
         <v>0.16129032258064363</v>
       </c>
-      <c r="BQ52" s="11">
+      <c r="BR52" s="11">
         <v>26.17</v>
       </c>
-      <c r="BR52" s="1" t="s">
+      <c r="BS52" s="1" t="s">
         <v>1026</v>
       </c>
     </row>
-    <row r="53" spans="1:70">
+    <row r="53" spans="1:71">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -16049,17 +16232,20 @@
       <c r="BO53" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP53" s="1">
+      <c r="BP53" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ53" s="1">
         <v>0.16129032258064363</v>
       </c>
-      <c r="BQ53" s="11">
+      <c r="BR53" s="11">
         <v>26.17</v>
       </c>
-      <c r="BR53" s="1" t="s">
+      <c r="BS53" s="1" t="s">
         <v>1027</v>
       </c>
     </row>
-    <row r="54" spans="1:70">
+    <row r="54" spans="1:71">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -16261,17 +16447,20 @@
       <c r="BO54" s="1" t="s">
         <v>1206</v>
       </c>
-      <c r="BP54" s="11">
+      <c r="BP54" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ54" s="11">
         <v>0.15053763440860024</v>
       </c>
-      <c r="BQ54" s="11">
+      <c r="BR54" s="11">
         <v>26.17</v>
       </c>
-      <c r="BR54" s="1" t="s">
+      <c r="BS54" s="1" t="s">
         <v>1009</v>
       </c>
     </row>
-    <row r="55" spans="1:70">
+    <row r="55" spans="1:71">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -16473,17 +16662,20 @@
       <c r="BO55" s="1" t="s">
         <v>1206</v>
       </c>
-      <c r="BP55" s="11">
+      <c r="BP55" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ55" s="11">
         <v>0.17204301075268699</v>
       </c>
-      <c r="BQ55" s="11">
+      <c r="BR55" s="11">
         <v>26.17</v>
       </c>
-      <c r="BR55" s="1" t="s">
+      <c r="BS55" s="1" t="s">
         <v>1011</v>
       </c>
     </row>
-    <row r="56" spans="1:70">
+    <row r="56" spans="1:71">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -16685,17 +16877,20 @@
       <c r="BO56" s="1" t="s">
         <v>1206</v>
       </c>
-      <c r="BP56" s="11">
+      <c r="BP56" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ56" s="11">
         <v>6.5217391304347394E-2</v>
       </c>
-      <c r="BQ56" s="11">
+      <c r="BR56" s="11">
         <v>26.17</v>
       </c>
-      <c r="BR56" s="1" t="s">
+      <c r="BS56" s="1" t="s">
         <v>1013</v>
       </c>
     </row>
-    <row r="57" spans="1:70">
+    <row r="57" spans="1:71">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -16897,17 +17092,20 @@
       <c r="BO57" s="1" t="s">
         <v>1206</v>
       </c>
-      <c r="BP57" s="11">
+      <c r="BP57" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ57" s="11">
         <v>0.47826086956521702</v>
       </c>
-      <c r="BQ57" s="11">
+      <c r="BR57" s="11">
         <v>26.17</v>
       </c>
-      <c r="BR57" s="1" t="s">
+      <c r="BS57" s="1" t="s">
         <v>1015</v>
       </c>
     </row>
-    <row r="58" spans="1:70">
+    <row r="58" spans="1:71">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -17109,17 +17307,20 @@
       <c r="BO58" s="1" t="s">
         <v>1206</v>
       </c>
-      <c r="BP58" s="11">
+      <c r="BP58" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ58" s="11">
         <v>0.14388489208633001</v>
       </c>
-      <c r="BQ58" s="11">
+      <c r="BR58" s="11">
         <v>26.17</v>
       </c>
-      <c r="BR58" s="1" t="s">
+      <c r="BS58" s="1" t="s">
         <v>1017</v>
       </c>
     </row>
-    <row r="59" spans="1:70">
+    <row r="59" spans="1:71">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -17321,17 +17522,20 @@
       <c r="BO59" s="1" t="s">
         <v>1206</v>
       </c>
-      <c r="BP59" s="11">
+      <c r="BP59" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ59" s="11">
         <v>0.15053763440860024</v>
       </c>
-      <c r="BQ59" s="11">
+      <c r="BR59" s="11">
         <v>26.17</v>
       </c>
-      <c r="BR59" s="1" t="s">
+      <c r="BS59" s="1" t="s">
         <v>1010</v>
       </c>
     </row>
-    <row r="60" spans="1:70">
+    <row r="60" spans="1:71">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -17533,17 +17737,20 @@
       <c r="BO60" s="1" t="s">
         <v>1206</v>
       </c>
-      <c r="BP60" s="11">
+      <c r="BP60" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ60" s="11">
         <v>0.17204301075268699</v>
       </c>
-      <c r="BQ60" s="11">
+      <c r="BR60" s="11">
         <v>26.17</v>
       </c>
-      <c r="BR60" s="1" t="s">
+      <c r="BS60" s="1" t="s">
         <v>1012</v>
       </c>
     </row>
-    <row r="61" spans="1:70">
+    <row r="61" spans="1:71">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -17745,17 +17952,20 @@
       <c r="BO61" s="1" t="s">
         <v>1206</v>
       </c>
-      <c r="BP61" s="11">
+      <c r="BP61" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ61" s="11">
         <v>6.5217391304347394E-2</v>
       </c>
-      <c r="BQ61" s="11">
+      <c r="BR61" s="11">
         <v>26.17</v>
       </c>
-      <c r="BR61" s="1" t="s">
+      <c r="BS61" s="1" t="s">
         <v>1014</v>
       </c>
     </row>
-    <row r="62" spans="1:70">
+    <row r="62" spans="1:71">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -17957,17 +18167,20 @@
       <c r="BO62" s="1" t="s">
         <v>1206</v>
       </c>
-      <c r="BP62" s="11">
+      <c r="BP62" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ62" s="11">
         <v>0.47826086956521702</v>
       </c>
-      <c r="BQ62" s="11">
+      <c r="BR62" s="11">
         <v>26.17</v>
       </c>
-      <c r="BR62" s="1" t="s">
+      <c r="BS62" s="1" t="s">
         <v>1016</v>
       </c>
     </row>
-    <row r="63" spans="1:70">
+    <row r="63" spans="1:71">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -18169,17 +18382,20 @@
       <c r="BO63" s="1" t="s">
         <v>1206</v>
       </c>
-      <c r="BP63" s="11">
+      <c r="BP63" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ63" s="11">
         <v>0.14388489208633001</v>
       </c>
-      <c r="BQ63" s="11">
+      <c r="BR63" s="11">
         <v>26.17</v>
       </c>
-      <c r="BR63" s="1" t="s">
+      <c r="BS63" s="1" t="s">
         <v>1018</v>
       </c>
     </row>
-    <row r="64" spans="1:70">
+    <row r="64" spans="1:71">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -18327,8 +18543,8 @@
       <c r="AW64" s="11">
         <v>0.98</v>
       </c>
-      <c r="AX64" s="11">
-        <v>0.18</v>
+      <c r="AX64" s="11" t="s">
+        <v>314</v>
       </c>
       <c r="AY64" s="11">
         <v>0</v>
@@ -18381,17 +18597,20 @@
       <c r="BO64" s="1" t="s">
         <v>1207</v>
       </c>
-      <c r="BP64" s="11">
+      <c r="BP64" s="1" t="s">
+        <v>1348</v>
+      </c>
+      <c r="BQ64" s="11">
         <v>0.43</v>
       </c>
-      <c r="BQ64" s="11">
+      <c r="BR64" s="11">
         <v>27</v>
       </c>
-      <c r="BR64" s="1" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="65" spans="1:70">
+      <c r="BS64" s="1" t="s">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="65" spans="1:71">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -18593,17 +18812,20 @@
       <c r="BO65" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP65" s="11">
+      <c r="BP65" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ65" s="11">
         <v>0.92648599819331412</v>
       </c>
-      <c r="BQ65" s="11">
+      <c r="BR65" s="11">
         <v>27.8</v>
       </c>
-      <c r="BR65" s="1" t="s">
+      <c r="BS65" s="1" t="s">
         <v>1208</v>
       </c>
     </row>
-    <row r="66" spans="1:70">
+    <row r="66" spans="1:71">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -18805,17 +19027,20 @@
       <c r="BO66" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP66" s="11">
+      <c r="BP66" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ66" s="11">
         <v>0.79214092140921299</v>
       </c>
-      <c r="BQ66" s="11">
+      <c r="BR66" s="11">
         <v>27.8</v>
       </c>
-      <c r="BR66" s="1" t="s">
+      <c r="BS66" s="1" t="s">
         <v>1209</v>
       </c>
     </row>
-    <row r="67" spans="1:70">
+    <row r="67" spans="1:71">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -19017,17 +19242,20 @@
       <c r="BO67" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP67" s="11">
+      <c r="BP67" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ67" s="11">
         <v>0.90614272809394603</v>
       </c>
-      <c r="BQ67" s="11">
+      <c r="BR67" s="11">
         <v>27.8</v>
       </c>
-      <c r="BR67" s="1" t="s">
+      <c r="BS67" s="1" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="68" spans="1:70">
+    <row r="68" spans="1:71">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -19229,17 +19457,20 @@
       <c r="BO68" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP68" s="11">
+      <c r="BP68" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ68" s="11">
         <v>1.2923215898825648</v>
       </c>
-      <c r="BQ68" s="11">
+      <c r="BR68" s="11">
         <v>27.8</v>
       </c>
-      <c r="BR68" s="1" t="s">
+      <c r="BS68" s="1" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="69" spans="1:70">
+    <row r="69" spans="1:71">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -19441,17 +19672,20 @@
       <c r="BO69" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP69" s="11">
+      <c r="BP69" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ69" s="11">
         <v>0.54272809394760502</v>
       </c>
-      <c r="BQ69" s="11">
+      <c r="BR69" s="11">
         <v>27.8</v>
       </c>
-      <c r="BR69" s="1" t="s">
+      <c r="BS69" s="1" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="70" spans="1:70">
+    <row r="70" spans="1:71">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -19653,17 +19887,20 @@
       <c r="BO70" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP70" s="11">
+      <c r="BP70" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ70" s="11">
         <v>1.0990966576332419</v>
       </c>
-      <c r="BQ70" s="11">
+      <c r="BR70" s="11">
         <v>27.8</v>
       </c>
-      <c r="BR70" s="1" t="s">
+      <c r="BS70" s="1" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="71" spans="1:70">
+    <row r="71" spans="1:71">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -19865,17 +20102,20 @@
       <c r="BO71" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP71" s="11">
+      <c r="BP71" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ71" s="11">
         <v>14.34291139240506</v>
       </c>
-      <c r="BQ71" s="11">
+      <c r="BR71" s="11">
         <v>12</v>
       </c>
-      <c r="BR71" s="1" t="s">
+      <c r="BS71" s="1" t="s">
         <v>1218</v>
       </c>
     </row>
-    <row r="72" spans="1:70">
+    <row r="72" spans="1:71">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -20077,17 +20317,20 @@
       <c r="BO72" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP72" s="11">
+      <c r="BP72" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ72" s="11">
         <v>14.34291139240506</v>
       </c>
-      <c r="BQ72" s="11">
+      <c r="BR72" s="11">
         <v>12</v>
       </c>
-      <c r="BR72" s="1" t="s">
+      <c r="BS72" s="1" t="s">
         <v>1162</v>
       </c>
     </row>
-    <row r="73" spans="1:70">
+    <row r="73" spans="1:71">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -20289,17 +20532,20 @@
       <c r="BO73" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP73" s="11">
+      <c r="BP73" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ73" s="11">
         <v>14.34291139240506</v>
       </c>
-      <c r="BQ73" s="11">
+      <c r="BR73" s="11">
         <v>12</v>
       </c>
-      <c r="BR73" s="1" t="s">
+      <c r="BS73" s="1" t="s">
         <v>1162</v>
       </c>
     </row>
-    <row r="74" spans="1:70">
+    <row r="74" spans="1:71">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -20501,17 +20747,20 @@
       <c r="BO74" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP74" s="11">
+      <c r="BP74" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ74" s="11">
         <v>14.34291139240506</v>
       </c>
-      <c r="BQ74" s="11">
+      <c r="BR74" s="11">
         <v>12</v>
       </c>
-      <c r="BR74" s="1" t="s">
+      <c r="BS74" s="1" t="s">
         <v>1162</v>
       </c>
     </row>
-    <row r="75" spans="1:70">
+    <row r="75" spans="1:71">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -20713,17 +20962,20 @@
       <c r="BO75" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP75" s="11">
+      <c r="BP75" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ75" s="11">
         <v>14.34291139240506</v>
       </c>
-      <c r="BQ75" s="11">
+      <c r="BR75" s="11">
         <v>12</v>
       </c>
-      <c r="BR75" s="1" t="s">
+      <c r="BS75" s="1" t="s">
         <v>1214</v>
       </c>
     </row>
-    <row r="76" spans="1:70">
+    <row r="76" spans="1:71">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -20925,17 +21177,20 @@
       <c r="BO76" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP76" s="11">
+      <c r="BP76" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ76" s="11">
         <v>14.34291139240506</v>
       </c>
-      <c r="BQ76" s="11">
+      <c r="BR76" s="11">
         <v>12</v>
       </c>
-      <c r="BR76" s="1" t="s">
+      <c r="BS76" s="1" t="s">
         <v>1163</v>
       </c>
     </row>
-    <row r="77" spans="1:70">
+    <row r="77" spans="1:71">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -21137,17 +21392,20 @@
       <c r="BO77" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP77" s="11">
+      <c r="BP77" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ77" s="11">
         <v>14.34291139240506</v>
       </c>
-      <c r="BQ77" s="11">
+      <c r="BR77" s="11">
         <v>12</v>
       </c>
-      <c r="BR77" s="1" t="s">
+      <c r="BS77" s="1" t="s">
         <v>1215</v>
       </c>
     </row>
-    <row r="78" spans="1:70">
+    <row r="78" spans="1:71">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -21349,17 +21607,20 @@
       <c r="BO78" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP78" s="11">
+      <c r="BP78" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ78" s="11">
         <v>23</v>
       </c>
-      <c r="BQ78" s="11">
+      <c r="BR78" s="11">
         <v>15</v>
       </c>
-      <c r="BR78" s="1" t="s">
+      <c r="BS78" s="1" t="s">
         <v>1219</v>
       </c>
     </row>
-    <row r="79" spans="1:70">
+    <row r="79" spans="1:71">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -21561,17 +21822,20 @@
       <c r="BO79" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP79" s="11">
+      <c r="BP79" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ79" s="11">
         <v>23</v>
       </c>
-      <c r="BQ79" s="11">
+      <c r="BR79" s="11">
         <v>15</v>
       </c>
-      <c r="BR79" s="1" t="s">
+      <c r="BS79" s="1" t="s">
         <v>1219</v>
       </c>
     </row>
-    <row r="80" spans="1:70">
+    <row r="80" spans="1:71">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -21773,17 +22037,20 @@
       <c r="BO80" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP80" s="11">
+      <c r="BP80" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ80" s="11">
         <v>23</v>
       </c>
-      <c r="BQ80" s="11">
+      <c r="BR80" s="11">
         <v>15</v>
       </c>
-      <c r="BR80" s="1" t="s">
+      <c r="BS80" s="1" t="s">
         <v>1219</v>
       </c>
     </row>
-    <row r="81" spans="1:70">
+    <row r="81" spans="1:71">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -21935,7 +22202,7 @@
         <v>314</v>
       </c>
       <c r="AY81" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ81" s="1" t="s">
         <v>314</v>
@@ -21985,17 +22252,20 @@
       <c r="BO81" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP81" s="11">
+      <c r="BP81" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ81" s="11">
         <v>23</v>
       </c>
-      <c r="BQ81" s="11">
+      <c r="BR81" s="11">
         <v>15</v>
       </c>
-      <c r="BR81" s="1" t="s">
+      <c r="BS81" s="1" t="s">
         <v>1220</v>
       </c>
     </row>
-    <row r="82" spans="1:70">
+    <row r="82" spans="1:71">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -22147,7 +22417,7 @@
         <v>314</v>
       </c>
       <c r="AY82" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ82" s="1" t="s">
         <v>314</v>
@@ -22197,17 +22467,20 @@
       <c r="BO82" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP82" s="11">
+      <c r="BP82" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ82" s="11">
         <v>23</v>
       </c>
-      <c r="BQ82" s="11">
+      <c r="BR82" s="11">
         <v>15</v>
       </c>
-      <c r="BR82" s="1" t="s">
+      <c r="BS82" s="1" t="s">
         <v>1221</v>
       </c>
     </row>
-    <row r="83" spans="1:70">
+    <row r="83" spans="1:71">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -22359,7 +22632,7 @@
         <v>314</v>
       </c>
       <c r="AY83" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ83" s="1" t="s">
         <v>314</v>
@@ -22409,17 +22682,20 @@
       <c r="BO83" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP83" s="11">
+      <c r="BP83" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ83" s="11">
         <v>23</v>
       </c>
-      <c r="BQ83" s="11">
+      <c r="BR83" s="11">
         <v>15</v>
       </c>
-      <c r="BR83" s="1" t="s">
+      <c r="BS83" s="1" t="s">
         <v>1222</v>
       </c>
     </row>
-    <row r="84" spans="1:70">
+    <row r="84" spans="1:71">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -22621,17 +22897,20 @@
       <c r="BO84" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP84" s="11">
+      <c r="BP84" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ84" s="11">
         <v>0.43</v>
       </c>
-      <c r="BQ84" s="11">
+      <c r="BR84" s="11">
         <v>27</v>
       </c>
-      <c r="BR84" s="1" t="s">
+      <c r="BS84" s="1" t="s">
         <v>1223</v>
       </c>
     </row>
-    <row r="85" spans="1:70">
+    <row r="85" spans="1:71">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -22833,17 +23112,20 @@
       <c r="BO85" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP85" s="11">
+      <c r="BP85" s="11" t="s">
+        <v>1345</v>
+      </c>
+      <c r="BQ85" s="11">
         <v>11</v>
       </c>
-      <c r="BQ85" s="11">
+      <c r="BR85" s="11">
         <v>15</v>
       </c>
-      <c r="BR85" s="1" t="s">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="86" spans="1:70">
+      <c r="BS85" s="1" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="86" spans="1:71">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -23045,17 +23327,20 @@
       <c r="BO86" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP86" s="11">
+      <c r="BP86" s="11" t="s">
+        <v>1345</v>
+      </c>
+      <c r="BQ86" s="11">
         <v>11</v>
       </c>
-      <c r="BQ86" s="11">
+      <c r="BR86" s="11">
         <v>15</v>
       </c>
-      <c r="BR86" s="1" t="s">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="87" spans="1:70">
+      <c r="BS86" s="1" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="87" spans="1:71">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -23257,17 +23542,20 @@
       <c r="BO87" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP87" s="11">
+      <c r="BP87" s="11" t="s">
+        <v>1345</v>
+      </c>
+      <c r="BQ87" s="11">
         <v>11</v>
       </c>
-      <c r="BQ87" s="11">
+      <c r="BR87" s="11">
         <v>15</v>
       </c>
-      <c r="BR87" s="1" t="s">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="88" spans="1:70">
+      <c r="BS87" s="1" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="88" spans="1:71">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -23469,17 +23757,20 @@
       <c r="BO88" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP88" s="11">
+      <c r="BP88" s="11" t="s">
+        <v>1345</v>
+      </c>
+      <c r="BQ88" s="11">
         <v>11</v>
       </c>
-      <c r="BQ88" s="11">
+      <c r="BR88" s="11">
         <v>15</v>
       </c>
-      <c r="BR88" s="1" t="s">
-        <v>1252</v>
-      </c>
-    </row>
-    <row r="89" spans="1:70">
+      <c r="BS88" s="1" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="89" spans="1:71">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -23681,17 +23972,20 @@
       <c r="BO89" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP89" s="11">
+      <c r="BP89" s="11" t="s">
+        <v>1345</v>
+      </c>
+      <c r="BQ89" s="11">
         <v>11</v>
       </c>
-      <c r="BQ89" s="11">
+      <c r="BR89" s="11">
         <v>15</v>
       </c>
-      <c r="BR89" s="1" t="s">
-        <v>1253</v>
-      </c>
-    </row>
-    <row r="90" spans="1:70">
+      <c r="BS89" s="1" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="90" spans="1:71">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -23893,17 +24187,20 @@
       <c r="BO90" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP90" s="11">
+      <c r="BP90" s="11" t="s">
+        <v>1345</v>
+      </c>
+      <c r="BQ90" s="11">
         <v>11</v>
       </c>
-      <c r="BQ90" s="11">
+      <c r="BR90" s="11">
         <v>15</v>
       </c>
-      <c r="BR90" s="1" t="s">
-        <v>1254</v>
-      </c>
-    </row>
-    <row r="91" spans="1:70">
+      <c r="BS90" s="1" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="91" spans="1:71">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -24105,17 +24402,20 @@
       <c r="BO91" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP91" s="11">
+      <c r="BP91" s="11" t="s">
+        <v>1345</v>
+      </c>
+      <c r="BQ91" s="11">
         <v>11</v>
       </c>
-      <c r="BQ91" s="11">
+      <c r="BR91" s="11">
         <v>15</v>
       </c>
-      <c r="BR91" s="1" t="s">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="92" spans="1:70">
+      <c r="BS91" s="1" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="92" spans="1:71">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -24317,17 +24617,20 @@
       <c r="BO92" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP92" s="11">
+      <c r="BP92" s="11" t="s">
+        <v>1345</v>
+      </c>
+      <c r="BQ92" s="11">
         <v>11</v>
       </c>
-      <c r="BQ92" s="11">
+      <c r="BR92" s="11">
         <v>15</v>
       </c>
-      <c r="BR92" s="1" t="s">
-        <v>1256</v>
-      </c>
-    </row>
-    <row r="93" spans="1:70">
+      <c r="BS92" s="1" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="93" spans="1:71">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -24529,17 +24832,20 @@
       <c r="BO93" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP93" s="11">
+      <c r="BP93" s="11" t="s">
+        <v>1345</v>
+      </c>
+      <c r="BQ93" s="11">
         <v>11</v>
       </c>
-      <c r="BQ93" s="11">
+      <c r="BR93" s="11">
         <v>15</v>
       </c>
-      <c r="BR93" s="1" t="s">
-        <v>1257</v>
-      </c>
-    </row>
-    <row r="94" spans="1:70">
+      <c r="BS93" s="1" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="94" spans="1:71">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -24741,17 +25047,20 @@
       <c r="BO94" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP94" s="11">
+      <c r="BP94" s="11" t="s">
+        <v>1345</v>
+      </c>
+      <c r="BQ94" s="11">
         <v>11</v>
       </c>
-      <c r="BQ94" s="11">
+      <c r="BR94" s="11">
         <v>15</v>
       </c>
-      <c r="BR94" s="1" t="s">
-        <v>1258</v>
-      </c>
-    </row>
-    <row r="95" spans="1:70">
+      <c r="BS94" s="1" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="95" spans="1:71">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -24953,17 +25262,20 @@
       <c r="BO95" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP95" s="11">
+      <c r="BP95" s="11" t="s">
+        <v>1345</v>
+      </c>
+      <c r="BQ95" s="11">
         <v>11</v>
       </c>
-      <c r="BQ95" s="11">
+      <c r="BR95" s="11">
         <v>15</v>
       </c>
-      <c r="BR95" s="1" t="s">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="96" spans="1:70">
+      <c r="BS95" s="1" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="96" spans="1:71">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -25165,17 +25477,20 @@
       <c r="BO96" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP96" s="11">
+      <c r="BP96" s="11" t="s">
+        <v>1345</v>
+      </c>
+      <c r="BQ96" s="11">
         <v>11</v>
       </c>
-      <c r="BQ96" s="11">
+      <c r="BR96" s="11">
         <v>15</v>
       </c>
-      <c r="BR96" s="1" t="s">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="97" spans="1:70">
+      <c r="BS96" s="1" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="97" spans="1:71">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -25377,17 +25692,20 @@
       <c r="BO97" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP97" s="11">
+      <c r="BP97" s="11" t="s">
+        <v>1345</v>
+      </c>
+      <c r="BQ97" s="11">
         <v>11</v>
       </c>
-      <c r="BQ97" s="11">
+      <c r="BR97" s="11">
         <v>15</v>
       </c>
-      <c r="BR97" s="1" t="s">
-        <v>1261</v>
-      </c>
-    </row>
-    <row r="98" spans="1:70">
+      <c r="BS97" s="1" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="98" spans="1:71">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -25589,17 +25907,20 @@
       <c r="BO98" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP98" s="11">
+      <c r="BP98" s="11" t="s">
+        <v>1345</v>
+      </c>
+      <c r="BQ98" s="11">
         <v>11</v>
       </c>
-      <c r="BQ98" s="11">
+      <c r="BR98" s="11">
         <v>15</v>
       </c>
-      <c r="BR98" s="1" t="s">
-        <v>1262</v>
-      </c>
-    </row>
-    <row r="99" spans="1:70">
+      <c r="BS98" s="1" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="99" spans="1:71">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -25801,17 +26122,20 @@
       <c r="BO99" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP99" s="11">
+      <c r="BP99" s="11" t="s">
+        <v>1345</v>
+      </c>
+      <c r="BQ99" s="11">
         <v>11</v>
       </c>
-      <c r="BQ99" s="11">
+      <c r="BR99" s="11">
         <v>15</v>
       </c>
-      <c r="BR99" s="1" t="s">
-        <v>1261</v>
-      </c>
-    </row>
-    <row r="100" spans="1:70">
+      <c r="BS99" s="1" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="100" spans="1:71">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -26013,17 +26337,20 @@
       <c r="BO100" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP100" s="11">
+      <c r="BP100" s="11" t="s">
+        <v>1345</v>
+      </c>
+      <c r="BQ100" s="11">
         <v>11</v>
       </c>
-      <c r="BQ100" s="11">
+      <c r="BR100" s="11">
         <v>15</v>
       </c>
-      <c r="BR100" s="1" t="s">
-        <v>1263</v>
-      </c>
-    </row>
-    <row r="101" spans="1:70">
+      <c r="BS100" s="1" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="101" spans="1:71">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -26225,17 +26552,20 @@
       <c r="BO101" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP101" s="11">
+      <c r="BP101" s="11" t="s">
+        <v>1345</v>
+      </c>
+      <c r="BQ101" s="11">
         <v>11</v>
       </c>
-      <c r="BQ101" s="11">
+      <c r="BR101" s="11">
         <v>15</v>
       </c>
-      <c r="BR101" s="1" t="s">
-        <v>1264</v>
-      </c>
-    </row>
-    <row r="102" spans="1:70">
+      <c r="BS101" s="1" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="102" spans="1:71">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -26437,17 +26767,20 @@
       <c r="BO102" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP102" s="11">
+      <c r="BP102" s="11" t="s">
+        <v>1345</v>
+      </c>
+      <c r="BQ102" s="11">
         <v>11</v>
       </c>
-      <c r="BQ102" s="11">
+      <c r="BR102" s="11">
         <v>15</v>
       </c>
-      <c r="BR102" s="1" t="s">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="103" spans="1:70">
+      <c r="BS102" s="1" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="103" spans="1:71">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -26649,17 +26982,20 @@
       <c r="BO103" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP103" s="11">
+      <c r="BP103" s="11" t="s">
+        <v>1345</v>
+      </c>
+      <c r="BQ103" s="11">
         <v>11</v>
       </c>
-      <c r="BQ103" s="11">
+      <c r="BR103" s="11">
         <v>15</v>
       </c>
-      <c r="BR103" s="1" t="s">
-        <v>1266</v>
-      </c>
-    </row>
-    <row r="104" spans="1:70">
+      <c r="BS103" s="1" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="104" spans="1:71">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -26805,7 +27141,7 @@
         <v>4</v>
       </c>
       <c r="AW104" s="1">
-        <v>0.97199999999999998</v>
+        <v>1.944</v>
       </c>
       <c r="AX104" s="1" t="s">
         <v>314</v>
@@ -26859,19 +27195,22 @@
         <v>314</v>
       </c>
       <c r="BO104" s="1" t="s">
-        <v>819</v>
-      </c>
-      <c r="BP104" s="1">
+        <v>1206</v>
+      </c>
+      <c r="BP104" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ104" s="1">
         <v>0.1</v>
       </c>
-      <c r="BQ104" s="1">
+      <c r="BR104" s="1">
         <v>23</v>
       </c>
-      <c r="BR104" s="1" t="s">
-        <v>1226</v>
-      </c>
-    </row>
-    <row r="105" spans="1:70">
+      <c r="BS104" s="1" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="105" spans="1:71">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -27017,7 +27356,7 @@
         <v>4</v>
       </c>
       <c r="AW105" s="1">
-        <v>0.97199999999999998</v>
+        <v>1.944</v>
       </c>
       <c r="AX105" s="1" t="s">
         <v>314</v>
@@ -27071,19 +27410,22 @@
         <v>314</v>
       </c>
       <c r="BO105" s="1" t="s">
-        <v>819</v>
-      </c>
-      <c r="BP105" s="1">
+        <v>1206</v>
+      </c>
+      <c r="BP105" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ105" s="1">
         <v>0.1</v>
       </c>
-      <c r="BQ105" s="1">
+      <c r="BR105" s="1">
         <v>23</v>
       </c>
-      <c r="BR105" s="1" t="s">
-        <v>1227</v>
-      </c>
-    </row>
-    <row r="106" spans="1:70">
+      <c r="BS105" s="1" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="106" spans="1:71">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -27151,7 +27493,7 @@
         <v>574</v>
       </c>
       <c r="W106" s="11" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="X106" s="1" t="s">
         <v>295</v>
@@ -27285,17 +27627,20 @@
       <c r="BO106" s="11" t="s">
         <v>819</v>
       </c>
-      <c r="BP106" s="11">
+      <c r="BP106" s="11" t="s">
+        <v>1347</v>
+      </c>
+      <c r="BQ106" s="11">
         <v>2.0993975903614448</v>
       </c>
-      <c r="BQ106" s="11">
+      <c r="BR106" s="11">
         <v>16</v>
       </c>
-      <c r="BR106" s="1" t="s">
-        <v>1229</v>
-      </c>
-    </row>
-    <row r="107" spans="1:70" s="11" customFormat="1">
+      <c r="BS106" s="1" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="107" spans="1:71" s="11" customFormat="1">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -27351,7 +27696,7 @@
         <v>764</v>
       </c>
       <c r="S107" s="11" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="T107" s="11" t="s">
         <v>333</v>
@@ -27497,17 +27842,20 @@
       <c r="BO107" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP107" s="11">
+      <c r="BP107" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ107" s="11">
         <v>1</v>
       </c>
-      <c r="BQ107" s="11">
+      <c r="BR107" s="11">
         <v>12</v>
       </c>
-      <c r="BR107" s="11" t="s">
-        <v>1230</v>
-      </c>
-    </row>
-    <row r="108" spans="1:70">
+      <c r="BS107" s="11" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="108" spans="1:71">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -27709,17 +28057,20 @@
       <c r="BO108" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="BP108" s="11">
+      <c r="BP108" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="BQ108" s="11">
         <v>1.4</v>
       </c>
-      <c r="BQ108" s="11">
+      <c r="BR108" s="11">
         <v>25</v>
       </c>
-      <c r="BR108" s="1" t="s">
-        <v>1310</v>
-      </c>
-    </row>
-    <row r="109" spans="1:70">
+      <c r="BS108" s="1" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="109" spans="1:71">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -27921,17 +28272,20 @@
       <c r="BO109" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP109" s="11">
+      <c r="BP109" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ109" s="11">
         <v>1.4</v>
       </c>
-      <c r="BQ109" s="11">
+      <c r="BR109" s="11">
         <v>25</v>
       </c>
-      <c r="BR109" s="1" t="s">
-        <v>1232</v>
-      </c>
-    </row>
-    <row r="110" spans="1:70">
+      <c r="BS109" s="1" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="110" spans="1:71">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -28133,17 +28487,20 @@
       <c r="BO110" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP110" s="11">
+      <c r="BP110" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ110" s="11">
         <v>1.4</v>
       </c>
-      <c r="BQ110" s="11">
+      <c r="BR110" s="11">
         <v>25</v>
       </c>
-      <c r="BR110" s="1" t="s">
-        <v>1233</v>
-      </c>
-    </row>
-    <row r="111" spans="1:70">
+      <c r="BS110" s="1" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="111" spans="1:71">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -28345,17 +28702,20 @@
       <c r="BO111" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP111" s="11">
+      <c r="BP111" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ111" s="11">
         <v>1.4</v>
       </c>
-      <c r="BQ111" s="11">
+      <c r="BR111" s="11">
         <v>25</v>
       </c>
-      <c r="BR111" s="1" t="s">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="112" spans="1:70">
+      <c r="BS111" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="112" spans="1:71">
       <c r="A112" s="1">
         <v>111</v>
       </c>
@@ -28557,17 +28917,20 @@
       <c r="BO112" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP112" s="11">
+      <c r="BP112" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ112" s="11">
         <v>1.4</v>
       </c>
-      <c r="BQ112" s="11">
+      <c r="BR112" s="11">
         <v>25</v>
       </c>
-      <c r="BR112" s="1" t="s">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="113" spans="1:70">
+      <c r="BS112" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="113" spans="1:71">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -28769,17 +29132,20 @@
       <c r="BO113" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP113" s="11">
+      <c r="BP113" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ113" s="11">
         <v>1.4</v>
       </c>
-      <c r="BQ113" s="11">
+      <c r="BR113" s="11">
         <v>25</v>
       </c>
-      <c r="BR113" s="1" t="s">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="114" spans="1:70">
+      <c r="BS113" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="114" spans="1:71">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -28981,17 +29347,20 @@
       <c r="BO114" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP114" s="11">
+      <c r="BP114" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ114" s="11">
         <v>1.4</v>
       </c>
-      <c r="BQ114" s="11">
+      <c r="BR114" s="11">
         <v>25</v>
       </c>
-      <c r="BR114" s="1" t="s">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="115" spans="1:70">
+      <c r="BS114" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="115" spans="1:71">
       <c r="A115" s="1">
         <v>114</v>
       </c>
@@ -29193,17 +29562,20 @@
       <c r="BO115" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP115" s="11">
+      <c r="BP115" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ115" s="11">
         <v>1.4</v>
       </c>
-      <c r="BQ115" s="11">
+      <c r="BR115" s="11">
         <v>25</v>
       </c>
-      <c r="BR115" s="1" t="s">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="116" spans="1:70">
+      <c r="BS115" s="1" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="116" spans="1:71">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -29405,17 +29777,20 @@
       <c r="BO116" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP116">
+      <c r="BP116" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ116">
         <v>1.58</v>
       </c>
-      <c r="BQ116" s="11">
+      <c r="BR116" s="11">
         <v>28</v>
       </c>
-      <c r="BR116" s="1" t="s">
-        <v>1235</v>
-      </c>
-    </row>
-    <row r="117" spans="1:70">
+      <c r="BS116" s="1" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="117" spans="1:71">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -29617,17 +29992,20 @@
       <c r="BO117" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP117">
+      <c r="BP117" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ117">
         <v>1.58</v>
       </c>
-      <c r="BQ117" s="11">
+      <c r="BR117" s="11">
         <v>28</v>
       </c>
-      <c r="BR117" s="1" t="s">
-        <v>1236</v>
-      </c>
-    </row>
-    <row r="118" spans="1:70">
+      <c r="BS117" s="1" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="118" spans="1:71">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -29829,17 +30207,20 @@
       <c r="BO118" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP118">
+      <c r="BP118" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ118">
         <v>1.58</v>
       </c>
-      <c r="BQ118" s="11">
+      <c r="BR118" s="11">
         <v>28</v>
       </c>
-      <c r="BR118" s="1" t="s">
-        <v>1237</v>
-      </c>
-    </row>
-    <row r="119" spans="1:70">
+      <c r="BS118" s="1" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="119" spans="1:71">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -30041,17 +30422,20 @@
       <c r="BO119" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP119">
+      <c r="BP119" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ119">
         <v>1.58</v>
       </c>
-      <c r="BQ119" s="11">
+      <c r="BR119" s="11">
         <v>28</v>
       </c>
-      <c r="BR119" s="1" t="s">
-        <v>1238</v>
-      </c>
-    </row>
-    <row r="120" spans="1:70">
+      <c r="BS119" s="1" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="120" spans="1:71">
       <c r="A120" s="1">
         <v>119</v>
       </c>
@@ -30253,17 +30637,20 @@
       <c r="BO120" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP120">
+      <c r="BP120" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ120">
         <v>1.58</v>
       </c>
-      <c r="BQ120" s="11">
+      <c r="BR120" s="11">
         <v>28</v>
       </c>
-      <c r="BR120" s="1" t="s">
-        <v>1239</v>
-      </c>
-    </row>
-    <row r="121" spans="1:70">
+      <c r="BS120" s="1" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="121" spans="1:71">
       <c r="A121" s="1">
         <v>120</v>
       </c>
@@ -30465,17 +30852,20 @@
       <c r="BO121" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP121">
+      <c r="BP121" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ121">
         <v>1.58</v>
       </c>
-      <c r="BQ121" s="11">
+      <c r="BR121" s="11">
         <v>28</v>
       </c>
-      <c r="BR121" s="1" t="s">
-        <v>1240</v>
-      </c>
-    </row>
-    <row r="122" spans="1:70">
+      <c r="BS121" s="1" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="122" spans="1:71">
       <c r="A122" s="1">
         <v>121</v>
       </c>
@@ -30677,17 +31067,20 @@
       <c r="BO122" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP122">
+      <c r="BP122" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ122">
         <v>1.58</v>
       </c>
-      <c r="BQ122" s="11">
+      <c r="BR122" s="11">
         <v>28</v>
       </c>
-      <c r="BR122" s="1" t="s">
-        <v>1241</v>
-      </c>
-    </row>
-    <row r="123" spans="1:70">
+      <c r="BS122" s="1" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="123" spans="1:71">
       <c r="A123" s="1">
         <v>122</v>
       </c>
@@ -30889,17 +31282,20 @@
       <c r="BO123" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP123">
+      <c r="BP123" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ123">
         <v>1.58</v>
       </c>
-      <c r="BQ123" s="11">
+      <c r="BR123" s="11">
         <v>28</v>
       </c>
-      <c r="BR123" s="1" t="s">
-        <v>1242</v>
-      </c>
-    </row>
-    <row r="124" spans="1:70">
+      <c r="BS123" s="1" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="124" spans="1:71">
       <c r="A124" s="1">
         <v>123</v>
       </c>
@@ -31101,17 +31497,20 @@
       <c r="BO124" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP124">
+      <c r="BP124" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ124">
         <v>1.58</v>
       </c>
-      <c r="BQ124" s="11">
+      <c r="BR124" s="11">
         <v>28</v>
       </c>
-      <c r="BR124" s="1" t="s">
-        <v>1243</v>
-      </c>
-    </row>
-    <row r="125" spans="1:70">
+      <c r="BS124" s="1" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="125" spans="1:71">
       <c r="A125" s="1">
         <v>124</v>
       </c>
@@ -31313,17 +31712,20 @@
       <c r="BO125" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP125">
+      <c r="BP125" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ125">
         <v>1.58</v>
       </c>
-      <c r="BQ125" s="11">
+      <c r="BR125" s="11">
         <v>28</v>
       </c>
-      <c r="BR125" s="1" t="s">
-        <v>1244</v>
-      </c>
-    </row>
-    <row r="126" spans="1:70">
+      <c r="BS125" s="1" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="126" spans="1:71">
       <c r="A126" s="1">
         <v>125</v>
       </c>
@@ -31525,17 +31927,20 @@
       <c r="BO126" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP126">
+      <c r="BP126" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ126">
         <v>1.58</v>
       </c>
-      <c r="BQ126" s="11">
+      <c r="BR126" s="11">
         <v>28</v>
       </c>
-      <c r="BR126" s="1" t="s">
-        <v>1245</v>
-      </c>
-    </row>
-    <row r="127" spans="1:70">
+      <c r="BS126" s="1" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="127" spans="1:71">
       <c r="A127" s="1">
         <v>126</v>
       </c>
@@ -31737,17 +32142,20 @@
       <c r="BO127" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP127">
+      <c r="BP127" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ127">
         <v>1.58</v>
       </c>
-      <c r="BQ127" s="11">
+      <c r="BR127" s="11">
         <v>28</v>
       </c>
-      <c r="BR127" s="1" t="s">
-        <v>1246</v>
-      </c>
-    </row>
-    <row r="128" spans="1:70">
+      <c r="BS127" s="1" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="128" spans="1:71">
       <c r="A128" s="1">
         <v>127</v>
       </c>
@@ -31904,17 +32312,17 @@
       <c r="AZ128" s="1">
         <v>0</v>
       </c>
-      <c r="BA128" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB128" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC128" s="1">
-        <v>21</v>
-      </c>
-      <c r="BD128" s="1">
-        <v>8</v>
+      <c r="BA128" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BB128" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BC128" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BD128" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="BE128" s="1">
         <v>16</v>
@@ -31949,17 +32357,20 @@
       <c r="BO128" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP128" s="1">
+      <c r="BP128" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ128" s="1">
         <v>21</v>
       </c>
-      <c r="BQ128" s="11">
+      <c r="BR128" s="11">
         <v>14</v>
       </c>
-      <c r="BR128" s="1" t="s">
+      <c r="BS128" s="1" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="129" spans="1:70">
+    <row r="129" spans="1:71">
       <c r="A129" s="1">
         <v>128</v>
       </c>
@@ -32116,17 +32527,17 @@
       <c r="AZ129" s="1">
         <v>0</v>
       </c>
-      <c r="BA129" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB129" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC129" s="1">
-        <v>14</v>
-      </c>
-      <c r="BD129" s="1">
-        <v>4</v>
+      <c r="BA129" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BB129" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BC129" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BD129" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="BE129" s="1">
         <v>16</v>
@@ -32161,17 +32572,20 @@
       <c r="BO129" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP129" s="1">
+      <c r="BP129" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ129" s="1">
         <v>14</v>
       </c>
-      <c r="BQ129" s="11">
+      <c r="BR129" s="11">
         <v>14</v>
       </c>
-      <c r="BR129" s="1" t="s">
+      <c r="BS129" s="1" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="130" spans="1:70">
+    <row r="130" spans="1:71">
       <c r="A130" s="1">
         <v>129</v>
       </c>
@@ -32328,17 +32742,17 @@
       <c r="AZ130" s="1">
         <v>0</v>
       </c>
-      <c r="BA130" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB130" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC130" s="1">
-        <v>21</v>
-      </c>
-      <c r="BD130" s="1">
-        <v>8</v>
+      <c r="BA130" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BB130" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BC130" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BD130" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="BE130" s="1">
         <v>16</v>
@@ -32373,17 +32787,20 @@
       <c r="BO130" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP130" s="1">
+      <c r="BP130" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ130" s="1">
         <v>21</v>
       </c>
-      <c r="BQ130" s="11">
+      <c r="BR130" s="11">
         <v>14</v>
       </c>
-      <c r="BR130" s="1" t="s">
+      <c r="BS130" s="1" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="131" spans="1:70">
+    <row r="131" spans="1:71">
       <c r="A131" s="1">
         <v>130</v>
       </c>
@@ -32540,17 +32957,17 @@
       <c r="AZ131" s="1">
         <v>0</v>
       </c>
-      <c r="BA131" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB131" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC131" s="1">
-        <v>14</v>
-      </c>
-      <c r="BD131" s="1">
-        <v>4</v>
+      <c r="BA131" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BB131" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BC131" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BD131" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="BE131" s="1">
         <v>16</v>
@@ -32585,17 +33002,20 @@
       <c r="BO131" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP131" s="1">
+      <c r="BP131" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ131" s="1">
         <v>14</v>
       </c>
-      <c r="BQ131" s="11">
+      <c r="BR131" s="11">
         <v>14</v>
       </c>
-      <c r="BR131" s="1" t="s">
+      <c r="BS131" s="1" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="132" spans="1:70">
+    <row r="132" spans="1:71">
       <c r="A132" s="1">
         <v>131</v>
       </c>
@@ -32752,17 +33172,17 @@
       <c r="AZ132" s="1">
         <v>0</v>
       </c>
-      <c r="BA132" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB132" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC132" s="1">
-        <v>21</v>
-      </c>
-      <c r="BD132" s="1">
-        <v>8</v>
+      <c r="BA132" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BB132" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BC132" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BD132" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="BE132" s="1">
         <v>16</v>
@@ -32797,17 +33217,20 @@
       <c r="BO132" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP132" s="1">
+      <c r="BP132" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ132" s="1">
         <v>21</v>
       </c>
-      <c r="BQ132" s="11">
+      <c r="BR132" s="11">
         <v>14</v>
       </c>
-      <c r="BR132" s="1" t="s">
+      <c r="BS132" s="1" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="133" spans="1:70">
+    <row r="133" spans="1:71">
       <c r="A133" s="1">
         <v>132</v>
       </c>
@@ -32964,17 +33387,17 @@
       <c r="AZ133" s="1">
         <v>0</v>
       </c>
-      <c r="BA133" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB133" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC133" s="1">
-        <v>14</v>
-      </c>
-      <c r="BD133" s="1">
-        <v>4</v>
+      <c r="BA133" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BB133" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BC133" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BD133" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="BE133" s="1">
         <v>16</v>
@@ -33009,17 +33432,20 @@
       <c r="BO133" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP133" s="1">
+      <c r="BP133" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ133" s="1">
         <v>14</v>
       </c>
-      <c r="BQ133" s="11">
+      <c r="BR133" s="11">
         <v>14</v>
       </c>
-      <c r="BR133" s="1" t="s">
+      <c r="BS133" s="1" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="134" spans="1:70">
+    <row r="134" spans="1:71">
       <c r="A134" s="1">
         <v>133</v>
       </c>
@@ -33176,17 +33602,17 @@
       <c r="AZ134" s="1">
         <v>0</v>
       </c>
-      <c r="BA134" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB134" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC134" s="1">
-        <v>21</v>
-      </c>
-      <c r="BD134" s="1">
-        <v>8</v>
+      <c r="BA134" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BB134" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BC134" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BD134" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="BE134" s="1">
         <v>16</v>
@@ -33221,17 +33647,20 @@
       <c r="BO134" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP134" s="1">
+      <c r="BP134" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ134" s="1">
         <v>21</v>
       </c>
-      <c r="BQ134" s="11">
+      <c r="BR134" s="11">
         <v>14</v>
       </c>
-      <c r="BR134" s="1" t="s">
+      <c r="BS134" s="1" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="135" spans="1:70">
+    <row r="135" spans="1:71">
       <c r="A135" s="1">
         <v>134</v>
       </c>
@@ -33388,17 +33817,17 @@
       <c r="AZ135" s="1">
         <v>0</v>
       </c>
-      <c r="BA135" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB135" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC135" s="1">
-        <v>14</v>
-      </c>
-      <c r="BD135" s="1">
-        <v>4</v>
+      <c r="BA135" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BB135" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BC135" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BD135" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="BE135" s="1">
         <v>16</v>
@@ -33433,17 +33862,20 @@
       <c r="BO135" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP135" s="1">
+      <c r="BP135" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ135" s="1">
         <v>14</v>
       </c>
-      <c r="BQ135" s="11">
+      <c r="BR135" s="11">
         <v>14</v>
       </c>
-      <c r="BR135" s="1" t="s">
+      <c r="BS135" s="1" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="136" spans="1:70">
+    <row r="136" spans="1:71">
       <c r="A136" s="1">
         <v>135</v>
       </c>
@@ -33600,17 +34032,17 @@
       <c r="AZ136" s="1">
         <v>0</v>
       </c>
-      <c r="BA136" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB136" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC136" s="1">
-        <v>21</v>
-      </c>
-      <c r="BD136" s="1">
-        <v>8</v>
+      <c r="BA136" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BB136" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BC136" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BD136" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="BE136" s="1">
         <v>16</v>
@@ -33645,17 +34077,20 @@
       <c r="BO136" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP136" s="1">
+      <c r="BP136" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ136" s="1">
         <v>21</v>
       </c>
-      <c r="BQ136" s="11">
+      <c r="BR136" s="11">
         <v>14</v>
       </c>
-      <c r="BR136" s="1" t="s">
+      <c r="BS136" s="1" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="137" spans="1:70">
+    <row r="137" spans="1:71">
       <c r="A137" s="1">
         <v>136</v>
       </c>
@@ -33812,17 +34247,17 @@
       <c r="AZ137" s="1">
         <v>0</v>
       </c>
-      <c r="BA137" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB137" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC137" s="1">
-        <v>14</v>
-      </c>
-      <c r="BD137" s="1">
-        <v>4</v>
+      <c r="BA137" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BB137" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BC137" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BD137" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="BE137" s="1">
         <v>16</v>
@@ -33857,17 +34292,20 @@
       <c r="BO137" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP137" s="1">
+      <c r="BP137" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ137" s="1">
         <v>14</v>
       </c>
-      <c r="BQ137" s="11">
+      <c r="BR137" s="11">
         <v>14</v>
       </c>
-      <c r="BR137" s="1" t="s">
+      <c r="BS137" s="1" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="138" spans="1:70">
+    <row r="138" spans="1:71">
       <c r="A138" s="1">
         <v>137</v>
       </c>
@@ -34024,17 +34462,17 @@
       <c r="AZ138" s="1">
         <v>0</v>
       </c>
-      <c r="BA138" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB138" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC138" s="1">
-        <v>21</v>
-      </c>
-      <c r="BD138" s="1">
-        <v>8</v>
+      <c r="BA138" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BB138" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BC138" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BD138" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="BE138" s="1">
         <v>16</v>
@@ -34069,17 +34507,20 @@
       <c r="BO138" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP138" s="1">
+      <c r="BP138" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ138" s="1">
         <v>21</v>
       </c>
-      <c r="BQ138" s="11">
+      <c r="BR138" s="11">
         <v>14</v>
       </c>
-      <c r="BR138" s="1" t="s">
+      <c r="BS138" s="1" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="139" spans="1:70">
+    <row r="139" spans="1:71">
       <c r="A139" s="1">
         <v>138</v>
       </c>
@@ -34236,17 +34677,17 @@
       <c r="AZ139" s="1">
         <v>0</v>
       </c>
-      <c r="BA139" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB139" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC139" s="1">
-        <v>14</v>
-      </c>
-      <c r="BD139" s="1">
-        <v>4</v>
+      <c r="BA139" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BB139" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BC139" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BD139" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="BE139" s="1">
         <v>16</v>
@@ -34281,17 +34722,20 @@
       <c r="BO139" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP139" s="1">
+      <c r="BP139" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ139" s="1">
         <v>14</v>
       </c>
-      <c r="BQ139" s="11">
+      <c r="BR139" s="11">
         <v>14</v>
       </c>
-      <c r="BR139" s="1" t="s">
+      <c r="BS139" s="1" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="140" spans="1:70">
+    <row r="140" spans="1:71">
       <c r="A140" s="1">
         <v>139</v>
       </c>
@@ -34448,17 +34892,17 @@
       <c r="AZ140" s="1">
         <v>0</v>
       </c>
-      <c r="BA140" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB140" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC140" s="1">
-        <v>21</v>
-      </c>
-      <c r="BD140" s="1">
-        <v>8</v>
+      <c r="BA140" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BB140" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BC140" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BD140" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="BE140" s="1">
         <v>16</v>
@@ -34493,17 +34937,20 @@
       <c r="BO140" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP140" s="1">
+      <c r="BP140" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ140" s="1">
         <v>21</v>
       </c>
-      <c r="BQ140" s="11">
+      <c r="BR140" s="11">
         <v>14</v>
       </c>
-      <c r="BR140" s="1" t="s">
+      <c r="BS140" s="1" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="141" spans="1:70">
+    <row r="141" spans="1:71">
       <c r="A141" s="1">
         <v>140</v>
       </c>
@@ -34660,17 +35107,17 @@
       <c r="AZ141" s="1">
         <v>0</v>
       </c>
-      <c r="BA141" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB141" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC141" s="1">
-        <v>14</v>
-      </c>
-      <c r="BD141" s="1">
-        <v>4</v>
+      <c r="BA141" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BB141" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BC141" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BD141" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="BE141" s="1">
         <v>16</v>
@@ -34705,17 +35152,20 @@
       <c r="BO141" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP141" s="1">
+      <c r="BP141" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ141" s="1">
         <v>14</v>
       </c>
-      <c r="BQ141" s="11">
+      <c r="BR141" s="11">
         <v>14</v>
       </c>
-      <c r="BR141" s="1" t="s">
+      <c r="BS141" s="1" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="142" spans="1:70">
+    <row r="142" spans="1:71">
       <c r="A142" s="1">
         <v>141</v>
       </c>
@@ -34872,17 +35322,17 @@
       <c r="AZ142" s="1">
         <v>0</v>
       </c>
-      <c r="BA142" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB142" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC142" s="1">
-        <v>21</v>
-      </c>
-      <c r="BD142" s="1">
-        <v>8</v>
+      <c r="BA142" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BB142" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BC142" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BD142" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="BE142" s="1">
         <v>16</v>
@@ -34917,17 +35367,20 @@
       <c r="BO142" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP142" s="1">
+      <c r="BP142" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ142" s="1">
         <v>21</v>
       </c>
-      <c r="BQ142" s="11">
+      <c r="BR142" s="11">
         <v>14</v>
       </c>
-      <c r="BR142" s="1" t="s">
+      <c r="BS142" s="1" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="143" spans="1:70">
+    <row r="143" spans="1:71">
       <c r="A143" s="1">
         <v>142</v>
       </c>
@@ -35084,17 +35537,17 @@
       <c r="AZ143" s="1">
         <v>0</v>
       </c>
-      <c r="BA143" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB143" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC143" s="1">
-        <v>14</v>
-      </c>
-      <c r="BD143" s="1">
-        <v>4</v>
+      <c r="BA143" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BB143" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BC143" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BD143" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="BE143" s="1">
         <v>16</v>
@@ -35129,17 +35582,20 @@
       <c r="BO143" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP143" s="1">
+      <c r="BP143" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ143" s="1">
         <v>14</v>
       </c>
-      <c r="BQ143" s="11">
+      <c r="BR143" s="11">
         <v>14</v>
       </c>
-      <c r="BR143" s="1" t="s">
+      <c r="BS143" s="1" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="144" spans="1:70">
+    <row r="144" spans="1:71">
       <c r="A144" s="1">
         <v>143</v>
       </c>
@@ -35296,17 +35752,17 @@
       <c r="AZ144" s="1">
         <v>0</v>
       </c>
-      <c r="BA144" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB144" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC144" s="1">
-        <v>21</v>
-      </c>
-      <c r="BD144" s="1">
-        <v>8</v>
+      <c r="BA144" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BB144" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BC144" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BD144" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="BE144" s="1">
         <v>16</v>
@@ -35341,17 +35797,20 @@
       <c r="BO144" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP144" s="1">
+      <c r="BP144" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ144" s="1">
         <v>21</v>
       </c>
-      <c r="BQ144" s="11">
+      <c r="BR144" s="11">
         <v>14</v>
       </c>
-      <c r="BR144" s="1" t="s">
+      <c r="BS144" s="1" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="145" spans="1:70">
+    <row r="145" spans="1:71">
       <c r="A145" s="1">
         <v>144</v>
       </c>
@@ -35508,17 +35967,17 @@
       <c r="AZ145" s="1">
         <v>0</v>
       </c>
-      <c r="BA145" s="1">
-        <v>0</v>
-      </c>
-      <c r="BB145" s="1">
-        <v>0</v>
-      </c>
-      <c r="BC145" s="1">
-        <v>14</v>
-      </c>
-      <c r="BD145" s="1">
-        <v>4</v>
+      <c r="BA145" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BB145" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BC145" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BD145" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="BE145" s="1">
         <v>16</v>
@@ -35553,17 +36012,20 @@
       <c r="BO145" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP145" s="1">
+      <c r="BP145" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ145" s="1">
         <v>14</v>
       </c>
-      <c r="BQ145" s="11">
+      <c r="BR145" s="11">
         <v>14</v>
       </c>
-      <c r="BR145" s="1" t="s">
+      <c r="BS145" s="1" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="146" spans="1:70">
+    <row r="146" spans="1:71">
       <c r="A146" s="1">
         <v>145</v>
       </c>
@@ -35765,17 +36227,20 @@
       <c r="BO146" s="11" t="s">
         <v>1206</v>
       </c>
-      <c r="BP146" s="7">
+      <c r="BP146" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ146" s="7">
         <v>0.38500000000000001</v>
       </c>
-      <c r="BQ146" s="11">
+      <c r="BR146" s="11">
         <v>28.4</v>
       </c>
-      <c r="BR146" s="1" t="s">
-        <v>1267</v>
-      </c>
-    </row>
-    <row r="147" spans="1:70">
+      <c r="BS146" s="1" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="147" spans="1:71">
       <c r="A147" s="1">
         <v>146</v>
       </c>
@@ -35977,17 +36442,20 @@
       <c r="BO147" s="20" t="s">
         <v>1206</v>
       </c>
-      <c r="BP147" s="1">
+      <c r="BP147" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ147" s="1">
         <v>10.8</v>
       </c>
-      <c r="BQ147" s="11">
+      <c r="BR147" s="11">
         <v>18</v>
       </c>
-      <c r="BR147" s="1" t="s">
-        <v>1269</v>
-      </c>
-    </row>
-    <row r="148" spans="1:70">
+      <c r="BS147" s="1" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="148" spans="1:71">
       <c r="A148" s="1">
         <v>147</v>
       </c>
@@ -36189,17 +36657,20 @@
       <c r="BO148" s="20" t="s">
         <v>1206</v>
       </c>
-      <c r="BP148" s="1">
+      <c r="BP148" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ148" s="1">
         <v>10.8</v>
       </c>
-      <c r="BQ148" s="11">
+      <c r="BR148" s="11">
         <v>18</v>
       </c>
-      <c r="BR148" s="1" t="s">
+      <c r="BS148" s="1" t="s">
         <v>1000</v>
       </c>
     </row>
-    <row r="149" spans="1:70">
+    <row r="149" spans="1:71">
       <c r="A149" s="1">
         <v>148</v>
       </c>
@@ -36401,17 +36872,20 @@
       <c r="BO149" s="20" t="s">
         <v>1206</v>
       </c>
-      <c r="BP149" s="1">
+      <c r="BP149" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ149" s="1">
         <v>10.8</v>
       </c>
-      <c r="BQ149" s="11">
+      <c r="BR149" s="11">
         <v>18</v>
       </c>
-      <c r="BR149" s="1" t="s">
+      <c r="BS149" s="1" t="s">
         <v>1000</v>
       </c>
     </row>
-    <row r="150" spans="1:70">
+    <row r="150" spans="1:71">
       <c r="A150" s="1">
         <v>149</v>
       </c>
@@ -36613,17 +37087,20 @@
       <c r="BO150" s="20" t="s">
         <v>1206</v>
       </c>
-      <c r="BP150" s="1">
+      <c r="BP150" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ150" s="1">
         <v>10.8</v>
       </c>
-      <c r="BQ150" s="11">
+      <c r="BR150" s="11">
         <v>18</v>
       </c>
-      <c r="BR150" s="1" t="s">
+      <c r="BS150" s="1" t="s">
         <v>1000</v>
       </c>
     </row>
-    <row r="151" spans="1:70">
+    <row r="151" spans="1:71">
       <c r="A151" s="1">
         <v>150</v>
       </c>
@@ -36825,17 +37302,20 @@
       <c r="BO151" s="20" t="s">
         <v>1206</v>
       </c>
-      <c r="BP151" s="1">
+      <c r="BP151" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ151" s="1">
         <v>4.3</v>
       </c>
-      <c r="BQ151" s="1">
+      <c r="BR151" s="1">
         <v>10</v>
       </c>
-      <c r="BR151" s="1" t="s">
+      <c r="BS151" s="1" t="s">
         <v>1000</v>
       </c>
     </row>
-    <row r="152" spans="1:70">
+    <row r="152" spans="1:71">
       <c r="A152" s="1">
         <v>151</v>
       </c>
@@ -37037,17 +37517,20 @@
       <c r="BO152" s="20" t="s">
         <v>1206</v>
       </c>
-      <c r="BP152" s="1">
+      <c r="BP152" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ152" s="1">
         <v>4.3</v>
       </c>
-      <c r="BQ152" s="11">
+      <c r="BR152" s="11">
         <v>18</v>
       </c>
-      <c r="BR152" s="1" t="s">
+      <c r="BS152" s="1" t="s">
         <v>1000</v>
       </c>
     </row>
-    <row r="153" spans="1:70">
+    <row r="153" spans="1:71">
       <c r="A153" s="1">
         <v>152</v>
       </c>
@@ -37249,17 +37732,20 @@
       <c r="BO153" s="20" t="s">
         <v>1206</v>
       </c>
-      <c r="BP153" s="1">
+      <c r="BP153" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ153" s="1">
         <v>1</v>
       </c>
-      <c r="BQ153" s="11">
+      <c r="BR153" s="11">
         <v>18</v>
       </c>
-      <c r="BR153" s="1" t="s">
+      <c r="BS153" s="1" t="s">
         <v>1000</v>
       </c>
     </row>
-    <row r="154" spans="1:70">
+    <row r="154" spans="1:71">
       <c r="A154" s="1">
         <v>153</v>
       </c>
@@ -37461,17 +37947,20 @@
       <c r="BO154" s="20" t="s">
         <v>1206</v>
       </c>
-      <c r="BP154" s="1">
+      <c r="BP154" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ154" s="1">
         <v>1</v>
       </c>
-      <c r="BQ154" s="11">
+      <c r="BR154" s="11">
         <v>18</v>
       </c>
-      <c r="BR154" s="1" t="s">
+      <c r="BS154" s="1" t="s">
         <v>1000</v>
       </c>
     </row>
-    <row r="155" spans="1:70">
+    <row r="155" spans="1:71">
       <c r="A155" s="1">
         <v>154</v>
       </c>
@@ -37673,17 +38162,20 @@
       <c r="BO155" s="20" t="s">
         <v>1206</v>
       </c>
-      <c r="BP155" s="1">
+      <c r="BP155" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ155" s="1">
         <v>1</v>
       </c>
-      <c r="BQ155" s="11">
+      <c r="BR155" s="11">
         <v>18</v>
       </c>
-      <c r="BR155" s="1" t="s">
+      <c r="BS155" s="1" t="s">
         <v>1000</v>
       </c>
     </row>
-    <row r="156" spans="1:70">
+    <row r="156" spans="1:71">
       <c r="A156" s="1">
         <v>155</v>
       </c>
@@ -37885,17 +38377,20 @@
       <c r="BO156" s="20" t="s">
         <v>1206</v>
       </c>
-      <c r="BP156" s="1">
+      <c r="BP156" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ156" s="1">
         <v>1</v>
       </c>
-      <c r="BQ156" s="11">
+      <c r="BR156" s="11">
         <v>18</v>
       </c>
-      <c r="BR156" s="1" t="s">
+      <c r="BS156" s="1" t="s">
         <v>1000</v>
       </c>
     </row>
-    <row r="157" spans="1:70">
+    <row r="157" spans="1:71">
       <c r="A157" s="1">
         <v>156</v>
       </c>
@@ -38097,17 +38592,20 @@
       <c r="BO157" s="20" t="s">
         <v>1206</v>
       </c>
-      <c r="BP157" s="1">
+      <c r="BP157" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ157" s="1">
         <v>1</v>
       </c>
-      <c r="BQ157" s="1">
+      <c r="BR157" s="1">
         <v>10</v>
       </c>
-      <c r="BR157" s="1" t="s">
+      <c r="BS157" s="1" t="s">
         <v>1000</v>
       </c>
     </row>
-    <row r="158" spans="1:70">
+    <row r="158" spans="1:71">
       <c r="A158" s="1">
         <v>157</v>
       </c>
@@ -38309,17 +38807,20 @@
       <c r="BO158" s="20" t="s">
         <v>1206</v>
       </c>
-      <c r="BP158" s="1">
+      <c r="BP158" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ158" s="1">
         <v>1</v>
       </c>
-      <c r="BQ158" s="11">
+      <c r="BR158" s="11">
         <v>18</v>
       </c>
-      <c r="BR158" s="1" t="s">
+      <c r="BS158" s="1" t="s">
         <v>1000</v>
       </c>
     </row>
-    <row r="159" spans="1:70">
+    <row r="159" spans="1:71">
       <c r="A159" s="1">
         <v>158</v>
       </c>
@@ -38521,17 +39022,20 @@
       <c r="BO159" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="BP159" s="1">
+      <c r="BP159" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="BQ159" s="1">
         <v>0.77</v>
       </c>
-      <c r="BQ159" s="11">
+      <c r="BR159" s="11">
         <v>25</v>
       </c>
-      <c r="BR159" s="1" t="s">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="160" spans="1:70">
+      <c r="BS159" s="1" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="160" spans="1:71">
       <c r="A160" s="1">
         <v>159</v>
       </c>
@@ -38733,17 +39237,20 @@
       <c r="BO160" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="BP160" s="1">
+      <c r="BP160" s="11" t="s">
+        <v>314</v>
+      </c>
+      <c r="BQ160" s="1">
         <v>0.77</v>
       </c>
-      <c r="BQ160" s="11">
+      <c r="BR160" s="11">
         <v>25</v>
       </c>
-      <c r="BR160" s="1" t="s">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="161" spans="1:70">
+      <c r="BS160" s="1" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="161" spans="1:71">
       <c r="A161" s="1">
         <v>160</v>
       </c>
@@ -38945,17 +39452,20 @@
       <c r="BO161" s="20" t="s">
         <v>1206</v>
       </c>
-      <c r="BP161" s="1">
+      <c r="BP161" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ161" s="1">
         <v>0.2</v>
       </c>
-      <c r="BQ161" s="11">
+      <c r="BR161" s="11">
         <v>28</v>
       </c>
-      <c r="BR161" s="1" t="s">
-        <v>1272</v>
-      </c>
-    </row>
-    <row r="162" spans="1:70">
+      <c r="BS161" s="1" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="162" spans="1:71">
       <c r="A162" s="1">
         <v>161</v>
       </c>
@@ -39157,17 +39667,20 @@
       <c r="BO162" s="20" t="s">
         <v>1206</v>
       </c>
-      <c r="BP162" s="1">
+      <c r="BP162" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ162" s="1">
         <v>0.2</v>
       </c>
-      <c r="BQ162" s="11">
+      <c r="BR162" s="11">
         <v>28</v>
       </c>
-      <c r="BR162" s="1" t="s">
-        <v>1271</v>
-      </c>
-    </row>
-    <row r="163" spans="1:70">
+      <c r="BS162" s="1" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="163" spans="1:71">
       <c r="A163" s="1">
         <v>162</v>
       </c>
@@ -39369,17 +39882,20 @@
       <c r="BO163" s="20" t="s">
         <v>1206</v>
       </c>
-      <c r="BP163" s="1">
+      <c r="BP163" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ163" s="1">
         <v>20.486076598151243</v>
       </c>
-      <c r="BQ163" s="5">
+      <c r="BR163" s="5">
         <v>14</v>
       </c>
-      <c r="BR163" s="1" t="s">
-        <v>1279</v>
-      </c>
-    </row>
-    <row r="164" spans="1:70">
+      <c r="BS163" s="1" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="164" spans="1:71">
       <c r="A164" s="1">
         <v>163</v>
       </c>
@@ -39581,17 +40097,20 @@
       <c r="BO164" s="20" t="s">
         <v>1206</v>
       </c>
-      <c r="BP164" s="1">
+      <c r="BP164" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ164" s="1">
         <v>20.486076598151243</v>
       </c>
-      <c r="BQ164" s="5">
+      <c r="BR164" s="5">
         <v>14</v>
       </c>
-      <c r="BR164" s="1" t="s">
-        <v>1277</v>
-      </c>
-    </row>
-    <row r="165" spans="1:70">
+      <c r="BS164" s="1" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="165" spans="1:71">
       <c r="A165" s="1">
         <v>164</v>
       </c>
@@ -39793,17 +40312,20 @@
       <c r="BO165" s="20" t="s">
         <v>1206</v>
       </c>
-      <c r="BP165" s="1">
+      <c r="BP165" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ165" s="1">
         <v>20.486076598151243</v>
       </c>
-      <c r="BQ165" s="5">
+      <c r="BR165" s="5">
         <v>14</v>
       </c>
-      <c r="BR165" s="1" t="s">
-        <v>1278</v>
-      </c>
-    </row>
-    <row r="166" spans="1:70">
+      <c r="BS165" s="1" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="166" spans="1:71">
       <c r="A166" s="1">
         <v>165</v>
       </c>
@@ -40005,17 +40527,20 @@
       <c r="BO166" s="20" t="s">
         <v>1206</v>
       </c>
-      <c r="BP166" s="1">
+      <c r="BP166" s="11" t="s">
+        <v>1343</v>
+      </c>
+      <c r="BQ166" s="1">
         <v>1.37</v>
       </c>
-      <c r="BQ166" s="11">
+      <c r="BR166" s="11">
         <v>25</v>
       </c>
-      <c r="BR166" s="1" t="s">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="167" spans="1:70">
+      <c r="BS166" s="1" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="167" spans="1:71">
       <c r="A167" s="1">
         <v>166</v>
       </c>
@@ -40217,17 +40742,20 @@
       <c r="BO167" s="20" t="s">
         <v>1207</v>
       </c>
-      <c r="BP167" s="1">
+      <c r="BP167" s="20" t="s">
+        <v>1340</v>
+      </c>
+      <c r="BQ167" s="1">
         <v>0.184668989547038</v>
       </c>
-      <c r="BQ167" s="11">
+      <c r="BR167" s="11">
         <v>30</v>
       </c>
-      <c r="BR167" s="1" t="s">
-        <v>1281</v>
-      </c>
-    </row>
-    <row r="168" spans="1:70">
+      <c r="BS167" s="1" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="168" spans="1:71">
       <c r="A168" s="1">
         <v>167</v>
       </c>
@@ -40429,17 +40957,20 @@
       <c r="BO168" s="20" t="s">
         <v>1207</v>
       </c>
-      <c r="BP168" s="1">
+      <c r="BP168" s="20" t="s">
+        <v>1340</v>
+      </c>
+      <c r="BQ168" s="1">
         <v>0.184668989547038</v>
       </c>
-      <c r="BQ168" s="11">
+      <c r="BR168" s="11">
         <v>30</v>
       </c>
-      <c r="BR168" s="1" t="s">
-        <v>1281</v>
-      </c>
-    </row>
-    <row r="169" spans="1:70">
+      <c r="BS168" s="1" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="169" spans="1:71">
       <c r="A169" s="1">
         <v>168</v>
       </c>
@@ -40641,17 +41172,20 @@
       <c r="BO169" s="20" t="s">
         <v>1207</v>
       </c>
-      <c r="BP169" s="1">
+      <c r="BP169" s="20" t="s">
+        <v>1340</v>
+      </c>
+      <c r="BQ169" s="1">
         <v>0.184668989547038</v>
       </c>
-      <c r="BQ169" s="21">
+      <c r="BR169" s="21">
         <v>30</v>
       </c>
-      <c r="BR169" s="1" t="s">
-        <v>1282</v>
-      </c>
-    </row>
-    <row r="170" spans="1:70">
+      <c r="BS169" s="1" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="170" spans="1:71">
       <c r="A170" s="1">
         <v>169</v>
       </c>
@@ -40853,17 +41387,20 @@
       <c r="BO170" s="20" t="s">
         <v>1207</v>
       </c>
-      <c r="BP170" s="1">
+      <c r="BP170" s="20" t="s">
+        <v>1340</v>
+      </c>
+      <c r="BQ170" s="1">
         <v>0.184668989547038</v>
       </c>
-      <c r="BQ170" s="11">
+      <c r="BR170" s="11">
         <v>30</v>
       </c>
-      <c r="BR170" s="1" t="s">
-        <v>1282</v>
-      </c>
-    </row>
-    <row r="171" spans="1:70">
+      <c r="BS170" s="1" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="171" spans="1:71">
       <c r="A171" s="1">
         <v>170</v>
       </c>
@@ -41065,17 +41602,20 @@
       <c r="BO171" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="BP171" s="1">
+      <c r="BP171" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BQ171" s="1">
         <v>2.5</v>
       </c>
-      <c r="BQ171" s="11">
+      <c r="BR171" s="11">
         <v>25</v>
       </c>
-      <c r="BR171" s="1" t="s">
-        <v>1286</v>
-      </c>
-    </row>
-    <row r="172" spans="1:70">
+      <c r="BS171" s="1" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="172" spans="1:71">
       <c r="A172" s="1">
         <v>171</v>
       </c>
@@ -41274,17 +41814,20 @@
       <c r="BO172" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="BP172" s="1">
+      <c r="BP172" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BQ172" s="1">
         <v>2.5</v>
       </c>
-      <c r="BQ172" s="11">
+      <c r="BR172" s="11">
         <v>25</v>
       </c>
-      <c r="BR172" s="1" t="s">
-        <v>1283</v>
-      </c>
-    </row>
-    <row r="173" spans="1:70">
+      <c r="BS172" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="173" spans="1:71">
       <c r="A173" s="1">
         <v>172</v>
       </c>
@@ -41486,17 +42029,20 @@
       <c r="BO173" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="BP173" s="1">
+      <c r="BP173" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BQ173" s="1">
         <v>2.5</v>
       </c>
-      <c r="BQ173" s="11">
+      <c r="BR173" s="11">
         <v>25</v>
       </c>
-      <c r="BR173" s="1" t="s">
-        <v>1284</v>
-      </c>
-    </row>
-    <row r="174" spans="1:70">
+      <c r="BS173" s="1" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="174" spans="1:71">
       <c r="A174" s="1">
         <v>173</v>
       </c>
@@ -41698,17 +42244,20 @@
       <c r="BO174" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="BP174" s="1">
+      <c r="BP174" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="BQ174" s="1">
         <v>2.5</v>
       </c>
-      <c r="BQ174" s="11">
+      <c r="BR174" s="11">
         <v>25</v>
       </c>
-      <c r="BR174" s="1" t="s">
-        <v>1285</v>
-      </c>
-    </row>
-    <row r="175" spans="1:70">
+      <c r="BS174" s="1" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="175" spans="1:71">
       <c r="A175" s="1">
         <v>174</v>
       </c>
@@ -41722,7 +42271,7 @@
         <v>257</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>174</v>
@@ -41731,10 +42280,10 @@
         <v>1985</v>
       </c>
       <c r="H175" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I175" s="1" t="s">
         <v>1275</v>
-      </c>
-      <c r="I175" s="1" t="s">
-        <v>1276</v>
       </c>
       <c r="J175" s="1">
         <v>17.759328</v>
@@ -41776,7 +42325,7 @@
         <v>314</v>
       </c>
       <c r="W175" s="1" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
       <c r="X175" s="11" t="s">
         <v>312</v>
@@ -41824,7 +42373,7 @@
         <v>1134</v>
       </c>
       <c r="AM175" s="11" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="AN175" s="11" t="s">
         <v>314</v>
@@ -41854,7 +42403,7 @@
         <v>102</v>
       </c>
       <c r="AW175" s="1">
-        <v>400</v>
+        <v>1.095</v>
       </c>
       <c r="AX175" s="1" t="s">
         <v>314</v>
@@ -41910,17 +42459,20 @@
       <c r="BO175" s="1" t="s">
         <v>1207</v>
       </c>
-      <c r="BP175" s="1">
+      <c r="BP175" s="1" t="s">
+        <v>1342</v>
+      </c>
+      <c r="BQ175" s="1">
         <v>0.2</v>
       </c>
-      <c r="BQ175" s="1">
+      <c r="BR175" s="1">
         <v>26.499666666666666</v>
       </c>
-      <c r="BR175" s="1" t="s">
-        <v>1340</v>
-      </c>
-    </row>
-    <row r="176" spans="1:70">
+      <c r="BS175" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="176" spans="1:71">
       <c r="A176" s="1">
         <v>175</v>
       </c>
@@ -41934,7 +42486,7 @@
         <v>257</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>174</v>
@@ -41943,10 +42495,10 @@
         <v>1985</v>
       </c>
       <c r="H176" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I176" s="1" t="s">
         <v>1275</v>
-      </c>
-      <c r="I176" s="1" t="s">
-        <v>1276</v>
       </c>
       <c r="J176" s="1">
         <v>17.759328</v>
@@ -41988,7 +42540,7 @@
         <v>314</v>
       </c>
       <c r="W176" s="1" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
       <c r="X176" s="11" t="s">
         <v>312</v>
@@ -42066,7 +42618,7 @@
         <v>81</v>
       </c>
       <c r="AW176" s="1">
-        <v>400</v>
+        <v>1.095</v>
       </c>
       <c r="AX176" s="1" t="s">
         <v>314</v>
@@ -42122,17 +42674,20 @@
       <c r="BO176" s="1" t="s">
         <v>1207</v>
       </c>
-      <c r="BP176" s="1">
+      <c r="BP176" s="1" t="s">
+        <v>1342</v>
+      </c>
+      <c r="BQ176" s="1">
         <v>0.2</v>
       </c>
-      <c r="BQ176" s="1">
+      <c r="BR176" s="1">
         <v>26.499666666666666</v>
       </c>
-      <c r="BR176" s="1" t="s">
-        <v>1339</v>
-      </c>
-    </row>
-    <row r="177" spans="1:70">
+      <c r="BS176" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="177" spans="1:71">
       <c r="A177" s="1">
         <v>176</v>
       </c>
@@ -42146,7 +42701,7 @@
         <v>257</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>174</v>
@@ -42155,10 +42710,10 @@
         <v>1985</v>
       </c>
       <c r="H177" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I177" s="1" t="s">
         <v>1275</v>
-      </c>
-      <c r="I177" s="1" t="s">
-        <v>1276</v>
       </c>
       <c r="J177" s="1">
         <v>17.759328</v>
@@ -42200,7 +42755,7 @@
         <v>314</v>
       </c>
       <c r="W177" s="1" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
       <c r="X177" s="11" t="s">
         <v>312</v>
@@ -42248,7 +42803,7 @@
         <v>1134</v>
       </c>
       <c r="AM177" s="11" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="AN177" s="11" t="s">
         <v>314</v>
@@ -42278,7 +42833,7 @@
         <v>29</v>
       </c>
       <c r="AW177" s="1">
-        <v>400</v>
+        <v>1.095</v>
       </c>
       <c r="AX177" s="1" t="s">
         <v>314</v>
@@ -42334,17 +42889,20 @@
       <c r="BO177" s="1" t="s">
         <v>1207</v>
       </c>
-      <c r="BP177" s="1">
+      <c r="BP177" s="1" t="s">
+        <v>1342</v>
+      </c>
+      <c r="BQ177" s="1">
         <v>0.2</v>
       </c>
-      <c r="BQ177" s="1">
+      <c r="BR177" s="1">
         <v>26.499666666666666</v>
       </c>
-      <c r="BR177" s="1" t="s">
-        <v>1339</v>
-      </c>
-    </row>
-    <row r="178" spans="1:70">
+      <c r="BS177" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="178" spans="1:71">
       <c r="A178" s="1">
         <v>177</v>
       </c>
@@ -42358,7 +42916,7 @@
         <v>257</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>174</v>
@@ -42367,10 +42925,10 @@
         <v>1985</v>
       </c>
       <c r="H178" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I178" s="1" t="s">
         <v>1275</v>
-      </c>
-      <c r="I178" s="1" t="s">
-        <v>1276</v>
       </c>
       <c r="J178" s="1">
         <v>17.759328</v>
@@ -42409,7 +42967,7 @@
         <v>1</v>
       </c>
       <c r="V178" s="1" t="s">
-        <v>1332</v>
+        <v>1327</v>
       </c>
       <c r="W178" s="1">
         <v>1981</v>
@@ -42490,7 +43048,7 @@
         <v>202</v>
       </c>
       <c r="AW178" s="1">
-        <v>400</v>
+        <v>1.095</v>
       </c>
       <c r="AX178" s="1" t="s">
         <v>314</v>
@@ -42546,17 +43104,20 @@
       <c r="BO178" s="1" t="s">
         <v>1207</v>
       </c>
-      <c r="BP178" s="1">
+      <c r="BP178" s="1" t="s">
+        <v>1342</v>
+      </c>
+      <c r="BQ178" s="1">
         <v>0.2</v>
       </c>
-      <c r="BQ178" s="1">
+      <c r="BR178" s="1">
         <v>26.499666666666666</v>
       </c>
-      <c r="BR178" s="1" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="179" spans="1:70">
+      <c r="BS178" s="1" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="179" spans="1:71">
       <c r="A179" s="1">
         <v>178</v>
       </c>
@@ -42570,7 +43131,7 @@
         <v>257</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>174</v>
@@ -42579,10 +43140,10 @@
         <v>1985</v>
       </c>
       <c r="H179" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I179" s="1" t="s">
         <v>1275</v>
-      </c>
-      <c r="I179" s="1" t="s">
-        <v>1276</v>
       </c>
       <c r="J179" s="1">
         <v>17.759328</v>
@@ -42621,7 +43182,7 @@
         <v>1</v>
       </c>
       <c r="V179" s="1" t="s">
-        <v>1332</v>
+        <v>1327</v>
       </c>
       <c r="W179" s="1">
         <v>1981</v>
@@ -42672,7 +43233,7 @@
         <v>1134</v>
       </c>
       <c r="AM179" s="11" t="s">
-        <v>1328</v>
+        <v>1323</v>
       </c>
       <c r="AN179" s="11" t="s">
         <v>658</v>
@@ -42702,7 +43263,7 @@
         <v>203</v>
       </c>
       <c r="AW179" s="1">
-        <v>400</v>
+        <v>1.095</v>
       </c>
       <c r="AX179" s="1" t="s">
         <v>314</v>
@@ -42758,17 +43319,20 @@
       <c r="BO179" s="1" t="s">
         <v>1207</v>
       </c>
-      <c r="BP179" s="1">
+      <c r="BP179" s="1" t="s">
+        <v>1342</v>
+      </c>
+      <c r="BQ179" s="1">
         <v>0.2</v>
       </c>
-      <c r="BQ179" s="1">
+      <c r="BR179" s="1">
         <v>26.499666666666666</v>
       </c>
-      <c r="BR179" s="1" t="s">
-        <v>1333</v>
-      </c>
-    </row>
-    <row r="180" spans="1:70">
+      <c r="BS179" s="1" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="180" spans="1:71">
       <c r="A180" s="1">
         <v>179</v>
       </c>
@@ -42782,7 +43346,7 @@
         <v>257</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>174</v>
@@ -42791,10 +43355,10 @@
         <v>1985</v>
       </c>
       <c r="H180" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I180" s="1" t="s">
         <v>1275</v>
-      </c>
-      <c r="I180" s="1" t="s">
-        <v>1276</v>
       </c>
       <c r="J180" s="1">
         <v>17.759328</v>
@@ -42833,7 +43397,7 @@
         <v>1</v>
       </c>
       <c r="V180" s="1" t="s">
-        <v>1332</v>
+        <v>1327</v>
       </c>
       <c r="W180" s="1">
         <v>1981</v>
@@ -42884,7 +43448,7 @@
         <v>1134</v>
       </c>
       <c r="AM180" s="11" t="s">
-        <v>1329</v>
+        <v>1324</v>
       </c>
       <c r="AN180" s="11" t="s">
         <v>658</v>
@@ -42914,7 +43478,7 @@
         <v>202</v>
       </c>
       <c r="AW180" s="1">
-        <v>400</v>
+        <v>1.095</v>
       </c>
       <c r="AX180" s="1" t="s">
         <v>314</v>
@@ -42970,17 +43534,20 @@
       <c r="BO180" s="1" t="s">
         <v>1207</v>
       </c>
-      <c r="BP180" s="1">
+      <c r="BP180" s="1" t="s">
+        <v>1342</v>
+      </c>
+      <c r="BQ180" s="1">
         <v>0.2</v>
       </c>
-      <c r="BQ180" s="1">
+      <c r="BR180" s="1">
         <v>26.499666666666666</v>
       </c>
-      <c r="BR180" s="1" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="181" spans="1:70">
+      <c r="BS180" s="1" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="181" spans="1:71">
       <c r="A181" s="1">
         <v>180</v>
       </c>
@@ -42994,7 +43561,7 @@
         <v>257</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>174</v>
@@ -43003,10 +43570,10 @@
         <v>1985</v>
       </c>
       <c r="H181" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I181" s="1" t="s">
         <v>1275</v>
-      </c>
-      <c r="I181" s="1" t="s">
-        <v>1276</v>
       </c>
       <c r="J181" s="1">
         <v>17.759328</v>
@@ -43045,7 +43612,7 @@
         <v>1</v>
       </c>
       <c r="V181" s="1" t="s">
-        <v>1332</v>
+        <v>1327</v>
       </c>
       <c r="W181" s="1">
         <v>1981</v>
@@ -43096,7 +43663,7 @@
         <v>1134</v>
       </c>
       <c r="AM181" s="11" t="s">
-        <v>1330</v>
+        <v>1325</v>
       </c>
       <c r="AN181" s="11" t="s">
         <v>658</v>
@@ -43126,7 +43693,7 @@
         <v>201</v>
       </c>
       <c r="AW181" s="1">
-        <v>400</v>
+        <v>1.095</v>
       </c>
       <c r="AX181" s="1" t="s">
         <v>314</v>
@@ -43182,17 +43749,20 @@
       <c r="BO181" s="1" t="s">
         <v>1207</v>
       </c>
-      <c r="BP181" s="1">
+      <c r="BP181" s="1" t="s">
+        <v>1342</v>
+      </c>
+      <c r="BQ181" s="1">
         <v>0.2</v>
       </c>
-      <c r="BQ181" s="1">
+      <c r="BR181" s="1">
         <v>26.499666666666666</v>
       </c>
-      <c r="BR181" s="1" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="182" spans="1:70">
+      <c r="BS181" s="1" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="182" spans="1:71">
       <c r="A182" s="1">
         <v>181</v>
       </c>
@@ -43206,7 +43776,7 @@
         <v>257</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>174</v>
@@ -43215,10 +43785,10 @@
         <v>1985</v>
       </c>
       <c r="H182" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I182" s="1" t="s">
         <v>1275</v>
-      </c>
-      <c r="I182" s="1" t="s">
-        <v>1276</v>
       </c>
       <c r="J182" s="1">
         <v>17.759328</v>
@@ -43257,7 +43827,7 @@
         <v>1</v>
       </c>
       <c r="V182" s="1" t="s">
-        <v>1332</v>
+        <v>1327</v>
       </c>
       <c r="W182" s="1">
         <v>1981</v>
@@ -43338,7 +43908,7 @@
         <v>201</v>
       </c>
       <c r="AW182" s="1">
-        <v>400</v>
+        <v>1.095</v>
       </c>
       <c r="AX182" s="1" t="s">
         <v>314</v>
@@ -43394,17 +43964,20 @@
       <c r="BO182" s="1" t="s">
         <v>1207</v>
       </c>
-      <c r="BP182" s="1">
+      <c r="BP182" s="1" t="s">
+        <v>1342</v>
+      </c>
+      <c r="BQ182" s="1">
         <v>0.2</v>
       </c>
-      <c r="BQ182" s="1">
+      <c r="BR182" s="1">
         <v>26.499666666666666</v>
       </c>
-      <c r="BR182" s="1" t="s">
-        <v>1336</v>
-      </c>
-    </row>
-    <row r="183" spans="1:70">
+      <c r="BS182" s="1" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="183" spans="1:71">
       <c r="A183" s="1">
         <v>182</v>
       </c>
@@ -43418,7 +43991,7 @@
         <v>257</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>174</v>
@@ -43427,10 +44000,10 @@
         <v>1985</v>
       </c>
       <c r="H183" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I183" s="1" t="s">
         <v>1275</v>
-      </c>
-      <c r="I183" s="1" t="s">
-        <v>1276</v>
       </c>
       <c r="J183" s="1">
         <v>17.759328</v>
@@ -43469,7 +44042,7 @@
         <v>1</v>
       </c>
       <c r="V183" s="1" t="s">
-        <v>1332</v>
+        <v>1327</v>
       </c>
       <c r="W183" s="1">
         <v>1981</v>
@@ -43520,7 +44093,7 @@
         <v>1134</v>
       </c>
       <c r="AM183" s="11" t="s">
-        <v>1331</v>
+        <v>1326</v>
       </c>
       <c r="AN183" s="11" t="s">
         <v>658</v>
@@ -43550,7 +44123,7 @@
         <v>182</v>
       </c>
       <c r="AW183" s="1">
-        <v>400</v>
+        <v>1.095</v>
       </c>
       <c r="AX183" s="1" t="s">
         <v>314</v>
@@ -43606,17 +44179,20 @@
       <c r="BO183" s="1" t="s">
         <v>1207</v>
       </c>
-      <c r="BP183" s="1">
+      <c r="BP183" s="1" t="s">
+        <v>1342</v>
+      </c>
+      <c r="BQ183" s="1">
         <v>0.2</v>
       </c>
-      <c r="BQ183" s="1">
+      <c r="BR183" s="1">
         <v>26.499666666666666</v>
       </c>
-      <c r="BR183" s="1" t="s">
-        <v>1337</v>
-      </c>
-    </row>
-    <row r="184" spans="1:70">
+      <c r="BS183" s="1" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="184" spans="1:71">
       <c r="D184"/>
       <c r="X184" s="11"/>
       <c r="Y184" s="11"/>
@@ -43630,7 +44206,7 @@
       <c r="AM184" s="11"/>
       <c r="AN184" s="11"/>
     </row>
-    <row r="185" spans="1:70">
+    <row r="185" spans="1:71">
       <c r="D185"/>
       <c r="X185" s="11"/>
       <c r="Y185" s="11"/>
@@ -43641,40 +44217,28 @@
       <c r="AJ185" s="11"/>
       <c r="AK185" s="11"/>
       <c r="AL185" s="11"/>
-      <c r="AM185" s="11">
-        <f>27.7*0.9</f>
-        <v>24.93</v>
-      </c>
+      <c r="AM185" s="11"/>
       <c r="AN185" s="11"/>
     </row>
-    <row r="186" spans="1:70">
+    <row r="186" spans="1:71">
       <c r="D186" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="AM186" s="11">
-        <f>27.7*0.97</f>
-        <v>26.869</v>
-      </c>
-      <c r="AN186" s="1">
-        <v>26.499666666666666</v>
-      </c>
-    </row>
-    <row r="187" spans="1:70">
+      <c r="AM186" s="11"/>
+    </row>
+    <row r="187" spans="1:71">
       <c r="D187" s="1" t="s">
         <v>1098</v>
       </c>
-      <c r="AM187" s="1">
-        <v>27.7</v>
-      </c>
-    </row>
-    <row r="188" spans="1:70">
+    </row>
+    <row r="188" spans="1:71">
       <c r="D188" s="1" t="s">
         <v>1115</v>
       </c>
     </row>
-    <row r="189" spans="1:70">
+    <row r="189" spans="1:71">
       <c r="D189" s="1" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
   </sheetData>
@@ -49640,7 +50204,7 @@
         <v>1179</v>
       </c>
       <c r="B40" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -49791,7 +50355,7 @@
         <v>3.42</v>
       </c>
       <c r="BR40" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="41" spans="1:70">
@@ -49799,7 +50363,7 @@
         <v>1179</v>
       </c>
       <c r="B41" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C41">
         <v>2</v>
@@ -49950,7 +50514,7 @@
         <v>3.42</v>
       </c>
       <c r="BR41" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="42" spans="1:70">
@@ -49958,7 +50522,7 @@
         <v>1179</v>
       </c>
       <c r="B42" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C42">
         <v>3</v>
@@ -50109,7 +50673,7 @@
         <v>3.42</v>
       </c>
       <c r="BR42" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="43" spans="1:70">
@@ -50117,7 +50681,7 @@
         <v>1179</v>
       </c>
       <c r="B43" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C43">
         <v>4</v>
@@ -50268,7 +50832,7 @@
         <v>10.65</v>
       </c>
       <c r="BR43" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="44" spans="1:70">
@@ -50276,7 +50840,7 @@
         <v>1179</v>
       </c>
       <c r="B44" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C44">
         <v>5</v>
@@ -50426,7 +50990,7 @@
         <v>10.65</v>
       </c>
       <c r="BR44" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="45" spans="1:70">
@@ -50434,7 +50998,7 @@
         <v>1179</v>
       </c>
       <c r="B45" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="C45">
         <v>6</v>
@@ -50584,7 +51148,7 @@
         <v>10.65</v>
       </c>
       <c r="BR45" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="46" spans="1:70" s="1" customFormat="1">
@@ -50592,7 +51156,7 @@
         <v>1183</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="C46" s="11">
         <v>1</v>

--- a/Output/Data/meta_analysis_data.xlsx
+++ b/Output/Data/meta_analysis_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emlim/Documents/MSc/Ch2-Meta-analysis/Output/Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emlim/Documents/PhD/Ch1-Meta-analysis/Output/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFE7F0A8-014D-D34A-8F0F-B5710DC0B5CA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5950907-3CB6-0A43-BA09-B3A6AFF54273}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30480" yWindow="460" windowWidth="34880" windowHeight="21840" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
+    <workbookView xWindow="1600" yWindow="460" windowWidth="24520" windowHeight="15940" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
   </bookViews>
   <sheets>
     <sheet name="Include" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11669" uniqueCount="1350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11669" uniqueCount="1347">
   <si>
     <t>paper_num</t>
   </si>
@@ -4233,9 +4233,6 @@
     <t>means are mean values over the course of the experiment? It’s a 2 way fully factorial ANOVA, farm site and ref site each had + mussel pee and - mussel pee. Our treatment is the farm site + pee and the control is ref site - pee. Nh4 measured in water n = 6, nitrate and nitrite presented together n = 15. temp from (same lagoon, also oysters, just averaged august temps from both available years) https://www.mdpi.com/2077-1312/8/6/382/htm</t>
   </si>
   <si>
-    <t>Change in leaf # per shoot. This is just the 0 mussel vs 1500 mussels per m2. We're ignoring the intermediate mussel treatment. Reports max nitrate at 3, but 1.4 = avg from  https://aslopubs.onlinelibrary.wiley.com/doi/epdf/10.4319/lo.2000.45.5.1041       Temperature from https://www.int-res.com/articles/meps2020/639/m639p037.pdf</t>
-  </si>
-  <si>
     <t>high vs low grunt density. The ammonium is the predicted nh4 excretion rate in mg/m^2/day. background 1.4 = avg from  https://aslopubs.onlinelibrary.wiley.com/doi/epdf/10.4319/lo.2000.45.5.1041.     temp from https://downloads.hindawi.com/journals/jmb/2011/981723.pdf</t>
   </si>
   <si>
@@ -4281,18 +4278,6 @@
     <t>tissue dry weight</t>
   </si>
   <si>
-    <t>growth (linear extension)</t>
-  </si>
-  <si>
-    <t>surface area</t>
-  </si>
-  <si>
-    <t>volume</t>
-  </si>
-  <si>
-    <t>dry weight</t>
-  </si>
-  <si>
     <t>all year</t>
   </si>
   <si>
@@ -4305,9 +4290,6 @@
     <t xml:space="preserve">volume (cm3 per 4 months). Growth over a year. Some coral with grunts, some without. </t>
   </si>
   <si>
-    <t xml:space="preserve">density (g/cm3). Growth over a year. Some coral with grunts, some without. </t>
-  </si>
-  <si>
     <t xml:space="preserve">tissue dry weight (mg per 4 months). Growth over a year. Some coral with grunts, some without. </t>
   </si>
   <si>
@@ -4360,6 +4342,15 @@
   </si>
   <si>
     <t>mg/L/h</t>
+  </si>
+  <si>
+    <t>skeletal density</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skeletal density (g/cm3). Growth over a year. Some coral with grunts, some without. </t>
+  </si>
+  <si>
+    <t>Change in leaf # per shoot. Measurement in Sept - measurement in May. This is just the 0 mussel vs 1500 mussels per m2. We're ignoring the intermediate mussel treatment. Reports max nitrate at 3, but 1.4 = avg from  https://aslopubs.onlinelibrary.wiley.com/doi/epdf/10.4319/lo.2000.45.5.1041       Temperature from https://www.int-res.com/articles/meps2020/639/m639p037.pdf</t>
   </si>
 </sst>
 </file>
@@ -4448,7 +4439,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4479,6 +4470,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -4493,7 +4490,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4522,6 +4519,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4840,7 +4838,9 @@
   <dimension ref="A1:BS189"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="62" width="10.83203125" style="1"/>
+    <col min="1" max="38" width="10.83203125" style="1"/>
+    <col min="39" max="39" width="10.83203125" style="22"/>
+    <col min="40" max="62" width="10.83203125" style="1"/>
     <col min="63" max="63" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="64" max="64" width="10.83203125" style="1"/>
     <col min="65" max="65" width="10.83203125" style="1" customWidth="1"/>
@@ -4965,7 +4965,7 @@
       <c r="AL1" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" s="22" t="s">
         <v>316</v>
       </c>
       <c r="AN1" s="1" t="s">
@@ -5053,7 +5053,7 @@
         <v>1205</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>1339</v>
+        <v>1333</v>
       </c>
       <c r="BQ1" s="1" t="s">
         <v>1210</v>
@@ -5180,7 +5180,7 @@
       <c r="AL2" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM2" s="1" t="s">
+      <c r="AM2" s="22" t="s">
         <v>643</v>
       </c>
       <c r="AN2" s="1" t="s">
@@ -5268,7 +5268,7 @@
         <v>1206</v>
       </c>
       <c r="BP2" s="1" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ2" s="1">
         <v>1.0649999999999999</v>
@@ -5395,7 +5395,7 @@
       <c r="AL3" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM3" s="1" t="s">
+      <c r="AM3" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN3" s="11" t="s">
@@ -5492,7 +5492,7 @@
         <v>11.3</v>
       </c>
       <c r="BS3" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="4" spans="1:71">
@@ -5610,7 +5610,7 @@
       <c r="AL4" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM4" s="1" t="s">
+      <c r="AM4" s="22" t="s">
         <v>348</v>
       </c>
       <c r="AN4" s="11" t="s">
@@ -5825,7 +5825,7 @@
       <c r="AL5" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM5" s="1" t="s">
+      <c r="AM5" s="22" t="s">
         <v>580</v>
       </c>
       <c r="AN5" s="11" t="s">
@@ -6040,7 +6040,7 @@
       <c r="AL6" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM6" s="1" t="s">
+      <c r="AM6" s="22" t="s">
         <v>866</v>
       </c>
       <c r="AN6" s="11" t="s">
@@ -6255,7 +6255,7 @@
       <c r="AL7" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM7" s="1" t="s">
+      <c r="AM7" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN7" s="11" t="s">
@@ -6470,7 +6470,7 @@
       <c r="AL8" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM8" s="11" t="s">
+      <c r="AM8" s="22" t="s">
         <v>348</v>
       </c>
       <c r="AN8" s="11" t="s">
@@ -6685,7 +6685,7 @@
       <c r="AL9" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM9" s="11" t="s">
+      <c r="AM9" s="22" t="s">
         <v>580</v>
       </c>
       <c r="AN9" s="11" t="s">
@@ -6900,7 +6900,7 @@
       <c r="AL10" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM10" s="11" t="s">
+      <c r="AM10" s="22" t="s">
         <v>866</v>
       </c>
       <c r="AN10" s="11" t="s">
@@ -7115,7 +7115,7 @@
       <c r="AL11" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM11" s="11" t="s">
+      <c r="AM11" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN11" s="11" t="s">
@@ -7330,7 +7330,7 @@
       <c r="AL12" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM12" s="11" t="s">
+      <c r="AM12" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN12" s="11" t="s">
@@ -7418,7 +7418,7 @@
         <v>1207</v>
       </c>
       <c r="BP12" s="11" t="s">
-        <v>1340</v>
+        <v>1334</v>
       </c>
       <c r="BQ12" s="11">
         <v>2.13</v>
@@ -7545,7 +7545,7 @@
       <c r="AL13" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM13" s="11" t="s">
+      <c r="AM13" s="22" t="s">
         <v>598</v>
       </c>
       <c r="AN13" s="11" t="s">
@@ -7633,7 +7633,7 @@
         <v>1207</v>
       </c>
       <c r="BP13" s="11" t="s">
-        <v>1340</v>
+        <v>1334</v>
       </c>
       <c r="BQ13" s="11">
         <v>2.13</v>
@@ -7760,7 +7760,7 @@
       <c r="AL14" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM14" s="11" t="s">
+      <c r="AM14" s="22" t="s">
         <v>348</v>
       </c>
       <c r="AN14" s="11" t="s">
@@ -7848,7 +7848,7 @@
         <v>1207</v>
       </c>
       <c r="BP14" s="11" t="s">
-        <v>1340</v>
+        <v>1334</v>
       </c>
       <c r="BQ14" s="11">
         <v>2.13</v>
@@ -7975,7 +7975,7 @@
       <c r="AL15" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM15" s="1" t="s">
+      <c r="AM15" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN15" s="1" t="s">
@@ -8063,7 +8063,7 @@
         <v>1206</v>
       </c>
       <c r="BP15" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ15" s="11">
         <v>2.7777777777777701</v>
@@ -8190,7 +8190,7 @@
       <c r="AL16" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM16" s="1" t="s">
+      <c r="AM16" s="22" t="s">
         <v>725</v>
       </c>
       <c r="AN16" s="1" t="s">
@@ -8278,7 +8278,7 @@
         <v>1206</v>
       </c>
       <c r="BP16" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ16" s="11">
         <v>2.7777777777777701</v>
@@ -8405,7 +8405,7 @@
       <c r="AL17" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM17" s="1" t="s">
+      <c r="AM17" s="22" t="s">
         <v>580</v>
       </c>
       <c r="AN17" s="1" t="s">
@@ -8493,7 +8493,7 @@
         <v>1206</v>
       </c>
       <c r="BP17" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ17">
         <v>10.616666666666667</v>
@@ -8620,7 +8620,7 @@
       <c r="AL18" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM18" s="1" t="s">
+      <c r="AM18" s="22" t="s">
         <v>580</v>
       </c>
       <c r="AN18" s="1" t="s">
@@ -8708,7 +8708,7 @@
         <v>1206</v>
       </c>
       <c r="BP18" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ18">
         <v>10.616666666666667</v>
@@ -8835,7 +8835,7 @@
       <c r="AL19" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM19" s="1" t="s">
+      <c r="AM19" s="22" t="s">
         <v>667</v>
       </c>
       <c r="AN19" s="1" t="s">
@@ -8923,7 +8923,7 @@
         <v>1206</v>
       </c>
       <c r="BP19" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ19" s="11">
         <v>1.0699999999999998</v>
@@ -9050,7 +9050,7 @@
       <c r="AL20" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM20" s="1" t="s">
+      <c r="AM20" s="22" t="s">
         <v>1296</v>
       </c>
       <c r="AN20" s="1" t="s">
@@ -9138,7 +9138,7 @@
         <v>1206</v>
       </c>
       <c r="BP20" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ20" s="11">
         <v>1.0699999999999998</v>
@@ -9265,7 +9265,7 @@
       <c r="AL21" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM21" s="1" t="s">
+      <c r="AM21" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN21" s="1" t="s">
@@ -9353,7 +9353,7 @@
         <v>1206</v>
       </c>
       <c r="BP21" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ21" s="11">
         <v>1.0699999999999998</v>
@@ -9480,7 +9480,7 @@
       <c r="AL22" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM22" s="1" t="s">
+      <c r="AM22" s="22" t="s">
         <v>348</v>
       </c>
       <c r="AN22" s="1" t="s">
@@ -9568,7 +9568,7 @@
         <v>1206</v>
       </c>
       <c r="BP22" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ22" s="11">
         <v>1.0699999999999998</v>
@@ -9695,7 +9695,7 @@
       <c r="AL23" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM23" s="1" t="s">
+      <c r="AM23" s="22" t="s">
         <v>725</v>
       </c>
       <c r="AN23" s="1" t="s">
@@ -9783,7 +9783,7 @@
         <v>1206</v>
       </c>
       <c r="BP23" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ23" s="11">
         <v>1.0699999999999998</v>
@@ -9910,7 +9910,7 @@
       <c r="AL24" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM24" s="1" t="s">
+      <c r="AM24" s="22" t="s">
         <v>596</v>
       </c>
       <c r="AN24" s="1" t="s">
@@ -10125,7 +10125,7 @@
       <c r="AL25" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM25" s="1" t="s">
+      <c r="AM25" s="22" t="s">
         <v>597</v>
       </c>
       <c r="AN25" s="1" t="s">
@@ -10340,7 +10340,7 @@
       <c r="AL26" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM26" s="1" t="s">
+      <c r="AM26" s="22" t="s">
         <v>598</v>
       </c>
       <c r="AN26" s="1" t="s">
@@ -10555,7 +10555,7 @@
       <c r="AL27" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM27" s="11" t="s">
+      <c r="AM27" s="22" t="s">
         <v>580</v>
       </c>
       <c r="AN27" s="11" t="s">
@@ -10643,7 +10643,7 @@
         <v>1206</v>
       </c>
       <c r="BP27" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ27" s="11">
         <v>3</v>
@@ -10770,7 +10770,7 @@
       <c r="AL28" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM28" s="1" t="s">
+      <c r="AM28" s="22" t="s">
         <v>589</v>
       </c>
       <c r="AN28" s="1" t="s">
@@ -10858,7 +10858,7 @@
         <v>1207</v>
       </c>
       <c r="BP28" s="11" t="s">
-        <v>1341</v>
+        <v>1335</v>
       </c>
       <c r="BQ28" s="11">
         <v>1.4</v>
@@ -10867,7 +10867,7 @@
         <v>25.725274725274684</v>
       </c>
       <c r="BS28" s="1" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="29" spans="1:71">
@@ -10985,7 +10985,7 @@
       <c r="AL29" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM29" s="1" t="s">
+      <c r="AM29" s="22" t="s">
         <v>1136</v>
       </c>
       <c r="AN29" s="1" t="s">
@@ -11073,7 +11073,7 @@
         <v>1207</v>
       </c>
       <c r="BP29" s="11" t="s">
-        <v>1341</v>
+        <v>1335</v>
       </c>
       <c r="BQ29" s="11">
         <v>1.4</v>
@@ -11200,7 +11200,7 @@
       <c r="AL30" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM30" s="1" t="s">
+      <c r="AM30" s="22" t="s">
         <v>1136</v>
       </c>
       <c r="AN30" s="1" t="s">
@@ -11288,7 +11288,7 @@
         <v>1207</v>
       </c>
       <c r="BP30" s="11" t="s">
-        <v>1341</v>
+        <v>1335</v>
       </c>
       <c r="BQ30" s="11">
         <v>1.4</v>
@@ -11415,7 +11415,7 @@
       <c r="AL31" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM31" s="1" t="s">
+      <c r="AM31" s="22" t="s">
         <v>1136</v>
       </c>
       <c r="AN31" s="1" t="s">
@@ -11503,7 +11503,7 @@
         <v>1207</v>
       </c>
       <c r="BP31" s="11" t="s">
-        <v>1341</v>
+        <v>1335</v>
       </c>
       <c r="BQ31" s="11">
         <v>1.4</v>
@@ -11630,7 +11630,7 @@
       <c r="AL32" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM32" s="1" t="s">
+      <c r="AM32" s="22" t="s">
         <v>1136</v>
       </c>
       <c r="AN32" s="1" t="s">
@@ -11718,7 +11718,7 @@
         <v>1207</v>
       </c>
       <c r="BP32" s="11" t="s">
-        <v>1341</v>
+        <v>1335</v>
       </c>
       <c r="BQ32" s="11">
         <v>1.4</v>
@@ -11845,7 +11845,7 @@
       <c r="AL33" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM33" s="1" t="s">
+      <c r="AM33" s="22" t="s">
         <v>1136</v>
       </c>
       <c r="AN33" s="1" t="s">
@@ -11933,7 +11933,7 @@
         <v>1207</v>
       </c>
       <c r="BP33" s="11" t="s">
-        <v>1341</v>
+        <v>1335</v>
       </c>
       <c r="BQ33" s="11">
         <v>1.4</v>
@@ -12060,7 +12060,7 @@
       <c r="AL34" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM34" s="1" t="s">
+      <c r="AM34" s="22" t="s">
         <v>1136</v>
       </c>
       <c r="AN34" s="1" t="s">
@@ -12148,7 +12148,7 @@
         <v>1207</v>
       </c>
       <c r="BP34" s="11" t="s">
-        <v>1341</v>
+        <v>1335</v>
       </c>
       <c r="BQ34" s="11">
         <v>1.4</v>
@@ -12275,7 +12275,7 @@
       <c r="AL35" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM35" s="1" t="s">
+      <c r="AM35" s="22" t="s">
         <v>1136</v>
       </c>
       <c r="AN35" s="1" t="s">
@@ -12363,7 +12363,7 @@
         <v>1207</v>
       </c>
       <c r="BP35" s="11" t="s">
-        <v>1341</v>
+        <v>1335</v>
       </c>
       <c r="BQ35" s="11">
         <v>1.4</v>
@@ -12490,7 +12490,7 @@
       <c r="AL36" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM36" s="1" t="s">
+      <c r="AM36" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN36" s="1" t="s">
@@ -12578,7 +12578,7 @@
         <v>819</v>
       </c>
       <c r="BP36" s="11" t="s">
-        <v>1349</v>
+        <v>1343</v>
       </c>
       <c r="BQ36" s="11">
         <v>2.13</v>
@@ -12587,7 +12587,7 @@
         <v>27.2</v>
       </c>
       <c r="BS36" s="1" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="37" spans="1:71">
@@ -12705,7 +12705,7 @@
       <c r="AL37" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM37" s="1" t="s">
+      <c r="AM37" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN37" s="1" t="s">
@@ -12793,7 +12793,7 @@
         <v>1206</v>
       </c>
       <c r="BP37" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ37">
         <v>6.3507812955294964</v>
@@ -12802,7 +12802,7 @@
         <v>26</v>
       </c>
       <c r="BS37" s="1" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="38" spans="1:71">
@@ -12920,7 +12920,7 @@
       <c r="AL38" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM38" s="1" t="s">
+      <c r="AM38" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN38" s="1" t="s">
@@ -13008,7 +13008,7 @@
         <v>1206</v>
       </c>
       <c r="BP38" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ38">
         <v>8.6337418919616322</v>
@@ -13017,7 +13017,7 @@
         <v>26</v>
       </c>
       <c r="BS38" s="1" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="39" spans="1:71">
@@ -13135,7 +13135,7 @@
       <c r="AL39" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM39" s="1" t="s">
+      <c r="AM39" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN39" s="1" t="s">
@@ -13223,7 +13223,7 @@
         <v>1206</v>
       </c>
       <c r="BP39" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ39">
         <v>7.5545241554664546</v>
@@ -13232,7 +13232,7 @@
         <v>26</v>
       </c>
       <c r="BS39" s="1" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="40" spans="1:71">
@@ -13350,7 +13350,7 @@
       <c r="AL40" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM40" s="1" t="s">
+      <c r="AM40" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN40" s="1" t="s">
@@ -13438,7 +13438,7 @@
         <v>1206</v>
       </c>
       <c r="BP40" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ40">
         <v>9.9620098753403727</v>
@@ -13447,7 +13447,7 @@
         <v>26</v>
       </c>
       <c r="BS40" s="1" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="41" spans="1:71">
@@ -13565,7 +13565,7 @@
       <c r="AL41" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM41" s="1" t="s">
+      <c r="AM41" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN41" s="1" t="s">
@@ -13653,7 +13653,7 @@
         <v>1206</v>
       </c>
       <c r="BP41" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ41">
         <v>7.4715074065052436</v>
@@ -13662,7 +13662,7 @@
         <v>26</v>
       </c>
       <c r="BS41" s="1" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="42" spans="1:71">
@@ -13780,7 +13780,7 @@
       <c r="AL42" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM42" s="1" t="s">
+      <c r="AM42" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN42" s="1" t="s">
@@ -13868,7 +13868,7 @@
         <v>1206</v>
       </c>
       <c r="BP42" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ42">
         <v>7.6375409044275955</v>
@@ -13877,7 +13877,7 @@
         <v>26</v>
       </c>
       <c r="BS42" s="1" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="43" spans="1:71">
@@ -13995,7 +13995,7 @@
       <c r="AL43" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM43" s="1" t="s">
+      <c r="AM43" s="22" t="s">
         <v>580</v>
       </c>
       <c r="AN43" s="1" t="s">
@@ -14092,7 +14092,7 @@
         <v>28.65</v>
       </c>
       <c r="BS43" s="1" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="44" spans="1:71">
@@ -14210,7 +14210,7 @@
       <c r="AL44" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="AM44" s="1" t="s">
+      <c r="AM44" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN44" s="1" t="s">
@@ -14298,7 +14298,7 @@
         <v>1206</v>
       </c>
       <c r="BP44" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ44" s="11" t="s">
         <v>314</v>
@@ -14307,7 +14307,7 @@
         <v>17</v>
       </c>
       <c r="BS44" s="1" t="s">
-        <v>1344</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="45" spans="1:71">
@@ -14425,7 +14425,7 @@
       <c r="AL45" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM45" s="1" t="s">
+      <c r="AM45" s="22" t="s">
         <v>696</v>
       </c>
       <c r="AN45" s="1" t="s">
@@ -14522,7 +14522,7 @@
         <v>27.94</v>
       </c>
       <c r="BS45" s="1" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="46" spans="1:71">
@@ -14640,7 +14640,7 @@
       <c r="AL46" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM46" s="1" t="s">
+      <c r="AM46" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN46" s="1" t="s">
@@ -14728,7 +14728,7 @@
         <v>1207</v>
       </c>
       <c r="BP46" s="11" t="s">
-        <v>1340</v>
+        <v>1334</v>
       </c>
       <c r="BQ46" s="11">
         <v>2.13</v>
@@ -14737,7 +14737,7 @@
         <v>25</v>
       </c>
       <c r="BS46" s="1" t="s">
-        <v>1338</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="47" spans="1:71">
@@ -14855,7 +14855,7 @@
       <c r="AL47" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM47" s="1" t="s">
+      <c r="AM47" s="22" t="s">
         <v>1146</v>
       </c>
       <c r="AN47" s="1" t="s">
@@ -14943,7 +14943,7 @@
         <v>1206</v>
       </c>
       <c r="BP47" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ47" s="1">
         <v>0.16129032258064363</v>
@@ -14952,7 +14952,7 @@
         <v>26.17</v>
       </c>
       <c r="BS47" s="1" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="48" spans="1:71">
@@ -15070,7 +15070,7 @@
       <c r="AL48" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM48" s="1" t="s">
+      <c r="AM48" s="22" t="s">
         <v>1147</v>
       </c>
       <c r="AN48" s="1" t="s">
@@ -15158,7 +15158,7 @@
         <v>1206</v>
       </c>
       <c r="BP48" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ48" s="1">
         <v>0.16129032258064363</v>
@@ -15285,7 +15285,7 @@
       <c r="AL49" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM49" s="1" t="s">
+      <c r="AM49" s="22" t="s">
         <v>1147</v>
       </c>
       <c r="AN49" s="1" t="s">
@@ -15373,7 +15373,7 @@
         <v>1206</v>
       </c>
       <c r="BP49" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ49" s="1">
         <v>0.16129032258064363</v>
@@ -15500,7 +15500,7 @@
       <c r="AL50" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM50" s="1" t="s">
+      <c r="AM50" s="22" t="s">
         <v>1147</v>
       </c>
       <c r="AN50" s="1" t="s">
@@ -15588,7 +15588,7 @@
         <v>1206</v>
       </c>
       <c r="BP50" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ50" s="1">
         <v>0.16129032258064363</v>
@@ -15715,7 +15715,7 @@
       <c r="AL51" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM51" s="1" t="s">
+      <c r="AM51" s="22" t="s">
         <v>1148</v>
       </c>
       <c r="AN51" s="1" t="s">
@@ -15803,7 +15803,7 @@
         <v>1206</v>
       </c>
       <c r="BP51" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ51" s="1">
         <v>0.16129032258064363</v>
@@ -15930,7 +15930,7 @@
       <c r="AL52" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM52" s="1" t="s">
+      <c r="AM52" s="22" t="s">
         <v>1148</v>
       </c>
       <c r="AN52" s="1" t="s">
@@ -16018,7 +16018,7 @@
         <v>1206</v>
       </c>
       <c r="BP52" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ52" s="1">
         <v>0.16129032258064363</v>
@@ -16145,7 +16145,7 @@
       <c r="AL53" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM53" s="1" t="s">
+      <c r="AM53" s="22" t="s">
         <v>1148</v>
       </c>
       <c r="AN53" s="1" t="s">
@@ -16233,7 +16233,7 @@
         <v>1206</v>
       </c>
       <c r="BP53" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ53" s="1">
         <v>0.16129032258064363</v>
@@ -16360,7 +16360,7 @@
       <c r="AL54" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM54" s="1" t="s">
+      <c r="AM54" s="22" t="s">
         <v>1008</v>
       </c>
       <c r="AN54" s="1" t="s">
@@ -16448,7 +16448,7 @@
         <v>1206</v>
       </c>
       <c r="BP54" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ54" s="11">
         <v>0.15053763440860024</v>
@@ -16575,7 +16575,7 @@
       <c r="AL55" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM55" s="1" t="s">
+      <c r="AM55" s="22" t="s">
         <v>1008</v>
       </c>
       <c r="AN55" s="1" t="s">
@@ -16663,7 +16663,7 @@
         <v>1206</v>
       </c>
       <c r="BP55" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ55" s="11">
         <v>0.17204301075268699</v>
@@ -16790,7 +16790,7 @@
       <c r="AL56" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM56" s="1" t="s">
+      <c r="AM56" s="22" t="s">
         <v>1008</v>
       </c>
       <c r="AN56" s="1" t="s">
@@ -16878,7 +16878,7 @@
         <v>1206</v>
       </c>
       <c r="BP56" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ56" s="11">
         <v>6.5217391304347394E-2</v>
@@ -17005,7 +17005,7 @@
       <c r="AL57" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM57" s="1" t="s">
+      <c r="AM57" s="22" t="s">
         <v>1008</v>
       </c>
       <c r="AN57" s="1" t="s">
@@ -17093,7 +17093,7 @@
         <v>1206</v>
       </c>
       <c r="BP57" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ57" s="11">
         <v>0.47826086956521702</v>
@@ -17220,7 +17220,7 @@
       <c r="AL58" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM58" s="1" t="s">
+      <c r="AM58" s="22" t="s">
         <v>1008</v>
       </c>
       <c r="AN58" s="1" t="s">
@@ -17308,7 +17308,7 @@
         <v>1206</v>
       </c>
       <c r="BP58" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ58" s="11">
         <v>0.14388489208633001</v>
@@ -17435,7 +17435,7 @@
       <c r="AL59" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM59" s="1" t="s">
+      <c r="AM59" s="22" t="s">
         <v>1008</v>
       </c>
       <c r="AN59" s="1" t="s">
@@ -17523,7 +17523,7 @@
         <v>1206</v>
       </c>
       <c r="BP59" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ59" s="11">
         <v>0.15053763440860024</v>
@@ -17650,7 +17650,7 @@
       <c r="AL60" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM60" s="1" t="s">
+      <c r="AM60" s="22" t="s">
         <v>1008</v>
       </c>
       <c r="AN60" s="1" t="s">
@@ -17738,7 +17738,7 @@
         <v>1206</v>
       </c>
       <c r="BP60" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ60" s="11">
         <v>0.17204301075268699</v>
@@ -17865,7 +17865,7 @@
       <c r="AL61" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM61" s="1" t="s">
+      <c r="AM61" s="22" t="s">
         <v>1008</v>
       </c>
       <c r="AN61" s="1" t="s">
@@ -17953,7 +17953,7 @@
         <v>1206</v>
       </c>
       <c r="BP61" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ61" s="11">
         <v>6.5217391304347394E-2</v>
@@ -18080,7 +18080,7 @@
       <c r="AL62" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM62" s="1" t="s">
+      <c r="AM62" s="22" t="s">
         <v>1008</v>
       </c>
       <c r="AN62" s="1" t="s">
@@ -18168,7 +18168,7 @@
         <v>1206</v>
       </c>
       <c r="BP62" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ62" s="11">
         <v>0.47826086956521702</v>
@@ -18295,7 +18295,7 @@
       <c r="AL63" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM63" s="1" t="s">
+      <c r="AM63" s="22" t="s">
         <v>1008</v>
       </c>
       <c r="AN63" s="1" t="s">
@@ -18383,7 +18383,7 @@
         <v>1206</v>
       </c>
       <c r="BP63" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ63" s="11">
         <v>0.14388489208633001</v>
@@ -18510,7 +18510,7 @@
       <c r="AL64" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM64" s="1" t="s">
+      <c r="AM64" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN64" s="1" t="s">
@@ -18598,7 +18598,7 @@
         <v>1207</v>
       </c>
       <c r="BP64" s="1" t="s">
-        <v>1348</v>
+        <v>1342</v>
       </c>
       <c r="BQ64" s="11">
         <v>0.43</v>
@@ -18607,7 +18607,7 @@
         <v>27</v>
       </c>
       <c r="BS64" s="1" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="65" spans="1:71">
@@ -18725,7 +18725,7 @@
       <c r="AL65" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM65" s="1" t="s">
+      <c r="AM65" s="22" t="s">
         <v>580</v>
       </c>
       <c r="AN65" s="1" t="s">
@@ -18813,7 +18813,7 @@
         <v>1206</v>
       </c>
       <c r="BP65" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ65" s="11">
         <v>0.92648599819331412</v>
@@ -18940,7 +18940,7 @@
       <c r="AL66" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM66" s="1" t="s">
+      <c r="AM66" s="22" t="s">
         <v>716</v>
       </c>
       <c r="AN66" s="1" t="s">
@@ -19028,7 +19028,7 @@
         <v>1206</v>
       </c>
       <c r="BP66" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ66" s="11">
         <v>0.79214092140921299</v>
@@ -19155,7 +19155,7 @@
       <c r="AL67" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM67" s="1" t="s">
+      <c r="AM67" s="22" t="s">
         <v>716</v>
       </c>
       <c r="AN67" s="1" t="s">
@@ -19243,7 +19243,7 @@
         <v>1206</v>
       </c>
       <c r="BP67" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ67" s="11">
         <v>0.90614272809394603</v>
@@ -19370,7 +19370,7 @@
       <c r="AL68" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM68" s="1" t="s">
+      <c r="AM68" s="22" t="s">
         <v>716</v>
       </c>
       <c r="AN68" s="1" t="s">
@@ -19458,7 +19458,7 @@
         <v>1206</v>
       </c>
       <c r="BP68" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ68" s="11">
         <v>1.2923215898825648</v>
@@ -19585,7 +19585,7 @@
       <c r="AL69" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM69" s="1" t="s">
+      <c r="AM69" s="22" t="s">
         <v>716</v>
       </c>
       <c r="AN69" s="1" t="s">
@@ -19673,7 +19673,7 @@
         <v>1206</v>
       </c>
       <c r="BP69" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ69" s="11">
         <v>0.54272809394760502</v>
@@ -19800,7 +19800,7 @@
       <c r="AL70" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM70" s="1" t="s">
+      <c r="AM70" s="22" t="s">
         <v>716</v>
       </c>
       <c r="AN70" s="1" t="s">
@@ -19888,7 +19888,7 @@
         <v>1206</v>
       </c>
       <c r="BP70" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ70" s="11">
         <v>1.0990966576332419</v>
@@ -20015,7 +20015,7 @@
       <c r="AL71" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM71" s="1" t="s">
+      <c r="AM71" s="22" t="s">
         <v>1008</v>
       </c>
       <c r="AN71" s="1" t="s">
@@ -20103,7 +20103,7 @@
         <v>1206</v>
       </c>
       <c r="BP71" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ71" s="11">
         <v>14.34291139240506</v>
@@ -20230,7 +20230,7 @@
       <c r="AL72" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM72" s="1" t="s">
+      <c r="AM72" s="22" t="s">
         <v>1008</v>
       </c>
       <c r="AN72" s="1" t="s">
@@ -20318,7 +20318,7 @@
         <v>1206</v>
       </c>
       <c r="BP72" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ72" s="11">
         <v>14.34291139240506</v>
@@ -20445,7 +20445,7 @@
       <c r="AL73" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM73" s="1" t="s">
+      <c r="AM73" s="22" t="s">
         <v>1008</v>
       </c>
       <c r="AN73" s="1" t="s">
@@ -20533,7 +20533,7 @@
         <v>1206</v>
       </c>
       <c r="BP73" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ73" s="11">
         <v>14.34291139240506</v>
@@ -20660,7 +20660,7 @@
       <c r="AL74" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM74" s="1" t="s">
+      <c r="AM74" s="22" t="s">
         <v>1008</v>
       </c>
       <c r="AN74" s="1" t="s">
@@ -20748,7 +20748,7 @@
         <v>1206</v>
       </c>
       <c r="BP74" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ74" s="11">
         <v>14.34291139240506</v>
@@ -20875,7 +20875,7 @@
       <c r="AL75" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM75" s="1" t="s">
+      <c r="AM75" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN75" s="1" t="s">
@@ -20963,7 +20963,7 @@
         <v>1206</v>
       </c>
       <c r="BP75" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ75" s="11">
         <v>14.34291139240506</v>
@@ -21090,7 +21090,7 @@
       <c r="AL76" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM76" s="1" t="s">
+      <c r="AM76" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN76" s="1" t="s">
@@ -21178,7 +21178,7 @@
         <v>1206</v>
       </c>
       <c r="BP76" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ76" s="11">
         <v>14.34291139240506</v>
@@ -21305,7 +21305,7 @@
       <c r="AL77" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM77" s="1" t="s">
+      <c r="AM77" s="22" t="s">
         <v>1008</v>
       </c>
       <c r="AN77" s="1" t="s">
@@ -21393,7 +21393,7 @@
         <v>1206</v>
       </c>
       <c r="BP77" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ77" s="11">
         <v>14.34291139240506</v>
@@ -21520,7 +21520,7 @@
       <c r="AL78" s="1" t="s">
         <v>1164</v>
       </c>
-      <c r="AM78" s="1" t="s">
+      <c r="AM78" s="22" t="s">
         <v>730</v>
       </c>
       <c r="AN78" s="1" t="s">
@@ -21608,7 +21608,7 @@
         <v>1206</v>
       </c>
       <c r="BP78" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ78" s="11">
         <v>23</v>
@@ -21735,7 +21735,7 @@
       <c r="AL79" s="1" t="s">
         <v>1164</v>
       </c>
-      <c r="AM79" s="1" t="s">
+      <c r="AM79" s="22" t="s">
         <v>598</v>
       </c>
       <c r="AN79" s="1" t="s">
@@ -21823,7 +21823,7 @@
         <v>1206</v>
       </c>
       <c r="BP79" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ79" s="11">
         <v>23</v>
@@ -21950,7 +21950,7 @@
       <c r="AL80" s="1" t="s">
         <v>1164</v>
       </c>
-      <c r="AM80" s="1" t="s">
+      <c r="AM80" s="22" t="s">
         <v>725</v>
       </c>
       <c r="AN80" s="1" t="s">
@@ -22038,7 +22038,7 @@
         <v>1206</v>
       </c>
       <c r="BP80" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ80" s="11">
         <v>23</v>
@@ -22165,7 +22165,7 @@
       <c r="AL81" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="AM81" s="1" t="s">
+      <c r="AM81" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN81" s="1" t="s">
@@ -22253,7 +22253,7 @@
         <v>1206</v>
       </c>
       <c r="BP81" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ81" s="11">
         <v>23</v>
@@ -22380,7 +22380,7 @@
       <c r="AL82" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="AM82" s="1" t="s">
+      <c r="AM82" s="22" t="s">
         <v>730</v>
       </c>
       <c r="AN82" s="1" t="s">
@@ -22468,7 +22468,7 @@
         <v>1206</v>
       </c>
       <c r="BP82" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ82" s="11">
         <v>23</v>
@@ -22595,7 +22595,7 @@
       <c r="AL83" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="AM83" s="1" t="s">
+      <c r="AM83" s="22" t="s">
         <v>731</v>
       </c>
       <c r="AN83" s="1" t="s">
@@ -22683,7 +22683,7 @@
         <v>1206</v>
       </c>
       <c r="BP83" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ83" s="11">
         <v>23</v>
@@ -22810,7 +22810,7 @@
       <c r="AL84" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM84" s="1" t="s">
+      <c r="AM84" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN84" s="1" t="s">
@@ -22898,7 +22898,7 @@
         <v>1206</v>
       </c>
       <c r="BP84" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ84" s="11">
         <v>0.43</v>
@@ -23025,7 +23025,7 @@
       <c r="AL85" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM85" s="1" t="s">
+      <c r="AM85" s="22" t="s">
         <v>731</v>
       </c>
       <c r="AN85" s="1" t="s">
@@ -23113,7 +23113,7 @@
         <v>1206</v>
       </c>
       <c r="BP85" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="BQ85" s="11">
         <v>11</v>
@@ -23240,7 +23240,7 @@
       <c r="AL86" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM86" s="1" t="s">
+      <c r="AM86" s="22" t="s">
         <v>598</v>
       </c>
       <c r="AN86" s="1" t="s">
@@ -23328,7 +23328,7 @@
         <v>1206</v>
       </c>
       <c r="BP86" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="BQ86" s="11">
         <v>11</v>
@@ -23455,7 +23455,7 @@
       <c r="AL87" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM87" s="1" t="s">
+      <c r="AM87" s="22" t="s">
         <v>743</v>
       </c>
       <c r="AN87" s="1" t="s">
@@ -23543,7 +23543,7 @@
         <v>1206</v>
       </c>
       <c r="BP87" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="BQ87" s="11">
         <v>11</v>
@@ -23670,7 +23670,7 @@
       <c r="AL88" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM88" s="1" t="s">
+      <c r="AM88" s="22" t="s">
         <v>730</v>
       </c>
       <c r="AN88" s="1" t="s">
@@ -23758,7 +23758,7 @@
         <v>1206</v>
       </c>
       <c r="BP88" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="BQ88" s="11">
         <v>11</v>
@@ -23885,7 +23885,7 @@
       <c r="AL89" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM89" s="1" t="s">
+      <c r="AM89" s="22" t="s">
         <v>725</v>
       </c>
       <c r="AN89" s="1" t="s">
@@ -23973,7 +23973,7 @@
         <v>1206</v>
       </c>
       <c r="BP89" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="BQ89" s="11">
         <v>11</v>
@@ -24100,7 +24100,7 @@
       <c r="AL90" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM90" s="1" t="s">
+      <c r="AM90" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN90" s="1" t="s">
@@ -24188,7 +24188,7 @@
         <v>1206</v>
       </c>
       <c r="BP90" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="BQ90" s="11">
         <v>11</v>
@@ -24315,7 +24315,7 @@
       <c r="AL91" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM91" s="1" t="s">
+      <c r="AM91" s="22" t="s">
         <v>731</v>
       </c>
       <c r="AN91" s="1" t="s">
@@ -24403,7 +24403,7 @@
         <v>1206</v>
       </c>
       <c r="BP91" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="BQ91" s="11">
         <v>11</v>
@@ -24530,7 +24530,7 @@
       <c r="AL92" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM92" s="1" t="s">
+      <c r="AM92" s="22" t="s">
         <v>598</v>
       </c>
       <c r="AN92" s="1" t="s">
@@ -24618,7 +24618,7 @@
         <v>1206</v>
       </c>
       <c r="BP92" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="BQ92" s="11">
         <v>11</v>
@@ -24745,7 +24745,7 @@
       <c r="AL93" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM93" s="1" t="s">
+      <c r="AM93" s="22" t="s">
         <v>743</v>
       </c>
       <c r="AN93" s="1" t="s">
@@ -24833,7 +24833,7 @@
         <v>1206</v>
       </c>
       <c r="BP93" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="BQ93" s="11">
         <v>11</v>
@@ -24960,7 +24960,7 @@
       <c r="AL94" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM94" s="1" t="s">
+      <c r="AM94" s="22" t="s">
         <v>730</v>
       </c>
       <c r="AN94" s="1" t="s">
@@ -25048,7 +25048,7 @@
         <v>1206</v>
       </c>
       <c r="BP94" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="BQ94" s="11">
         <v>11</v>
@@ -25175,7 +25175,7 @@
       <c r="AL95" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM95" s="1" t="s">
+      <c r="AM95" s="22" t="s">
         <v>725</v>
       </c>
       <c r="AN95" s="1" t="s">
@@ -25263,7 +25263,7 @@
         <v>1206</v>
       </c>
       <c r="BP95" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="BQ95" s="11">
         <v>11</v>
@@ -25390,7 +25390,7 @@
       <c r="AL96" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM96" s="1" t="s">
+      <c r="AM96" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN96" s="1" t="s">
@@ -25478,7 +25478,7 @@
         <v>1206</v>
       </c>
       <c r="BP96" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="BQ96" s="11">
         <v>11</v>
@@ -25605,7 +25605,7 @@
       <c r="AL97" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM97" s="1" t="s">
+      <c r="AM97" s="22" t="s">
         <v>731</v>
       </c>
       <c r="AN97" s="1" t="s">
@@ -25693,7 +25693,7 @@
         <v>1206</v>
       </c>
       <c r="BP97" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="BQ97" s="11">
         <v>11</v>
@@ -25820,7 +25820,7 @@
       <c r="AL98" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM98" s="1" t="s">
+      <c r="AM98" s="22" t="s">
         <v>598</v>
       </c>
       <c r="AN98" s="1" t="s">
@@ -25908,7 +25908,7 @@
         <v>1206</v>
       </c>
       <c r="BP98" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="BQ98" s="11">
         <v>11</v>
@@ -26035,7 +26035,7 @@
       <c r="AL99" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM99" s="1" t="s">
+      <c r="AM99" s="22" t="s">
         <v>743</v>
       </c>
       <c r="AN99" s="1" t="s">
@@ -26123,7 +26123,7 @@
         <v>1206</v>
       </c>
       <c r="BP99" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="BQ99" s="11">
         <v>11</v>
@@ -26250,7 +26250,7 @@
       <c r="AL100" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM100" s="1" t="s">
+      <c r="AM100" s="22" t="s">
         <v>730</v>
       </c>
       <c r="AN100" s="1" t="s">
@@ -26338,7 +26338,7 @@
         <v>1206</v>
       </c>
       <c r="BP100" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="BQ100" s="11">
         <v>11</v>
@@ -26465,7 +26465,7 @@
       <c r="AL101" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM101" s="1" t="s">
+      <c r="AM101" s="22" t="s">
         <v>725</v>
       </c>
       <c r="AN101" s="1" t="s">
@@ -26553,7 +26553,7 @@
         <v>1206</v>
       </c>
       <c r="BP101" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="BQ101" s="11">
         <v>11</v>
@@ -26680,7 +26680,7 @@
       <c r="AL102" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM102" s="1" t="s">
+      <c r="AM102" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN102" s="1" t="s">
@@ -26768,7 +26768,7 @@
         <v>1206</v>
       </c>
       <c r="BP102" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="BQ102" s="11">
         <v>11</v>
@@ -26895,7 +26895,7 @@
       <c r="AL103" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM103" s="1" t="s">
+      <c r="AM103" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN103" s="1" t="s">
@@ -26983,7 +26983,7 @@
         <v>1206</v>
       </c>
       <c r="BP103" s="11" t="s">
-        <v>1345</v>
+        <v>1339</v>
       </c>
       <c r="BQ103" s="11">
         <v>11</v>
@@ -27110,7 +27110,7 @@
       <c r="AL104" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM104" s="1" t="s">
+      <c r="AM104" s="22" t="s">
         <v>754</v>
       </c>
       <c r="AN104" s="1" t="s">
@@ -27198,7 +27198,7 @@
         <v>1206</v>
       </c>
       <c r="BP104" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ104" s="1">
         <v>0.1</v>
@@ -27207,7 +27207,7 @@
         <v>23</v>
       </c>
       <c r="BS104" s="1" t="s">
-        <v>1346</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="105" spans="1:71">
@@ -27325,7 +27325,7 @@
       <c r="AL105" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM105" s="1" t="s">
+      <c r="AM105" s="22" t="s">
         <v>889</v>
       </c>
       <c r="AN105" s="1" t="s">
@@ -27413,7 +27413,7 @@
         <v>1206</v>
       </c>
       <c r="BP105" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ105" s="1">
         <v>0.1</v>
@@ -27540,7 +27540,7 @@
       <c r="AL106" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM106" s="1" t="s">
+      <c r="AM106" s="22" t="s">
         <v>763</v>
       </c>
       <c r="AN106" s="1" t="s">
@@ -27628,7 +27628,7 @@
         <v>819</v>
       </c>
       <c r="BP106" s="11" t="s">
-        <v>1347</v>
+        <v>1341</v>
       </c>
       <c r="BQ106" s="11">
         <v>2.0993975903614448</v>
@@ -27755,7 +27755,7 @@
       <c r="AL107" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM107" s="11" t="s">
+      <c r="AM107" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN107" s="11" t="s">
@@ -27843,7 +27843,7 @@
         <v>1206</v>
       </c>
       <c r="BP107" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ107" s="11">
         <v>1</v>
@@ -27970,7 +27970,7 @@
       <c r="AL108" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM108" s="1" t="s">
+      <c r="AM108" s="22" t="s">
         <v>730</v>
       </c>
       <c r="AN108" s="1" t="s">
@@ -28067,7 +28067,7 @@
         <v>25</v>
       </c>
       <c r="BS108" s="1" t="s">
-        <v>1307</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="109" spans="1:71">
@@ -28185,7 +28185,7 @@
       <c r="AL109" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM109" s="1" t="s">
+      <c r="AM109" s="22" t="s">
         <v>773</v>
       </c>
       <c r="AN109" s="1" t="s">
@@ -28273,7 +28273,7 @@
         <v>1206</v>
       </c>
       <c r="BP109" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ109" s="11">
         <v>1.4</v>
@@ -28400,7 +28400,7 @@
       <c r="AL110" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM110" s="1" t="s">
+      <c r="AM110" s="22" t="s">
         <v>774</v>
       </c>
       <c r="AN110" s="1" t="s">
@@ -28488,7 +28488,7 @@
         <v>1206</v>
       </c>
       <c r="BP110" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ110" s="11">
         <v>1.4</v>
@@ -28615,8 +28615,8 @@
       <c r="AL111" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM111" s="1" t="s">
-        <v>775</v>
+      <c r="AM111" s="22" t="s">
+        <v>317</v>
       </c>
       <c r="AN111" s="1" t="s">
         <v>658</v>
@@ -28703,7 +28703,7 @@
         <v>1206</v>
       </c>
       <c r="BP111" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ111" s="11">
         <v>1.4</v>
@@ -28830,8 +28830,8 @@
       <c r="AL112" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM112" s="1" t="s">
-        <v>775</v>
+      <c r="AM112" s="22" t="s">
+        <v>317</v>
       </c>
       <c r="AN112" s="1" t="s">
         <v>658</v>
@@ -28918,7 +28918,7 @@
         <v>1206</v>
       </c>
       <c r="BP112" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ112" s="11">
         <v>1.4</v>
@@ -29045,8 +29045,8 @@
       <c r="AL113" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM113" s="1" t="s">
-        <v>775</v>
+      <c r="AM113" s="22" t="s">
+        <v>317</v>
       </c>
       <c r="AN113" s="1" t="s">
         <v>658</v>
@@ -29133,7 +29133,7 @@
         <v>1206</v>
       </c>
       <c r="BP113" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ113" s="11">
         <v>1.4</v>
@@ -29260,8 +29260,8 @@
       <c r="AL114" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM114" s="1" t="s">
-        <v>775</v>
+      <c r="AM114" s="22" t="s">
+        <v>317</v>
       </c>
       <c r="AN114" s="1" t="s">
         <v>658</v>
@@ -29348,7 +29348,7 @@
         <v>1206</v>
       </c>
       <c r="BP114" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ114" s="11">
         <v>1.4</v>
@@ -29475,8 +29475,8 @@
       <c r="AL115" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM115" s="1" t="s">
-        <v>775</v>
+      <c r="AM115" s="22" t="s">
+        <v>317</v>
       </c>
       <c r="AN115" s="1" t="s">
         <v>658</v>
@@ -29563,7 +29563,7 @@
         <v>1206</v>
       </c>
       <c r="BP115" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ115" s="11">
         <v>1.4</v>
@@ -29690,7 +29690,7 @@
       <c r="AL116" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="AM116" s="1" t="s">
+      <c r="AM116" s="22" t="s">
         <v>775</v>
       </c>
       <c r="AN116" s="1" t="s">
@@ -29778,7 +29778,7 @@
         <v>1206</v>
       </c>
       <c r="BP116" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ116">
         <v>1.58</v>
@@ -29905,7 +29905,7 @@
       <c r="AL117" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="AM117" s="1" t="s">
+      <c r="AM117" s="22" t="s">
         <v>775</v>
       </c>
       <c r="AN117" s="1" t="s">
@@ -29993,7 +29993,7 @@
         <v>1206</v>
       </c>
       <c r="BP117" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ117">
         <v>1.58</v>
@@ -30120,7 +30120,7 @@
       <c r="AL118" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="AM118" s="1" t="s">
+      <c r="AM118" s="22" t="s">
         <v>775</v>
       </c>
       <c r="AN118" s="1" t="s">
@@ -30208,7 +30208,7 @@
         <v>1206</v>
       </c>
       <c r="BP118" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ118">
         <v>1.58</v>
@@ -30335,7 +30335,7 @@
       <c r="AL119" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="AM119" s="1" t="s">
+      <c r="AM119" s="22" t="s">
         <v>775</v>
       </c>
       <c r="AN119" s="1" t="s">
@@ -30423,7 +30423,7 @@
         <v>1206</v>
       </c>
       <c r="BP119" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ119">
         <v>1.58</v>
@@ -30550,7 +30550,7 @@
       <c r="AL120" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="AM120" s="1" t="s">
+      <c r="AM120" s="22" t="s">
         <v>775</v>
       </c>
       <c r="AN120" s="1" t="s">
@@ -30638,7 +30638,7 @@
         <v>1206</v>
       </c>
       <c r="BP120" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ120">
         <v>1.58</v>
@@ -30765,7 +30765,7 @@
       <c r="AL121" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="AM121" s="1" t="s">
+      <c r="AM121" s="22" t="s">
         <v>775</v>
       </c>
       <c r="AN121" s="1" t="s">
@@ -30853,7 +30853,7 @@
         <v>1206</v>
       </c>
       <c r="BP121" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ121">
         <v>1.58</v>
@@ -30980,7 +30980,7 @@
       <c r="AL122" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="AM122" s="1" t="s">
+      <c r="AM122" s="22" t="s">
         <v>775</v>
       </c>
       <c r="AN122" s="1" t="s">
@@ -31068,7 +31068,7 @@
         <v>1206</v>
       </c>
       <c r="BP122" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ122">
         <v>1.58</v>
@@ -31195,7 +31195,7 @@
       <c r="AL123" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="AM123" s="1" t="s">
+      <c r="AM123" s="22" t="s">
         <v>775</v>
       </c>
       <c r="AN123" s="1" t="s">
@@ -31283,7 +31283,7 @@
         <v>1206</v>
       </c>
       <c r="BP123" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ123">
         <v>1.58</v>
@@ -31410,7 +31410,7 @@
       <c r="AL124" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="AM124" s="1" t="s">
+      <c r="AM124" s="22" t="s">
         <v>775</v>
       </c>
       <c r="AN124" s="1" t="s">
@@ -31498,7 +31498,7 @@
         <v>1206</v>
       </c>
       <c r="BP124" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ124">
         <v>1.58</v>
@@ -31625,7 +31625,7 @@
       <c r="AL125" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="AM125" s="1" t="s">
+      <c r="AM125" s="22" t="s">
         <v>775</v>
       </c>
       <c r="AN125" s="1" t="s">
@@ -31713,7 +31713,7 @@
         <v>1206</v>
       </c>
       <c r="BP125" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ125">
         <v>1.58</v>
@@ -31840,7 +31840,7 @@
       <c r="AL126" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="AM126" s="1" t="s">
+      <c r="AM126" s="22" t="s">
         <v>775</v>
       </c>
       <c r="AN126" s="1" t="s">
@@ -31928,7 +31928,7 @@
         <v>1206</v>
       </c>
       <c r="BP126" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ126">
         <v>1.58</v>
@@ -32055,7 +32055,7 @@
       <c r="AL127" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="AM127" s="1" t="s">
+      <c r="AM127" s="22" t="s">
         <v>775</v>
       </c>
       <c r="AN127" s="1" t="s">
@@ -32143,7 +32143,7 @@
         <v>1206</v>
       </c>
       <c r="BP127" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ127">
         <v>1.58</v>
@@ -32270,7 +32270,7 @@
       <c r="AL128" s="1" t="s">
         <v>1169</v>
       </c>
-      <c r="AM128" s="1" t="s">
+      <c r="AM128" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN128" s="1" t="s">
@@ -32358,7 +32358,7 @@
         <v>1206</v>
       </c>
       <c r="BP128" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ128" s="1">
         <v>21</v>
@@ -32485,7 +32485,7 @@
       <c r="AL129" s="1" t="s">
         <v>1170</v>
       </c>
-      <c r="AM129" s="1" t="s">
+      <c r="AM129" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN129" s="1" t="s">
@@ -32573,7 +32573,7 @@
         <v>1206</v>
       </c>
       <c r="BP129" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ129" s="1">
         <v>14</v>
@@ -32700,7 +32700,7 @@
       <c r="AL130" s="1" t="s">
         <v>1169</v>
       </c>
-      <c r="AM130" s="1" t="s">
+      <c r="AM130" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN130" s="1" t="s">
@@ -32788,7 +32788,7 @@
         <v>1206</v>
       </c>
       <c r="BP130" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ130" s="1">
         <v>21</v>
@@ -32915,7 +32915,7 @@
       <c r="AL131" s="1" t="s">
         <v>1170</v>
       </c>
-      <c r="AM131" s="1" t="s">
+      <c r="AM131" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN131" s="1" t="s">
@@ -33003,7 +33003,7 @@
         <v>1206</v>
       </c>
       <c r="BP131" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ131" s="1">
         <v>14</v>
@@ -33130,7 +33130,7 @@
       <c r="AL132" s="1" t="s">
         <v>1169</v>
       </c>
-      <c r="AM132" s="1" t="s">
+      <c r="AM132" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN132" s="1" t="s">
@@ -33218,7 +33218,7 @@
         <v>1206</v>
       </c>
       <c r="BP132" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ132" s="1">
         <v>21</v>
@@ -33345,7 +33345,7 @@
       <c r="AL133" s="1" t="s">
         <v>1170</v>
       </c>
-      <c r="AM133" s="1" t="s">
+      <c r="AM133" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN133" s="1" t="s">
@@ -33433,7 +33433,7 @@
         <v>1206</v>
       </c>
       <c r="BP133" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ133" s="1">
         <v>14</v>
@@ -33560,7 +33560,7 @@
       <c r="AL134" s="1" t="s">
         <v>1169</v>
       </c>
-      <c r="AM134" s="1" t="s">
+      <c r="AM134" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN134" s="1" t="s">
@@ -33648,7 +33648,7 @@
         <v>1206</v>
       </c>
       <c r="BP134" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ134" s="1">
         <v>21</v>
@@ -33775,7 +33775,7 @@
       <c r="AL135" s="1" t="s">
         <v>1170</v>
       </c>
-      <c r="AM135" s="1" t="s">
+      <c r="AM135" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN135" s="1" t="s">
@@ -33863,7 +33863,7 @@
         <v>1206</v>
       </c>
       <c r="BP135" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ135" s="1">
         <v>14</v>
@@ -33990,7 +33990,7 @@
       <c r="AL136" s="1" t="s">
         <v>1169</v>
       </c>
-      <c r="AM136" s="1" t="s">
+      <c r="AM136" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN136" s="1" t="s">
@@ -34078,7 +34078,7 @@
         <v>1206</v>
       </c>
       <c r="BP136" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ136" s="1">
         <v>21</v>
@@ -34205,7 +34205,7 @@
       <c r="AL137" s="1" t="s">
         <v>1170</v>
       </c>
-      <c r="AM137" s="1" t="s">
+      <c r="AM137" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN137" s="1" t="s">
@@ -34293,7 +34293,7 @@
         <v>1206</v>
       </c>
       <c r="BP137" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ137" s="1">
         <v>14</v>
@@ -34420,7 +34420,7 @@
       <c r="AL138" s="1" t="s">
         <v>1169</v>
       </c>
-      <c r="AM138" s="1" t="s">
+      <c r="AM138" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN138" s="1" t="s">
@@ -34508,7 +34508,7 @@
         <v>1206</v>
       </c>
       <c r="BP138" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ138" s="1">
         <v>21</v>
@@ -34635,7 +34635,7 @@
       <c r="AL139" s="1" t="s">
         <v>1170</v>
       </c>
-      <c r="AM139" s="1" t="s">
+      <c r="AM139" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN139" s="1" t="s">
@@ -34723,7 +34723,7 @@
         <v>1206</v>
       </c>
       <c r="BP139" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ139" s="1">
         <v>14</v>
@@ -34850,7 +34850,7 @@
       <c r="AL140" s="1" t="s">
         <v>1169</v>
       </c>
-      <c r="AM140" s="1" t="s">
+      <c r="AM140" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN140" s="1" t="s">
@@ -34938,7 +34938,7 @@
         <v>1206</v>
       </c>
       <c r="BP140" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ140" s="1">
         <v>21</v>
@@ -35065,7 +35065,7 @@
       <c r="AL141" s="1" t="s">
         <v>1170</v>
       </c>
-      <c r="AM141" s="1" t="s">
+      <c r="AM141" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN141" s="1" t="s">
@@ -35153,7 +35153,7 @@
         <v>1206</v>
       </c>
       <c r="BP141" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ141" s="1">
         <v>14</v>
@@ -35280,7 +35280,7 @@
       <c r="AL142" s="1" t="s">
         <v>1169</v>
       </c>
-      <c r="AM142" s="1" t="s">
+      <c r="AM142" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN142" s="1" t="s">
@@ -35368,7 +35368,7 @@
         <v>1206</v>
       </c>
       <c r="BP142" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ142" s="1">
         <v>21</v>
@@ -35495,7 +35495,7 @@
       <c r="AL143" s="1" t="s">
         <v>1170</v>
       </c>
-      <c r="AM143" s="1" t="s">
+      <c r="AM143" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN143" s="1" t="s">
@@ -35583,7 +35583,7 @@
         <v>1206</v>
       </c>
       <c r="BP143" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ143" s="1">
         <v>14</v>
@@ -35710,7 +35710,7 @@
       <c r="AL144" s="1" t="s">
         <v>1169</v>
       </c>
-      <c r="AM144" s="1" t="s">
+      <c r="AM144" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN144" s="1" t="s">
@@ -35798,7 +35798,7 @@
         <v>1206</v>
       </c>
       <c r="BP144" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ144" s="1">
         <v>21</v>
@@ -35925,7 +35925,7 @@
       <c r="AL145" s="1" t="s">
         <v>1170</v>
       </c>
-      <c r="AM145" s="1" t="s">
+      <c r="AM145" s="22" t="s">
         <v>650</v>
       </c>
       <c r="AN145" s="1" t="s">
@@ -36013,7 +36013,7 @@
         <v>1206</v>
       </c>
       <c r="BP145" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ145" s="1">
         <v>14</v>
@@ -36140,7 +36140,7 @@
       <c r="AL146" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="AM146" s="1" t="s">
+      <c r="AM146" s="22" t="s">
         <v>775</v>
       </c>
       <c r="AN146" s="1" t="s">
@@ -36228,7 +36228,7 @@
         <v>1206</v>
       </c>
       <c r="BP146" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ146" s="7">
         <v>0.38500000000000001</v>
@@ -36355,7 +36355,7 @@
       <c r="AL147" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="AM147" s="1" t="s">
+      <c r="AM147" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN147" s="1" t="s">
@@ -36443,7 +36443,7 @@
         <v>1206</v>
       </c>
       <c r="BP147" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ147" s="1">
         <v>10.8</v>
@@ -36570,7 +36570,7 @@
       <c r="AL148" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="AM148" s="1" t="s">
+      <c r="AM148" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN148" s="1" t="s">
@@ -36658,7 +36658,7 @@
         <v>1206</v>
       </c>
       <c r="BP148" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ148" s="1">
         <v>10.8</v>
@@ -36785,7 +36785,7 @@
       <c r="AL149" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="AM149" s="1" t="s">
+      <c r="AM149" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN149" s="1" t="s">
@@ -36873,7 +36873,7 @@
         <v>1206</v>
       </c>
       <c r="BP149" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ149" s="1">
         <v>10.8</v>
@@ -37000,7 +37000,7 @@
       <c r="AL150" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="AM150" s="1" t="s">
+      <c r="AM150" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN150" s="1" t="s">
@@ -37088,7 +37088,7 @@
         <v>1206</v>
       </c>
       <c r="BP150" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ150" s="1">
         <v>10.8</v>
@@ -37215,7 +37215,7 @@
       <c r="AL151" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="AM151" s="1" t="s">
+      <c r="AM151" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN151" s="1" t="s">
@@ -37303,7 +37303,7 @@
         <v>1206</v>
       </c>
       <c r="BP151" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ151" s="1">
         <v>4.3</v>
@@ -37430,7 +37430,7 @@
       <c r="AL152" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="AM152" s="1" t="s">
+      <c r="AM152" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN152" s="1" t="s">
@@ -37518,7 +37518,7 @@
         <v>1206</v>
       </c>
       <c r="BP152" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ152" s="1">
         <v>4.3</v>
@@ -37645,7 +37645,7 @@
       <c r="AL153" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="AM153" s="1" t="s">
+      <c r="AM153" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN153" s="1" t="s">
@@ -37733,7 +37733,7 @@
         <v>1206</v>
       </c>
       <c r="BP153" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ153" s="1">
         <v>1</v>
@@ -37860,7 +37860,7 @@
       <c r="AL154" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="AM154" s="1" t="s">
+      <c r="AM154" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN154" s="1" t="s">
@@ -37948,7 +37948,7 @@
         <v>1206</v>
       </c>
       <c r="BP154" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ154" s="1">
         <v>1</v>
@@ -38075,7 +38075,7 @@
       <c r="AL155" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="AM155" s="1" t="s">
+      <c r="AM155" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN155" s="1" t="s">
@@ -38163,7 +38163,7 @@
         <v>1206</v>
       </c>
       <c r="BP155" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ155" s="1">
         <v>1</v>
@@ -38290,7 +38290,7 @@
       <c r="AL156" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="AM156" s="1" t="s">
+      <c r="AM156" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN156" s="1" t="s">
@@ -38378,7 +38378,7 @@
         <v>1206</v>
       </c>
       <c r="BP156" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ156" s="1">
         <v>1</v>
@@ -38505,7 +38505,7 @@
       <c r="AL157" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="AM157" s="1" t="s">
+      <c r="AM157" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN157" s="1" t="s">
@@ -38593,7 +38593,7 @@
         <v>1206</v>
       </c>
       <c r="BP157" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ157" s="1">
         <v>1</v>
@@ -38720,7 +38720,7 @@
       <c r="AL158" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="AM158" s="1" t="s">
+      <c r="AM158" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN158" s="1" t="s">
@@ -38808,7 +38808,7 @@
         <v>1206</v>
       </c>
       <c r="BP158" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ158" s="1">
         <v>1</v>
@@ -38935,7 +38935,7 @@
       <c r="AL159" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM159" s="1" t="s">
+      <c r="AM159" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN159" s="1" t="s">
@@ -39150,7 +39150,7 @@
       <c r="AL160" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM160" s="1" t="s">
+      <c r="AM160" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN160" s="1" t="s">
@@ -39365,7 +39365,7 @@
       <c r="AL161" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM161" s="1" t="s">
+      <c r="AM161" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN161" s="1" t="s">
@@ -39453,7 +39453,7 @@
         <v>1206</v>
       </c>
       <c r="BP161" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ161" s="1">
         <v>0.2</v>
@@ -39580,7 +39580,7 @@
       <c r="AL162" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM162" s="1" t="s">
+      <c r="AM162" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN162" s="1" t="s">
@@ -39668,7 +39668,7 @@
         <v>1206</v>
       </c>
       <c r="BP162" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ162" s="1">
         <v>0.2</v>
@@ -39795,7 +39795,7 @@
       <c r="AL163" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM163" s="1" t="s">
+      <c r="AM163" s="22" t="s">
         <v>580</v>
       </c>
       <c r="AN163" s="1" t="s">
@@ -39883,7 +39883,7 @@
         <v>1206</v>
       </c>
       <c r="BP163" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ163" s="1">
         <v>20.486076598151243</v>
@@ -40010,7 +40010,7 @@
       <c r="AL164" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM164" s="1" t="s">
+      <c r="AM164" s="22" t="s">
         <v>580</v>
       </c>
       <c r="AN164" s="1" t="s">
@@ -40098,7 +40098,7 @@
         <v>1206</v>
       </c>
       <c r="BP164" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ164" s="1">
         <v>20.486076598151243</v>
@@ -40225,7 +40225,7 @@
       <c r="AL165" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM165" s="1" t="s">
+      <c r="AM165" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN165" s="1" t="s">
@@ -40313,7 +40313,7 @@
         <v>1206</v>
       </c>
       <c r="BP165" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ165" s="1">
         <v>20.486076598151243</v>
@@ -40440,7 +40440,7 @@
       <c r="AL166" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="AM166" s="1" t="s">
+      <c r="AM166" s="22" t="s">
         <v>725</v>
       </c>
       <c r="AN166" s="1" t="s">
@@ -40528,7 +40528,7 @@
         <v>1206</v>
       </c>
       <c r="BP166" s="11" t="s">
-        <v>1343</v>
+        <v>1337</v>
       </c>
       <c r="BQ166" s="1">
         <v>1.37</v>
@@ -40655,7 +40655,7 @@
       <c r="AL167" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM167" s="11" t="s">
+      <c r="AM167" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN167" s="11" t="s">
@@ -40743,7 +40743,7 @@
         <v>1207</v>
       </c>
       <c r="BP167" s="20" t="s">
-        <v>1340</v>
+        <v>1334</v>
       </c>
       <c r="BQ167" s="1">
         <v>0.184668989547038</v>
@@ -40752,7 +40752,7 @@
         <v>30</v>
       </c>
       <c r="BS167" s="1" t="s">
-        <v>1336</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="168" spans="1:71">
@@ -40870,7 +40870,7 @@
       <c r="AL168" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM168" s="11" t="s">
+      <c r="AM168" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN168" s="11" t="s">
@@ -40958,7 +40958,7 @@
         <v>1207</v>
       </c>
       <c r="BP168" s="20" t="s">
-        <v>1340</v>
+        <v>1334</v>
       </c>
       <c r="BQ168" s="1">
         <v>0.184668989547038</v>
@@ -40967,7 +40967,7 @@
         <v>30</v>
       </c>
       <c r="BS168" s="1" t="s">
-        <v>1336</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="169" spans="1:71">
@@ -41085,7 +41085,7 @@
       <c r="AL169" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM169" s="11" t="s">
+      <c r="AM169" s="22" t="s">
         <v>348</v>
       </c>
       <c r="AN169" s="11" t="s">
@@ -41173,7 +41173,7 @@
         <v>1207</v>
       </c>
       <c r="BP169" s="20" t="s">
-        <v>1340</v>
+        <v>1334</v>
       </c>
       <c r="BQ169" s="1">
         <v>0.184668989547038</v>
@@ -41182,7 +41182,7 @@
         <v>30</v>
       </c>
       <c r="BS169" s="1" t="s">
-        <v>1337</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="170" spans="1:71">
@@ -41300,7 +41300,7 @@
       <c r="AL170" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM170" s="11" t="s">
+      <c r="AM170" s="22" t="s">
         <v>348</v>
       </c>
       <c r="AN170" s="11" t="s">
@@ -41388,7 +41388,7 @@
         <v>1207</v>
       </c>
       <c r="BP170" s="20" t="s">
-        <v>1340</v>
+        <v>1334</v>
       </c>
       <c r="BQ170" s="1">
         <v>0.184668989547038</v>
@@ -41397,7 +41397,7 @@
         <v>30</v>
       </c>
       <c r="BS170" s="1" t="s">
-        <v>1337</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="171" spans="1:71">
@@ -41515,7 +41515,7 @@
       <c r="AL171" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM171" s="11" t="s">
+      <c r="AM171" s="22" t="s">
         <v>1122</v>
       </c>
       <c r="AN171" s="11" t="s">
@@ -41730,7 +41730,7 @@
       <c r="AL172" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM172" s="11" t="s">
+      <c r="AM172" s="22" t="s">
         <v>1123</v>
       </c>
       <c r="AO172" s="1">
@@ -41942,7 +41942,7 @@
       <c r="AL173" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM173" s="11" t="s">
+      <c r="AM173" s="22" t="s">
         <v>1126</v>
       </c>
       <c r="AN173" s="11" t="s">
@@ -42157,7 +42157,7 @@
       <c r="AL174" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM174" s="11" t="s">
+      <c r="AM174" s="22" t="s">
         <v>1127</v>
       </c>
       <c r="AN174" s="11" t="s">
@@ -42325,7 +42325,7 @@
         <v>314</v>
       </c>
       <c r="W175" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="X175" s="11" t="s">
         <v>312</v>
@@ -42372,8 +42372,8 @@
       <c r="AL175" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM175" s="11" t="s">
-        <v>1322</v>
+      <c r="AM175" s="22" t="s">
+        <v>1321</v>
       </c>
       <c r="AN175" s="11" t="s">
         <v>314</v>
@@ -42460,7 +42460,7 @@
         <v>1207</v>
       </c>
       <c r="BP175" s="1" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="BQ175" s="1">
         <v>0.2</v>
@@ -42469,7 +42469,7 @@
         <v>26.499666666666666</v>
       </c>
       <c r="BS175" s="1" t="s">
-        <v>1335</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="176" spans="1:71">
@@ -42540,7 +42540,7 @@
         <v>314</v>
       </c>
       <c r="W176" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="X176" s="11" t="s">
         <v>312</v>
@@ -42587,7 +42587,7 @@
       <c r="AL176" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM176" s="11" t="s">
+      <c r="AM176" s="22" t="s">
         <v>348</v>
       </c>
       <c r="AN176" s="11" t="s">
@@ -42675,7 +42675,7 @@
         <v>1207</v>
       </c>
       <c r="BP176" s="1" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="BQ176" s="1">
         <v>0.2</v>
@@ -42684,7 +42684,7 @@
         <v>26.499666666666666</v>
       </c>
       <c r="BS176" s="1" t="s">
-        <v>1334</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="177" spans="1:71">
@@ -42755,7 +42755,7 @@
         <v>314</v>
       </c>
       <c r="W177" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="X177" s="11" t="s">
         <v>312</v>
@@ -42802,8 +42802,8 @@
       <c r="AL177" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM177" s="11" t="s">
-        <v>1322</v>
+      <c r="AM177" s="22" t="s">
+        <v>1321</v>
       </c>
       <c r="AN177" s="11" t="s">
         <v>314</v>
@@ -42890,7 +42890,7 @@
         <v>1207</v>
       </c>
       <c r="BP177" s="1" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="BQ177" s="1">
         <v>0.2</v>
@@ -42899,7 +42899,7 @@
         <v>26.499666666666666</v>
       </c>
       <c r="BS177" s="1" t="s">
-        <v>1334</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="178" spans="1:71">
@@ -42967,7 +42967,7 @@
         <v>1</v>
       </c>
       <c r="V178" s="1" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="W178" s="1">
         <v>1981</v>
@@ -43017,7 +43017,7 @@
       <c r="AL178" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM178" s="11" t="s">
+      <c r="AM178" s="22" t="s">
         <v>317</v>
       </c>
       <c r="AN178" s="11" t="s">
@@ -43105,7 +43105,7 @@
         <v>1207</v>
       </c>
       <c r="BP178" s="1" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="BQ178" s="1">
         <v>0.2</v>
@@ -43114,7 +43114,7 @@
         <v>26.499666666666666</v>
       </c>
       <c r="BS178" s="1" t="s">
-        <v>1333</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="179" spans="1:71">
@@ -43182,7 +43182,7 @@
         <v>1</v>
       </c>
       <c r="V179" s="1" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="W179" s="1">
         <v>1981</v>
@@ -43232,8 +43232,8 @@
       <c r="AL179" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM179" s="11" t="s">
-        <v>1323</v>
+      <c r="AM179" s="22" t="s">
+        <v>317</v>
       </c>
       <c r="AN179" s="11" t="s">
         <v>658</v>
@@ -43320,7 +43320,7 @@
         <v>1207</v>
       </c>
       <c r="BP179" s="1" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="BQ179" s="1">
         <v>0.2</v>
@@ -43329,7 +43329,7 @@
         <v>26.499666666666666</v>
       </c>
       <c r="BS179" s="1" t="s">
-        <v>1328</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="180" spans="1:71">
@@ -43397,7 +43397,7 @@
         <v>1</v>
       </c>
       <c r="V180" s="1" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="W180" s="1">
         <v>1981</v>
@@ -43447,8 +43447,8 @@
       <c r="AL180" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM180" s="11" t="s">
-        <v>1324</v>
+      <c r="AM180" s="22" t="s">
+        <v>317</v>
       </c>
       <c r="AN180" s="11" t="s">
         <v>658</v>
@@ -43535,7 +43535,7 @@
         <v>1207</v>
       </c>
       <c r="BP180" s="1" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="BQ180" s="1">
         <v>0.2</v>
@@ -43544,7 +43544,7 @@
         <v>26.499666666666666</v>
       </c>
       <c r="BS180" s="1" t="s">
-        <v>1329</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="181" spans="1:71">
@@ -43612,7 +43612,7 @@
         <v>1</v>
       </c>
       <c r="V181" s="1" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="W181" s="1">
         <v>1981</v>
@@ -43662,8 +43662,8 @@
       <c r="AL181" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM181" s="11" t="s">
-        <v>1325</v>
+      <c r="AM181" s="22" t="s">
+        <v>317</v>
       </c>
       <c r="AN181" s="11" t="s">
         <v>658</v>
@@ -43750,7 +43750,7 @@
         <v>1207</v>
       </c>
       <c r="BP181" s="1" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="BQ181" s="1">
         <v>0.2</v>
@@ -43759,7 +43759,7 @@
         <v>26.499666666666666</v>
       </c>
       <c r="BS181" s="1" t="s">
-        <v>1330</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="182" spans="1:71">
@@ -43827,7 +43827,7 @@
         <v>1</v>
       </c>
       <c r="V182" s="1" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="W182" s="1">
         <v>1981</v>
@@ -43877,8 +43877,8 @@
       <c r="AL182" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM182" s="11" t="s">
-        <v>348</v>
+      <c r="AM182" s="22" t="s">
+        <v>1344</v>
       </c>
       <c r="AN182" s="11" t="s">
         <v>658</v>
@@ -43965,7 +43965,7 @@
         <v>1207</v>
       </c>
       <c r="BP182" s="1" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="BQ182" s="1">
         <v>0.2</v>
@@ -43974,7 +43974,7 @@
         <v>26.499666666666666</v>
       </c>
       <c r="BS182" s="1" t="s">
-        <v>1331</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="183" spans="1:71">
@@ -44042,7 +44042,7 @@
         <v>1</v>
       </c>
       <c r="V183" s="1" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="W183" s="1">
         <v>1981</v>
@@ -44092,8 +44092,8 @@
       <c r="AL183" s="11" t="s">
         <v>1134</v>
       </c>
-      <c r="AM183" s="11" t="s">
-        <v>1326</v>
+      <c r="AM183" s="22" t="s">
+        <v>317</v>
       </c>
       <c r="AN183" s="11" t="s">
         <v>658</v>
@@ -44180,7 +44180,7 @@
         <v>1207</v>
       </c>
       <c r="BP183" s="1" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="BQ183" s="1">
         <v>0.2</v>
@@ -44189,7 +44189,7 @@
         <v>26.499666666666666</v>
       </c>
       <c r="BS183" s="1" t="s">
-        <v>1332</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="184" spans="1:71">
@@ -44203,7 +44203,6 @@
       <c r="AJ184" s="11"/>
       <c r="AK184" s="11"/>
       <c r="AL184" s="11"/>
-      <c r="AM184" s="11"/>
       <c r="AN184" s="11"/>
     </row>
     <row r="185" spans="1:71">
@@ -44217,14 +44216,12 @@
       <c r="AJ185" s="11"/>
       <c r="AK185" s="11"/>
       <c r="AL185" s="11"/>
-      <c r="AM185" s="11"/>
       <c r="AN185" s="11"/>
     </row>
     <row r="186" spans="1:71">
       <c r="D186" s="1" t="s">
         <v>566</v>
       </c>
-      <c r="AM186" s="11"/>
     </row>
     <row r="187" spans="1:71">
       <c r="D187" s="1" t="s">

--- a/Output/Data/meta_analysis_data.xlsx
+++ b/Output/Data/meta_analysis_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emlim/Documents/PhD/Ch1-Meta-analysis/Output/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F30B687-9AC0-7A4C-B017-554736D137CF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93A5E7A-7308-9948-94BD-693409FCCD58}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1220" yWindow="460" windowWidth="26780" windowHeight="15940" activeTab="2" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
+    <workbookView xWindow="1220" yWindow="460" windowWidth="26780" windowHeight="15940" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
   </bookViews>
   <sheets>
     <sheet name="Include" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13622" uniqueCount="1426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13640" uniqueCount="1426">
   <si>
     <t>paper_num</t>
   </si>
@@ -37959,6 +37959,9 @@
       <c r="BT136" s="11" t="s">
         <v>1258</v>
       </c>
+      <c r="BU136" s="11" t="s">
+        <v>1259</v>
+      </c>
       <c r="BV136" s="11" t="s">
         <v>314</v>
       </c>
@@ -38199,6 +38202,9 @@
       <c r="BT137" s="11" t="s">
         <v>1258</v>
       </c>
+      <c r="BU137" s="11" t="s">
+        <v>1259</v>
+      </c>
       <c r="BV137" s="11" t="s">
         <v>314</v>
       </c>
@@ -38439,6 +38445,9 @@
       <c r="BT138" s="11" t="s">
         <v>1258</v>
       </c>
+      <c r="BU138" s="11" t="s">
+        <v>1259</v>
+      </c>
       <c r="BV138" s="11" t="s">
         <v>314</v>
       </c>
@@ -38679,6 +38688,9 @@
       <c r="BT139" s="11" t="s">
         <v>1258</v>
       </c>
+      <c r="BU139" s="11" t="s">
+        <v>1259</v>
+      </c>
       <c r="BV139" s="11" t="s">
         <v>314</v>
       </c>
@@ -38919,6 +38931,9 @@
       <c r="BT140" s="11" t="s">
         <v>1258</v>
       </c>
+      <c r="BU140" s="11" t="s">
+        <v>1259</v>
+      </c>
       <c r="BV140" s="11" t="s">
         <v>314</v>
       </c>
@@ -39159,6 +39174,9 @@
       <c r="BT141" s="11" t="s">
         <v>1258</v>
       </c>
+      <c r="BU141" s="11" t="s">
+        <v>1259</v>
+      </c>
       <c r="BV141" s="11" t="s">
         <v>314</v>
       </c>
@@ -39399,6 +39417,9 @@
       <c r="BT142" s="11" t="s">
         <v>1258</v>
       </c>
+      <c r="BU142" s="11" t="s">
+        <v>1259</v>
+      </c>
       <c r="BV142" s="11" t="s">
         <v>314</v>
       </c>
@@ -39639,6 +39660,9 @@
       <c r="BT143" s="11" t="s">
         <v>1258</v>
       </c>
+      <c r="BU143" s="11" t="s">
+        <v>1259</v>
+      </c>
       <c r="BV143" s="11" t="s">
         <v>314</v>
       </c>
@@ -39879,6 +39903,9 @@
       <c r="BT144" s="11" t="s">
         <v>1258</v>
       </c>
+      <c r="BU144" s="11" t="s">
+        <v>1259</v>
+      </c>
       <c r="BV144" s="11" t="s">
         <v>314</v>
       </c>
@@ -40119,6 +40146,9 @@
       <c r="BT145" s="11" t="s">
         <v>1258</v>
       </c>
+      <c r="BU145" s="11" t="s">
+        <v>1259</v>
+      </c>
       <c r="BV145" s="11" t="s">
         <v>314</v>
       </c>
@@ -40359,6 +40389,9 @@
       <c r="BT146" s="11" t="s">
         <v>1258</v>
       </c>
+      <c r="BU146" s="11" t="s">
+        <v>1259</v>
+      </c>
       <c r="BV146" s="11" t="s">
         <v>314</v>
       </c>
@@ -40599,6 +40632,9 @@
       <c r="BT147" s="11" t="s">
         <v>1258</v>
       </c>
+      <c r="BU147" s="11" t="s">
+        <v>1259</v>
+      </c>
       <c r="BV147" s="11" t="s">
         <v>314</v>
       </c>
@@ -40839,6 +40875,9 @@
       <c r="BT148" s="11" t="s">
         <v>1258</v>
       </c>
+      <c r="BU148" s="11" t="s">
+        <v>1259</v>
+      </c>
       <c r="BV148" s="11" t="s">
         <v>314</v>
       </c>
@@ -41079,6 +41118,9 @@
       <c r="BT149" s="11" t="s">
         <v>1258</v>
       </c>
+      <c r="BU149" s="11" t="s">
+        <v>1259</v>
+      </c>
       <c r="BV149" s="11" t="s">
         <v>314</v>
       </c>
@@ -41319,6 +41361,9 @@
       <c r="BT150" s="11" t="s">
         <v>1258</v>
       </c>
+      <c r="BU150" s="11" t="s">
+        <v>1259</v>
+      </c>
       <c r="BV150" s="11" t="s">
         <v>314</v>
       </c>
@@ -41559,6 +41604,9 @@
       <c r="BT151" s="11" t="s">
         <v>1258</v>
       </c>
+      <c r="BU151" s="11" t="s">
+        <v>1259</v>
+      </c>
       <c r="BV151" s="11" t="s">
         <v>314</v>
       </c>
@@ -41799,6 +41847,9 @@
       <c r="BT152" s="11" t="s">
         <v>1258</v>
       </c>
+      <c r="BU152" s="11" t="s">
+        <v>1259</v>
+      </c>
       <c r="BV152" s="11" t="s">
         <v>314</v>
       </c>
@@ -42038,6 +42089,9 @@
       </c>
       <c r="BT153" s="11" t="s">
         <v>1258</v>
+      </c>
+      <c r="BU153" s="11" t="s">
+        <v>1259</v>
       </c>
       <c r="BV153" s="11" t="s">
         <v>314</v>

--- a/Output/Data/meta_analysis_data.xlsx
+++ b/Output/Data/meta_analysis_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emlim/Documents/PhD/Ch1-Meta-analysis/Output/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93A5E7A-7308-9948-94BD-693409FCCD58}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B92A1E2-F52E-BF4D-B338-3AC8DC0967B5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1220" yWindow="460" windowWidth="26780" windowHeight="15940" xr2:uid="{40EEFA15-B542-CE42-935C-BBE1E5D9457F}"/>
   </bookViews>
